--- a/data/kee_lab_content.xlsx
+++ b/data/kee_lab_content.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jihoon/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jihoon/Downloads/kee-lab-v0.2-excel/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{786B5D0C-D775-AE4D-AB15-3D28A20E8821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5568C2BB-C6A4-4940-9594-2CA180D0EEE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="23400" windowHeight="21380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="107">
   <si>
     <t>KEE LAB 콘텐츠 관리 엑셀</t>
   </si>
@@ -300,10 +300,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>Lifelong Learning; Adult Education</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>jihoon.shin.916@gmail.com</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -313,6 +309,61 @@
   </si>
   <si>
     <t>shinjihoon.jpg</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>dr_2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>박시언</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ph.D. Candidate</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>양사동</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>YANG SIDONG</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>PARK SIEON</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>re_1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>HRD; Vocational Education Training; Lifelong Learning</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>김예빈</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KIM YEBIN</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ma</t>
+  </si>
+  <si>
+    <t>Master</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>kimyebin.jpeg</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>yangsidong.jpeg</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -448,11 +499,11 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -693,10 +744,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="40" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
+      <c r="B1" s="11"/>
     </row>
     <row r="2" spans="1:2" ht="30">
       <c r="A2" s="1" t="s">
@@ -881,7 +932,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="16">
+    <row r="3" spans="1:11" ht="32">
       <c r="A3" s="4" t="b">
         <v>1</v>
       </c>
@@ -904,56 +955,98 @@
         <v>37</v>
       </c>
       <c r="H3" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="I3" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="J3" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="K3" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="K3" s="5" t="s">
+    </row>
+    <row r="4" spans="1:11" ht="15">
+      <c r="A4" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
+      <c r="C4" s="6">
+        <v>10</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>95</v>
+      </c>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
     </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
+    <row r="5" spans="1:11" ht="15">
+      <c r="A5" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>93</v>
+      </c>
       <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
+      <c r="D5" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>95</v>
+      </c>
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
+      <c r="K5" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15">
+      <c r="A6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
+      <c r="D6" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>104</v>
+      </c>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
+      <c r="K6" s="6" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="6"/>

--- a/data/kee_lab_content.xlsx
+++ b/data/kee_lab_content.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jihoon/Downloads/kee-lab-v0.2-excel/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jihoon/Downloads/kee-lab-v0.3-excel-deploy/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5568C2BB-C6A4-4940-9594-2CA180D0EEE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1EAF8D-ED0A-E944-846D-506FF25C0ED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="23400" windowHeight="21380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -289,82 +289,82 @@
   </si>
   <si>
     <t>dr_1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>신지훈</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>SHIN JIHOON</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>HRD; Vocational Education Training; Lifelong Learning</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>jihoon.shin.916@gmail.com</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>www.linkedin.com/in/shinjihoon</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>shinjihoon.jpg</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>dr_2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>박시언</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>PARK SIEON</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Ph.D. Candidate</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>양사동</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>YANG SIDONG</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>PARK SIEON</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <t>yangsidong.jpeg</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>re_1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>HRD; Vocational Education Training; Lifelong Learning</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>김예빈</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>KIM YEBIN</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>ma</t>
   </si>
   <si>
     <t>Master</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>kimyebin.jpeg</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>yangsidong.jpeg</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -413,16 +413,16 @@
       <name val="Carlito"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
       <sz val="8"/>
       <name val="1973 미미월드 B"/>
       <family val="3"/>
       <charset val="129"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Carlito"/>
     </font>
   </fonts>
   <fills count="6">
@@ -465,7 +465,7 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -499,11 +499,11 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -744,10 +744,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="40" customHeight="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
+      <c r="B1" s="10"/>
     </row>
     <row r="2" spans="1:2" ht="30">
       <c r="A2" s="1" t="s">
@@ -841,7 +841,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -955,16 +955,16 @@
         <v>37</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="I3" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="I3" s="11" t="s">
         <v>91</v>
       </c>
+      <c r="J3" s="11" t="s">
+        <v>92</v>
+      </c>
       <c r="K3" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15">
@@ -972,22 +972,22 @@
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C4" s="6">
         <v>10</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>36</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
@@ -999,26 +999,26 @@
         <v>1</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>36</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
       <c r="K5" s="6" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15">
@@ -1026,26 +1026,26 @@
         <v>1</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
       <c r="K6" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -3584,7 +3584,7 @@
       <c r="K201" s="6"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
     <dataValidation type="list" sqref="A2:A501" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"TRUE,FALSE"</formula1>
@@ -3594,8 +3594,8 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="I3" r:id="rId1" xr:uid="{0025690D-B897-C249-8ACB-371D568ACCEC}"/>
-    <hyperlink ref="J3" r:id="rId2" xr:uid="{7A418F06-387D-AB46-A769-EEDE1AAC0F5B}"/>
+    <hyperlink ref="I3" r:id="rId1" xr:uid="{5A7F1B6D-0051-9240-9306-9EB3DC399A54}"/>
+    <hyperlink ref="J3" r:id="rId2" xr:uid="{E66F4FC8-FABE-A743-919A-43253486070E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5865,7 +5865,7 @@
       <c r="I201" s="6"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
     <dataValidation type="list" sqref="A2:A501" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"TRUE,FALSE"</formula1>
@@ -8756,7 +8756,7 @@
       <c r="L201" s="6"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
     <dataValidation type="list" sqref="A2:A501 C2:C501" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"TRUE,FALSE"</formula1>
@@ -12137,7 +12137,7 @@
       <c r="D501" s="9"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
     <dataValidation type="list" sqref="A2:A501 C2:C501" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"TRUE,FALSE"</formula1>
@@ -15314,7 +15314,7 @@
       <c r="D501" s="9"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
     <dataValidation type="list" sqref="A2:A501 C2:C501" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>"TRUE,FALSE"</formula1>

--- a/data/kee_lab_content.xlsx
+++ b/data/kee_lab_content.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jihoon/Downloads/kee-lab-v0.3-excel-deploy/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jihoon/Downloads/kee-lab-v0.4-direct-excel/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1EAF8D-ED0A-E944-846D-506FF25C0ED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9B4EA79-6E7F-9845-970C-750A6A8DE31E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3594,8 +3594,8 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="I3" r:id="rId1" xr:uid="{5A7F1B6D-0051-9240-9306-9EB3DC399A54}"/>
-    <hyperlink ref="J3" r:id="rId2" xr:uid="{E66F4FC8-FABE-A743-919A-43253486070E}"/>
+    <hyperlink ref="I3" r:id="rId1" xr:uid="{FD4A1E6D-79AE-704E-8FE6-17C76A310010}"/>
+    <hyperlink ref="J3" r:id="rId2" xr:uid="{D2D8C87D-53AF-5842-A44C-35B78F137B6C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/kee_lab_content.xlsx
+++ b/data/kee_lab_content.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jihoon/Downloads/kee-lab-v0.4-direct-excel/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jihoon/Downloads/kee-lab-v0.5-excel-managed/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9B4EA79-6E7F-9845-970C-750A6A8DE31E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8310E2D-42BD-224E-812D-96E5EA1EC2F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1280" yWindow="6940" windowWidth="27720" windowHeight="14820" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -19,13 +19,14 @@
     <sheet name="Publications" sheetId="4" r:id="rId4"/>
     <sheet name="News" sheetId="5" r:id="rId5"/>
     <sheet name="Gallery" sheetId="6" r:id="rId6"/>
+    <sheet name="Professor" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="242">
   <si>
     <t>KEE LAB 콘텐츠 관리 엑셀</t>
   </si>
@@ -288,83 +289,490 @@
     <t>2026 International Conference</t>
   </si>
   <si>
+    <t>university</t>
+  </si>
+  <si>
+    <t>department</t>
+  </si>
+  <si>
+    <t>office</t>
+  </si>
+  <si>
+    <t>home_bio</t>
+  </si>
+  <si>
+    <t>biography</t>
+  </si>
+  <si>
+    <t>기영화</t>
+  </si>
+  <si>
+    <t>Youngwha Kee</t>
+  </si>
+  <si>
+    <t>Professor</t>
+  </si>
+  <si>
+    <t>Soongsil University</t>
+  </si>
+  <si>
+    <t>Lifelong Learning | Adult Education | Community Learning | Community Well-being</t>
+  </si>
+  <si>
+    <t>사용법: 교수님 사진 파일을 assets/uploads/professor/ 폴더에 업로드한 뒤 photo_file에 파일명(예: youngwha-kee.jpg)을 정확히 입력하세요. active=TRUE인 첫 번째 행이 HOME과 Professor 페이지에 자동 반영됩니다. research_interests는 | 로 구분합니다.</t>
+  </si>
+  <si>
+    <t>youngwha-kee.jpg</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
     <t>dr_1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>신지훈</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>SHIN JIHOON</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>HRD; Vocational Education Training; Lifelong Learning</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>jihoon.shin.916@gmail.com</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>www.linkedin.com/in/shinjihoon</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>shinjihoon.jpg</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>dr_2</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>박시언</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>PARK SIEON</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Ph.D. Candidate</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>양사동</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>YANG SIDONG</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>yangsidong.jpeg</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>re_1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>김예빈</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>KIM YEBIN</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>ma</t>
   </si>
   <si>
     <t>Master</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>kimyebin.jpeg</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>alumni_dr1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>김주섭</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>alumni_dr2</t>
+  </si>
+  <si>
+    <t>최일완</t>
+  </si>
+  <si>
+    <t>alumni_dr3</t>
+  </si>
+  <si>
+    <t>이의수</t>
+  </si>
+  <si>
+    <t>alumni_dr4</t>
+  </si>
+  <si>
+    <t>김남숙</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>alumni_dr5</t>
+  </si>
+  <si>
+    <t>이부일</t>
+  </si>
+  <si>
+    <t>alumni_dr6</t>
+  </si>
+  <si>
+    <t>여문연</t>
+  </si>
+  <si>
+    <t>alumni_dr7</t>
+  </si>
+  <si>
+    <t>신재홍</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>alumni_dr8</t>
+  </si>
+  <si>
+    <t>이관배</t>
+  </si>
+  <si>
+    <t>alumni_dr9</t>
+  </si>
+  <si>
+    <t>김희아</t>
+  </si>
+  <si>
+    <t>alumni_dr10</t>
+  </si>
+  <si>
+    <t>박윤희</t>
+  </si>
+  <si>
+    <t>alumni_dr11</t>
+  </si>
+  <si>
+    <t>박표진</t>
+  </si>
+  <si>
+    <t>alumni_dr12</t>
+  </si>
+  <si>
+    <t>신영재</t>
+  </si>
+  <si>
+    <t>alumni_dr13</t>
+  </si>
+  <si>
+    <t>장뢰이</t>
+  </si>
+  <si>
+    <t>alumni_dr14</t>
+  </si>
+  <si>
+    <t>이영은</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>alumni_dr15</t>
+  </si>
+  <si>
+    <t>정대용</t>
+  </si>
+  <si>
+    <t>alumni_dr16</t>
+  </si>
+  <si>
+    <t>정서린</t>
+  </si>
+  <si>
+    <t>alumni_dr17</t>
+  </si>
+  <si>
+    <t>한우식</t>
+  </si>
+  <si>
+    <t>alumni_dr18</t>
+  </si>
+  <si>
+    <t>원지선</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>alumni_dr19</t>
+  </si>
+  <si>
+    <t>이석진</t>
+  </si>
+  <si>
+    <t>alumni_dr20</t>
+  </si>
+  <si>
+    <t>주옥채</t>
+  </si>
+  <si>
+    <t>alumni_dr21</t>
+  </si>
+  <si>
+    <t>차혜경</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>alumni_dr22</t>
+  </si>
+  <si>
+    <t>김태훈</t>
+  </si>
+  <si>
+    <t>alumni_dr23</t>
+  </si>
+  <si>
+    <t>우진중</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>alumni_dr24</t>
+  </si>
+  <si>
+    <t>배윤주</t>
+  </si>
+  <si>
+    <t>alumni_dr25</t>
+  </si>
+  <si>
+    <t>이윤진</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>alumni_dr26</t>
+  </si>
+  <si>
+    <t>조인묵</t>
+  </si>
+  <si>
+    <t>alumni_dr27</t>
+  </si>
+  <si>
+    <t>박종민</t>
+  </si>
+  <si>
+    <t>alumni_dr28</t>
+  </si>
+  <si>
+    <t>김민정</t>
+  </si>
+  <si>
+    <t>M.A.</t>
+  </si>
+  <si>
+    <t>alumni_dr29</t>
+  </si>
+  <si>
+    <t>김주현</t>
+  </si>
+  <si>
+    <t>alumni_dr30</t>
+  </si>
+  <si>
+    <t>김선복</t>
+  </si>
+  <si>
+    <t>alumni_dr31</t>
+  </si>
+  <si>
+    <t>권순영</t>
+  </si>
+  <si>
+    <t>alumni_dr32</t>
+  </si>
+  <si>
+    <t>박진홍</t>
+  </si>
+  <si>
+    <t>alumni_dr33</t>
+  </si>
+  <si>
+    <t>김선미</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>alumni_dr34</t>
+  </si>
+  <si>
+    <t>박혜영</t>
+  </si>
+  <si>
+    <t>alumni_dr35</t>
+  </si>
+  <si>
+    <t>정현수</t>
+  </si>
+  <si>
+    <t>alumni_dr36</t>
+  </si>
+  <si>
+    <t>구자봉</t>
+  </si>
+  <si>
+    <t>alumni_dr37</t>
+  </si>
+  <si>
+    <t>김연희</t>
+  </si>
+  <si>
+    <t>alumni_dr38</t>
+  </si>
+  <si>
+    <t>김영문</t>
+  </si>
+  <si>
+    <t>alumni_dr39</t>
+  </si>
+  <si>
+    <t>신효정</t>
+  </si>
+  <si>
+    <t>alumni_dr40</t>
+  </si>
+  <si>
+    <t>엄미란</t>
+  </si>
+  <si>
+    <t>alumni_dr41</t>
+  </si>
+  <si>
+    <t>이경희</t>
+  </si>
+  <si>
+    <t>alumni_dr42</t>
+  </si>
+  <si>
+    <t>이선정</t>
+  </si>
+  <si>
+    <t>alumni_dr43</t>
+  </si>
+  <si>
+    <t>김정진</t>
+  </si>
+  <si>
+    <t>alumni_dr44</t>
+  </si>
+  <si>
+    <t>alumni_dr45</t>
+  </si>
+  <si>
+    <t>함수정</t>
+  </si>
+  <si>
+    <t>alumni_dr46</t>
+  </si>
+  <si>
+    <t>alumni_dr47</t>
+  </si>
+  <si>
+    <t>노경남</t>
+  </si>
+  <si>
+    <t>alumni_dr48</t>
+  </si>
+  <si>
+    <t>허현수</t>
+  </si>
+  <si>
+    <t>alumni_dr49</t>
+  </si>
+  <si>
+    <t>고진석</t>
+  </si>
+  <si>
+    <t>alumni_dr50</t>
+  </si>
+  <si>
+    <t>김승현</t>
+  </si>
+  <si>
+    <t>alumni_dr51</t>
+  </si>
+  <si>
+    <t>이민호</t>
+  </si>
+  <si>
+    <t>alumni_dr52</t>
+  </si>
+  <si>
+    <t>임지회</t>
+  </si>
+  <si>
+    <t>alumni_dr53</t>
+  </si>
+  <si>
+    <t>조성현</t>
+  </si>
+  <si>
+    <t>alumni_dr54</t>
+  </si>
+  <si>
+    <t>유다솜</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>alumni_dr55</t>
+  </si>
+  <si>
+    <t>김예빈</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>alumni_dr56</t>
+  </si>
+  <si>
+    <t>신지훈</t>
+  </si>
+  <si>
+    <t>2025</t>
   </si>
 </sst>
 </file>
@@ -413,19 +821,19 @@
       <name val="Carlito"/>
     </font>
     <font>
+      <sz val="8"/>
+      <name val="1973 미미월드 B"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Carlito"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <name val="1973 미미월드 B"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -452,6 +860,16 @@
         <fgColor rgb="FFF6FCFC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF087FA5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF9FB"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -465,9 +883,9 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -499,11 +917,28 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -744,10 +1179,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="40" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
+      <c r="B1" s="13"/>
     </row>
     <row r="2" spans="1:2" ht="30">
       <c r="A2" s="1" t="s">
@@ -841,7 +1276,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -937,16 +1372,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="C3" s="5">
         <v>10</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>36</v>
@@ -955,16 +1390,16 @@
         <v>37</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>92</v>
+        <v>102</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>104</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15">
@@ -972,22 +1407,22 @@
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="C4" s="6">
         <v>10</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>36</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
@@ -999,26 +1434,26 @@
         <v>1</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>36</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
       <c r="K5" s="6" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15">
@@ -1026,26 +1461,26 @@
         <v>1</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
       <c r="K6" s="6" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -3584,7 +4019,7 @@
       <c r="K201" s="6"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <dataValidations count="2">
     <dataValidation type="list" sqref="A2:A501" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"TRUE,FALSE"</formula1>
@@ -3594,8 +4029,8 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="I3" r:id="rId1" xr:uid="{FD4A1E6D-79AE-704E-8FE6-17C76A310010}"/>
-    <hyperlink ref="J3" r:id="rId2" xr:uid="{D2D8C87D-53AF-5842-A44C-35B78F137B6C}"/>
+    <hyperlink ref="I3" r:id="rId1" xr:uid="{08EFECAE-71E2-7F41-8591-76D48AF259CA}"/>
+    <hyperlink ref="J3" r:id="rId2" xr:uid="{631B9F73-7FA5-AC4A-8DC8-BB9639841662}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3675,618 +4110,1178 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
+    <row r="3" spans="1:9" ht="16">
+      <c r="A3" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>120</v>
+      </c>
       <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
+      <c r="E3" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>121</v>
+      </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
+    <row r="4" spans="1:9" ht="16">
+      <c r="A4" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>123</v>
+      </c>
       <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
+      <c r="E4" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>121</v>
+      </c>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
     </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
+    <row r="5" spans="1:9" ht="16">
+      <c r="A5" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>125</v>
+      </c>
       <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
+      <c r="E5" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>121</v>
+      </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
     </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
+    <row r="6" spans="1:9" ht="16">
+      <c r="A6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>127</v>
+      </c>
       <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
+      <c r="E6" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
     </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
+    <row r="7" spans="1:9" ht="16">
+      <c r="A7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>130</v>
+      </c>
       <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
+      <c r="E7" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
     </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
+    <row r="8" spans="1:9" ht="16">
+      <c r="A8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>132</v>
+      </c>
       <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
+      <c r="E8" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
     </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
+    <row r="9" spans="1:9" ht="16">
+      <c r="A9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>134</v>
+      </c>
       <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
+      <c r="E9" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>135</v>
+      </c>
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
       <c r="I9" s="6"/>
     </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
+    <row r="10" spans="1:9" ht="16">
+      <c r="A10" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>137</v>
+      </c>
       <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
+      <c r="E10" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>135</v>
+      </c>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
     </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
+    <row r="11" spans="1:9" ht="16">
+      <c r="A11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>139</v>
+      </c>
       <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
+      <c r="E11" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>135</v>
+      </c>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
     </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
+    <row r="12" spans="1:9" ht="16">
+      <c r="A12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>141</v>
+      </c>
       <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
+      <c r="E12" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>135</v>
+      </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
     </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
+    <row r="13" spans="1:9" ht="16">
+      <c r="A13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>143</v>
+      </c>
       <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
+      <c r="E13" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>135</v>
+      </c>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
     </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
+    <row r="14" spans="1:9" ht="16">
+      <c r="A14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>145</v>
+      </c>
       <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
+      <c r="E14" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>135</v>
+      </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
     </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
+    <row r="15" spans="1:9" ht="16">
+      <c r="A15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>147</v>
+      </c>
       <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
+      <c r="E15" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>135</v>
+      </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
     </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
+    <row r="16" spans="1:9" ht="16">
+      <c r="A16" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>149</v>
+      </c>
       <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
+      <c r="E16" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>150</v>
+      </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
     </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
+    <row r="17" spans="1:9" ht="16">
+      <c r="A17" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>152</v>
+      </c>
       <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
+      <c r="E17" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>150</v>
+      </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
     </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
+    <row r="18" spans="1:9" ht="16">
+      <c r="A18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>154</v>
+      </c>
       <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
+      <c r="E18" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>150</v>
+      </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
     </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
+    <row r="19" spans="1:9" ht="16">
+      <c r="A19" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>156</v>
+      </c>
       <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
+      <c r="E19" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>150</v>
+      </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
     </row>
-    <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
+    <row r="20" spans="1:9" ht="16">
+      <c r="A20" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>158</v>
+      </c>
       <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
+      <c r="E20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>159</v>
+      </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
     </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
+    <row r="21" spans="1:9" ht="16">
+      <c r="A21" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>161</v>
+      </c>
       <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
+      <c r="E21" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>159</v>
+      </c>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
     </row>
-    <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
+    <row r="22" spans="1:9" ht="16">
+      <c r="A22" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>163</v>
+      </c>
       <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
+      <c r="E22" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>159</v>
+      </c>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
     </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
+    <row r="23" spans="1:9" ht="16">
+      <c r="A23" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>165</v>
+      </c>
       <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
+      <c r="E23" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>166</v>
+      </c>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
     </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
+    <row r="24" spans="1:9" ht="16">
+      <c r="A24" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>168</v>
+      </c>
       <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
+      <c r="E24" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>166</v>
+      </c>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
     </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
+    <row r="25" spans="1:9" ht="16">
+      <c r="A25" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>170</v>
+      </c>
       <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
+      <c r="E25" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>171</v>
+      </c>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
       <c r="I25" s="6"/>
     </row>
-    <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
+    <row r="26" spans="1:9" ht="16">
+      <c r="A26" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>173</v>
+      </c>
       <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
+      <c r="E26" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>171</v>
+      </c>
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
     </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
+    <row r="27" spans="1:9" ht="16">
+      <c r="A27" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>175</v>
+      </c>
       <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
+      <c r="E27" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>176</v>
+      </c>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
     </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
+    <row r="28" spans="1:9" ht="16">
+      <c r="A28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>178</v>
+      </c>
       <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
+      <c r="E28" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>176</v>
+      </c>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
     </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
+    <row r="29" spans="1:9" ht="16">
+      <c r="A29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>180</v>
+      </c>
       <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
+      <c r="E29" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>176</v>
+      </c>
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
       <c r="I29" s="6"/>
     </row>
-    <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
+    <row r="30" spans="1:9" ht="16">
+      <c r="A30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>182</v>
+      </c>
       <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
+      <c r="E30" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>135</v>
+      </c>
       <c r="G30" s="6"/>
       <c r="H30" s="6"/>
       <c r="I30" s="6"/>
     </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
+    <row r="31" spans="1:9" ht="16">
+      <c r="A31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>185</v>
+      </c>
       <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
+      <c r="E31" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F31" s="15" t="s">
+        <v>135</v>
+      </c>
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
     </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
+    <row r="32" spans="1:9" ht="16">
+      <c r="A32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>187</v>
+      </c>
       <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
+      <c r="E32" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F32" s="15" t="s">
+        <v>135</v>
+      </c>
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
       <c r="I32" s="6"/>
     </row>
-    <row r="33" spans="1:9">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
+    <row r="33" spans="1:9" ht="16">
+      <c r="A33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>189</v>
+      </c>
       <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
+      <c r="E33" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F33" s="15" t="s">
+        <v>150</v>
+      </c>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
       <c r="I33" s="6"/>
     </row>
-    <row r="34" spans="1:9">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
+    <row r="34" spans="1:9" ht="16">
+      <c r="A34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>191</v>
+      </c>
       <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
+      <c r="E34" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F34" s="15" t="s">
+        <v>150</v>
+      </c>
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
       <c r="I34" s="6"/>
     </row>
-    <row r="35" spans="1:9">
-      <c r="A35" s="6"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
+    <row r="35" spans="1:9" ht="16">
+      <c r="A35" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>193</v>
+      </c>
       <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
+      <c r="E35" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F35" s="15" t="s">
+        <v>194</v>
+      </c>
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
       <c r="I35" s="6"/>
     </row>
-    <row r="36" spans="1:9">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
+    <row r="36" spans="1:9" ht="16">
+      <c r="A36" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>196</v>
+      </c>
       <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
+      <c r="E36" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F36" s="15" t="s">
+        <v>194</v>
+      </c>
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
       <c r="I36" s="6"/>
     </row>
-    <row r="37" spans="1:9">
-      <c r="A37" s="6"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
+    <row r="37" spans="1:9" ht="16">
+      <c r="A37" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>198</v>
+      </c>
       <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
+      <c r="E37" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F37" s="15" t="s">
+        <v>194</v>
+      </c>
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
       <c r="I37" s="6"/>
     </row>
-    <row r="38" spans="1:9">
-      <c r="A38" s="6"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
+    <row r="38" spans="1:9" ht="16">
+      <c r="A38" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>200</v>
+      </c>
       <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
+      <c r="E38" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F38" s="15" t="s">
+        <v>194</v>
+      </c>
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
     </row>
-    <row r="39" spans="1:9">
-      <c r="A39" s="6"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
+    <row r="39" spans="1:9" ht="16">
+      <c r="A39" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>202</v>
+      </c>
       <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
+      <c r="E39" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F39" s="15" t="s">
+        <v>194</v>
+      </c>
       <c r="G39" s="6"/>
       <c r="H39" s="6"/>
       <c r="I39" s="6"/>
     </row>
-    <row r="40" spans="1:9">
-      <c r="A40" s="6"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
+    <row r="40" spans="1:9" ht="16">
+      <c r="A40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>204</v>
+      </c>
       <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
+      <c r="E40" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F40" s="15" t="s">
+        <v>194</v>
+      </c>
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
       <c r="I40" s="6"/>
     </row>
-    <row r="41" spans="1:9">
-      <c r="A41" s="6"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
+    <row r="41" spans="1:9" ht="16">
+      <c r="A41" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>206</v>
+      </c>
       <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
+      <c r="E41" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F41" s="15" t="s">
+        <v>194</v>
+      </c>
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
       <c r="I41" s="6"/>
     </row>
-    <row r="42" spans="1:9">
-      <c r="A42" s="6"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
+    <row r="42" spans="1:9" ht="16">
+      <c r="A42" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>208</v>
+      </c>
       <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
+      <c r="E42" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F42" s="15" t="s">
+        <v>194</v>
+      </c>
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
       <c r="I42" s="6"/>
     </row>
-    <row r="43" spans="1:9">
-      <c r="A43" s="6"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
+    <row r="43" spans="1:9" ht="16">
+      <c r="A43" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>210</v>
+      </c>
       <c r="D43" s="6"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
+      <c r="E43" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F43" s="15" t="s">
+        <v>194</v>
+      </c>
       <c r="G43" s="6"/>
       <c r="H43" s="6"/>
       <c r="I43" s="6"/>
     </row>
-    <row r="44" spans="1:9">
-      <c r="A44" s="6"/>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
+    <row r="44" spans="1:9" ht="16">
+      <c r="A44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>212</v>
+      </c>
       <c r="D44" s="6"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
+      <c r="E44" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F44" s="15" t="s">
+        <v>194</v>
+      </c>
       <c r="G44" s="6"/>
       <c r="H44" s="6"/>
       <c r="I44" s="6"/>
     </row>
-    <row r="45" spans="1:9">
-      <c r="A45" s="6"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
+    <row r="45" spans="1:9" ht="16">
+      <c r="A45" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>214</v>
+      </c>
       <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
+      <c r="E45" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F45" s="15" t="s">
+        <v>159</v>
+      </c>
       <c r="G45" s="6"/>
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
     </row>
-    <row r="46" spans="1:9">
-      <c r="A46" s="6"/>
-      <c r="B46" s="6"/>
-      <c r="C46" s="6"/>
+    <row r="46" spans="1:9" ht="16">
+      <c r="A46" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>173</v>
+      </c>
       <c r="D46" s="6"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
+      <c r="E46" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F46" s="15" t="s">
+        <v>159</v>
+      </c>
       <c r="G46" s="6"/>
       <c r="H46" s="6"/>
       <c r="I46" s="6"/>
     </row>
-    <row r="47" spans="1:9">
-      <c r="A47" s="6"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6"/>
+    <row r="47" spans="1:9" ht="16">
+      <c r="A47" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>217</v>
+      </c>
       <c r="D47" s="6"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6"/>
+      <c r="E47" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F47" s="15" t="s">
+        <v>159</v>
+      </c>
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
       <c r="I47" s="6"/>
     </row>
-    <row r="48" spans="1:9">
-      <c r="A48" s="6"/>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
+    <row r="48" spans="1:9" ht="16">
+      <c r="A48" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>175</v>
+      </c>
       <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
+      <c r="E48" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F48" s="15" t="s">
+        <v>166</v>
+      </c>
       <c r="G48" s="6"/>
       <c r="H48" s="6"/>
       <c r="I48" s="6"/>
     </row>
-    <row r="49" spans="1:9">
-      <c r="A49" s="6"/>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
+    <row r="49" spans="1:9" ht="16">
+      <c r="A49" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>220</v>
+      </c>
       <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
+      <c r="E49" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F49" s="15" t="s">
+        <v>166</v>
+      </c>
       <c r="G49" s="6"/>
       <c r="H49" s="6"/>
       <c r="I49" s="6"/>
     </row>
-    <row r="50" spans="1:9">
-      <c r="A50" s="6"/>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6"/>
+    <row r="50" spans="1:9" ht="16">
+      <c r="A50" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>222</v>
+      </c>
       <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
+      <c r="E50" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F50" s="15" t="s">
+        <v>166</v>
+      </c>
       <c r="G50" s="6"/>
       <c r="H50" s="6"/>
       <c r="I50" s="6"/>
     </row>
-    <row r="51" spans="1:9">
-      <c r="A51" s="6"/>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
+    <row r="51" spans="1:9" ht="16">
+      <c r="A51" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>224</v>
+      </c>
       <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6"/>
+      <c r="E51" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F51" s="15" t="s">
+        <v>171</v>
+      </c>
       <c r="G51" s="6"/>
       <c r="H51" s="6"/>
       <c r="I51" s="6"/>
     </row>
-    <row r="52" spans="1:9">
-      <c r="A52" s="6"/>
-      <c r="B52" s="6"/>
-      <c r="C52" s="6"/>
+    <row r="52" spans="1:9" ht="16">
+      <c r="A52" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>226</v>
+      </c>
       <c r="D52" s="6"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="6"/>
+      <c r="E52" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F52" s="15" t="s">
+        <v>171</v>
+      </c>
       <c r="G52" s="6"/>
       <c r="H52" s="6"/>
       <c r="I52" s="6"/>
     </row>
-    <row r="53" spans="1:9">
-      <c r="A53" s="6"/>
-      <c r="B53" s="6"/>
-      <c r="C53" s="6"/>
+    <row r="53" spans="1:9" ht="16">
+      <c r="A53" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>228</v>
+      </c>
       <c r="D53" s="6"/>
-      <c r="E53" s="6"/>
-      <c r="F53" s="6"/>
+      <c r="E53" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F53" s="15" t="s">
+        <v>171</v>
+      </c>
       <c r="G53" s="6"/>
       <c r="H53" s="6"/>
       <c r="I53" s="6"/>
     </row>
-    <row r="54" spans="1:9">
-      <c r="A54" s="6"/>
-      <c r="B54" s="6"/>
-      <c r="C54" s="6"/>
+    <row r="54" spans="1:9" ht="16">
+      <c r="A54" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>230</v>
+      </c>
       <c r="D54" s="6"/>
-      <c r="E54" s="6"/>
-      <c r="F54" s="6"/>
+      <c r="E54" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F54" s="15" t="s">
+        <v>171</v>
+      </c>
       <c r="G54" s="6"/>
       <c r="H54" s="6"/>
       <c r="I54" s="6"/>
     </row>
-    <row r="55" spans="1:9">
-      <c r="A55" s="6"/>
-      <c r="B55" s="6"/>
-      <c r="C55" s="6"/>
+    <row r="55" spans="1:9" ht="16">
+      <c r="A55" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>232</v>
+      </c>
       <c r="D55" s="6"/>
-      <c r="E55" s="6"/>
-      <c r="F55" s="6"/>
+      <c r="E55" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F55" s="15" t="s">
+        <v>171</v>
+      </c>
       <c r="G55" s="6"/>
       <c r="H55" s="6"/>
       <c r="I55" s="6"/>
     </row>
-    <row r="56" spans="1:9">
-      <c r="A56" s="6"/>
-      <c r="B56" s="6"/>
-      <c r="C56" s="6"/>
+    <row r="56" spans="1:9" ht="16">
+      <c r="A56" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="C56" s="15" t="s">
+        <v>234</v>
+      </c>
       <c r="D56" s="6"/>
-      <c r="E56" s="6"/>
-      <c r="F56" s="6"/>
+      <c r="E56" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F56" s="15" t="s">
+        <v>235</v>
+      </c>
       <c r="G56" s="6"/>
       <c r="H56" s="6"/>
       <c r="I56" s="6"/>
     </row>
-    <row r="57" spans="1:9">
-      <c r="A57" s="6"/>
-      <c r="B57" s="6"/>
-      <c r="C57" s="6"/>
+    <row r="57" spans="1:9" ht="16">
+      <c r="A57" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="C57" s="15" t="s">
+        <v>237</v>
+      </c>
       <c r="D57" s="6"/>
-      <c r="E57" s="6"/>
-      <c r="F57" s="6"/>
+      <c r="E57" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F57" s="15" t="s">
+        <v>238</v>
+      </c>
       <c r="G57" s="6"/>
       <c r="H57" s="6"/>
       <c r="I57" s="6"/>
     </row>
-    <row r="58" spans="1:9">
-      <c r="A58" s="6"/>
-      <c r="B58" s="6"/>
-      <c r="C58" s="6"/>
+    <row r="58" spans="1:9" ht="16">
+      <c r="A58" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>240</v>
+      </c>
       <c r="D58" s="6"/>
-      <c r="E58" s="6"/>
-      <c r="F58" s="6"/>
+      <c r="E58" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F58" s="15" t="s">
+        <v>241</v>
+      </c>
       <c r="G58" s="6"/>
       <c r="H58" s="6"/>
       <c r="I58" s="6"/>
@@ -5865,7 +6860,7 @@
       <c r="I201" s="6"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <dataValidations count="2">
     <dataValidation type="list" sqref="A2:A501" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"TRUE,FALSE"</formula1>
@@ -8756,7 +9751,7 @@
       <c r="L201" s="6"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <dataValidations count="2">
     <dataValidation type="list" sqref="A2:A501 C2:C501" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"TRUE,FALSE"</formula1>
@@ -12137,7 +13132,7 @@
       <c r="D501" s="9"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <dataValidations count="2">
     <dataValidation type="list" sqref="A2:A501 C2:C501" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"TRUE,FALSE"</formula1>
@@ -15314,7 +16309,7 @@
       <c r="D501" s="9"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <dataValidations count="2">
     <dataValidation type="list" sqref="A2:A501 C2:C501" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>"TRUE,FALSE"</formula1>
@@ -15325,4 +16320,119 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="10" max="10" width="38" customWidth="1"/>
+    <col min="11" max="11" width="48" customWidth="1"/>
+    <col min="12" max="12" width="44" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="16">
+      <c r="A1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="30">
+      <c r="A2" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="64" customHeight="1">
+      <c r="A4" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A4:L4"/>
+  </mergeCells>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="A2:A200" xr:uid="{00000000-0002-0000-0600-000000000000}">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/kee_lab_content.xlsx
+++ b/data/kee_lab_content.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jihoon/Downloads/kee-lab-v0.5-excel-managed/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8310E2D-42BD-224E-812D-96E5EA1EC2F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DFCFE6E-40B6-5B4B-B3D6-39952D7F4F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1280" yWindow="6940" windowWidth="27720" windowHeight="14820" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1280" yWindow="6940" windowWidth="27720" windowHeight="14820" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -931,14 +931,14 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1179,10 +1179,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="40" customHeight="1">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
+      <c r="B1" s="15"/>
     </row>
     <row r="2" spans="1:2" ht="30">
       <c r="A2" s="1" t="s">
@@ -1436,7 +1436,9 @@
       <c r="B5" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="6"/>
+      <c r="C5" s="6">
+        <v>10</v>
+      </c>
       <c r="D5" s="6" t="s">
         <v>110</v>
       </c>
@@ -1463,7 +1465,9 @@
       <c r="B6" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="C6" s="6"/>
+      <c r="C6" s="6">
+        <v>10</v>
+      </c>
       <c r="D6" s="6" t="s">
         <v>114</v>
       </c>
@@ -4117,14 +4121,14 @@
       <c r="B3" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="13" t="s">
         <v>120</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="13" t="s">
         <v>121</v>
       </c>
       <c r="G3" s="6"/>
@@ -4138,14 +4142,14 @@
       <c r="B4" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="13" t="s">
         <v>123</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="13" t="s">
         <v>121</v>
       </c>
       <c r="G4" s="6"/>
@@ -4159,14 +4163,14 @@
       <c r="B5" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="13" t="s">
         <v>125</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="13" t="s">
         <v>121</v>
       </c>
       <c r="G5" s="6"/>
@@ -4180,14 +4184,14 @@
       <c r="B6" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="13" t="s">
         <v>127</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="13" t="s">
         <v>128</v>
       </c>
       <c r="G6" s="6"/>
@@ -4201,14 +4205,14 @@
       <c r="B7" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="13" t="s">
         <v>130</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="13" t="s">
         <v>128</v>
       </c>
       <c r="G7" s="6"/>
@@ -4222,14 +4226,14 @@
       <c r="B8" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="13" t="s">
         <v>132</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="13" t="s">
         <v>128</v>
       </c>
       <c r="G8" s="6"/>
@@ -4243,14 +4247,14 @@
       <c r="B9" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="13" t="s">
         <v>134</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="13" t="s">
         <v>135</v>
       </c>
       <c r="G9" s="6"/>
@@ -4264,14 +4268,14 @@
       <c r="B10" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="13" t="s">
         <v>137</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="13" t="s">
         <v>135</v>
       </c>
       <c r="G10" s="6"/>
@@ -4285,14 +4289,14 @@
       <c r="B11" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="13" t="s">
         <v>139</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="13" t="s">
         <v>135</v>
       </c>
       <c r="G11" s="6"/>
@@ -4306,14 +4310,14 @@
       <c r="B12" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="13" t="s">
         <v>141</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="F12" s="13" t="s">
         <v>135</v>
       </c>
       <c r="G12" s="6"/>
@@ -4327,14 +4331,14 @@
       <c r="B13" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="13" t="s">
         <v>143</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F13" s="13" t="s">
         <v>135</v>
       </c>
       <c r="G13" s="6"/>
@@ -4348,14 +4352,14 @@
       <c r="B14" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="13" t="s">
         <v>145</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="F14" s="13" t="s">
         <v>135</v>
       </c>
       <c r="G14" s="6"/>
@@ -4369,14 +4373,14 @@
       <c r="B15" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="13" t="s">
         <v>147</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="F15" s="13" t="s">
         <v>135</v>
       </c>
       <c r="G15" s="6"/>
@@ -4390,14 +4394,14 @@
       <c r="B16" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="13" t="s">
         <v>149</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="F16" s="13" t="s">
         <v>150</v>
       </c>
       <c r="G16" s="6"/>
@@ -4411,14 +4415,14 @@
       <c r="B17" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="13" t="s">
         <v>152</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="15" t="s">
+      <c r="F17" s="13" t="s">
         <v>150</v>
       </c>
       <c r="G17" s="6"/>
@@ -4432,14 +4436,14 @@
       <c r="B18" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="13" t="s">
         <v>154</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F18" s="15" t="s">
+      <c r="F18" s="13" t="s">
         <v>150</v>
       </c>
       <c r="G18" s="6"/>
@@ -4453,14 +4457,14 @@
       <c r="B19" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="13" t="s">
         <v>156</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F19" s="15" t="s">
+      <c r="F19" s="13" t="s">
         <v>150</v>
       </c>
       <c r="G19" s="6"/>
@@ -4474,14 +4478,14 @@
       <c r="B20" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="13" t="s">
         <v>158</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F20" s="15" t="s">
+      <c r="F20" s="13" t="s">
         <v>159</v>
       </c>
       <c r="G20" s="6"/>
@@ -4495,14 +4499,14 @@
       <c r="B21" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="13" t="s">
         <v>161</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F21" s="15" t="s">
+      <c r="F21" s="13" t="s">
         <v>159</v>
       </c>
       <c r="G21" s="6"/>
@@ -4516,14 +4520,14 @@
       <c r="B22" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="13" t="s">
         <v>163</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F22" s="15" t="s">
+      <c r="F22" s="13" t="s">
         <v>159</v>
       </c>
       <c r="G22" s="6"/>
@@ -4537,14 +4541,14 @@
       <c r="B23" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="13" t="s">
         <v>165</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F23" s="15" t="s">
+      <c r="F23" s="13" t="s">
         <v>166</v>
       </c>
       <c r="G23" s="6"/>
@@ -4558,14 +4562,14 @@
       <c r="B24" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="13" t="s">
         <v>168</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F24" s="15" t="s">
+      <c r="F24" s="13" t="s">
         <v>166</v>
       </c>
       <c r="G24" s="6"/>
@@ -4579,14 +4583,14 @@
       <c r="B25" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="13" t="s">
         <v>170</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F25" s="15" t="s">
+      <c r="F25" s="13" t="s">
         <v>171</v>
       </c>
       <c r="G25" s="6"/>
@@ -4600,14 +4604,14 @@
       <c r="B26" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="13" t="s">
         <v>173</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F26" s="15" t="s">
+      <c r="F26" s="13" t="s">
         <v>171</v>
       </c>
       <c r="G26" s="6"/>
@@ -4621,14 +4625,14 @@
       <c r="B27" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="13" t="s">
         <v>175</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F27" s="15" t="s">
+      <c r="F27" s="13" t="s">
         <v>176</v>
       </c>
       <c r="G27" s="6"/>
@@ -4642,14 +4646,14 @@
       <c r="B28" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="13" t="s">
         <v>178</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F28" s="15" t="s">
+      <c r="F28" s="13" t="s">
         <v>176</v>
       </c>
       <c r="G28" s="6"/>
@@ -4663,14 +4667,14 @@
       <c r="B29" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="13" t="s">
         <v>180</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F29" s="15" t="s">
+      <c r="F29" s="13" t="s">
         <v>176</v>
       </c>
       <c r="G29" s="6"/>
@@ -4684,14 +4688,14 @@
       <c r="B30" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C30" s="13" t="s">
         <v>182</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F30" s="15" t="s">
+      <c r="F30" s="13" t="s">
         <v>135</v>
       </c>
       <c r="G30" s="6"/>
@@ -4705,14 +4709,14 @@
       <c r="B31" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="13" t="s">
         <v>185</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F31" s="15" t="s">
+      <c r="F31" s="13" t="s">
         <v>135</v>
       </c>
       <c r="G31" s="6"/>
@@ -4726,14 +4730,14 @@
       <c r="B32" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="13" t="s">
         <v>187</v>
       </c>
       <c r="D32" s="6"/>
       <c r="E32" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F32" s="15" t="s">
+      <c r="F32" s="13" t="s">
         <v>135</v>
       </c>
       <c r="G32" s="6"/>
@@ -4747,14 +4751,14 @@
       <c r="B33" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="C33" s="13" t="s">
         <v>189</v>
       </c>
       <c r="D33" s="6"/>
       <c r="E33" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F33" s="15" t="s">
+      <c r="F33" s="13" t="s">
         <v>150</v>
       </c>
       <c r="G33" s="6"/>
@@ -4768,14 +4772,14 @@
       <c r="B34" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="13" t="s">
         <v>191</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F34" s="15" t="s">
+      <c r="F34" s="13" t="s">
         <v>150</v>
       </c>
       <c r="G34" s="6"/>
@@ -4789,14 +4793,14 @@
       <c r="B35" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="13" t="s">
         <v>193</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F35" s="15" t="s">
+      <c r="F35" s="13" t="s">
         <v>194</v>
       </c>
       <c r="G35" s="6"/>
@@ -4810,14 +4814,14 @@
       <c r="B36" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="C36" s="15" t="s">
+      <c r="C36" s="13" t="s">
         <v>196</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F36" s="15" t="s">
+      <c r="F36" s="13" t="s">
         <v>194</v>
       </c>
       <c r="G36" s="6"/>
@@ -4831,14 +4835,14 @@
       <c r="B37" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="C37" s="13" t="s">
         <v>198</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F37" s="15" t="s">
+      <c r="F37" s="13" t="s">
         <v>194</v>
       </c>
       <c r="G37" s="6"/>
@@ -4852,14 +4856,14 @@
       <c r="B38" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="C38" s="15" t="s">
+      <c r="C38" s="13" t="s">
         <v>200</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F38" s="15" t="s">
+      <c r="F38" s="13" t="s">
         <v>194</v>
       </c>
       <c r="G38" s="6"/>
@@ -4873,14 +4877,14 @@
       <c r="B39" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="13" t="s">
         <v>202</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F39" s="15" t="s">
+      <c r="F39" s="13" t="s">
         <v>194</v>
       </c>
       <c r="G39" s="6"/>
@@ -4894,14 +4898,14 @@
       <c r="B40" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="C40" s="15" t="s">
+      <c r="C40" s="13" t="s">
         <v>204</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F40" s="15" t="s">
+      <c r="F40" s="13" t="s">
         <v>194</v>
       </c>
       <c r="G40" s="6"/>
@@ -4915,14 +4919,14 @@
       <c r="B41" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="C41" s="13" t="s">
         <v>206</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F41" s="15" t="s">
+      <c r="F41" s="13" t="s">
         <v>194</v>
       </c>
       <c r="G41" s="6"/>
@@ -4936,14 +4940,14 @@
       <c r="B42" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="13" t="s">
         <v>208</v>
       </c>
       <c r="D42" s="6"/>
       <c r="E42" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F42" s="15" t="s">
+      <c r="F42" s="13" t="s">
         <v>194</v>
       </c>
       <c r="G42" s="6"/>
@@ -4957,14 +4961,14 @@
       <c r="B43" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="C43" s="15" t="s">
+      <c r="C43" s="13" t="s">
         <v>210</v>
       </c>
       <c r="D43" s="6"/>
       <c r="E43" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F43" s="15" t="s">
+      <c r="F43" s="13" t="s">
         <v>194</v>
       </c>
       <c r="G43" s="6"/>
@@ -4978,14 +4982,14 @@
       <c r="B44" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="C44" s="15" t="s">
+      <c r="C44" s="13" t="s">
         <v>212</v>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F44" s="15" t="s">
+      <c r="F44" s="13" t="s">
         <v>194</v>
       </c>
       <c r="G44" s="6"/>
@@ -4999,14 +5003,14 @@
       <c r="B45" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="C45" s="15" t="s">
+      <c r="C45" s="13" t="s">
         <v>214</v>
       </c>
       <c r="D45" s="6"/>
       <c r="E45" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F45" s="15" t="s">
+      <c r="F45" s="13" t="s">
         <v>159</v>
       </c>
       <c r="G45" s="6"/>
@@ -5020,14 +5024,14 @@
       <c r="B46" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="C46" s="15" t="s">
+      <c r="C46" s="13" t="s">
         <v>173</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F46" s="15" t="s">
+      <c r="F46" s="13" t="s">
         <v>159</v>
       </c>
       <c r="G46" s="6"/>
@@ -5041,14 +5045,14 @@
       <c r="B47" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="C47" s="13" t="s">
         <v>217</v>
       </c>
       <c r="D47" s="6"/>
       <c r="E47" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F47" s="15" t="s">
+      <c r="F47" s="13" t="s">
         <v>159</v>
       </c>
       <c r="G47" s="6"/>
@@ -5062,14 +5066,14 @@
       <c r="B48" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="C48" s="15" t="s">
+      <c r="C48" s="13" t="s">
         <v>175</v>
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F48" s="15" t="s">
+      <c r="F48" s="13" t="s">
         <v>166</v>
       </c>
       <c r="G48" s="6"/>
@@ -5083,14 +5087,14 @@
       <c r="B49" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="C49" s="15" t="s">
+      <c r="C49" s="13" t="s">
         <v>220</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F49" s="15" t="s">
+      <c r="F49" s="13" t="s">
         <v>166</v>
       </c>
       <c r="G49" s="6"/>
@@ -5104,14 +5108,14 @@
       <c r="B50" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="C50" s="15" t="s">
+      <c r="C50" s="13" t="s">
         <v>222</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F50" s="15" t="s">
+      <c r="F50" s="13" t="s">
         <v>166</v>
       </c>
       <c r="G50" s="6"/>
@@ -5125,14 +5129,14 @@
       <c r="B51" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="C51" s="15" t="s">
+      <c r="C51" s="13" t="s">
         <v>224</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F51" s="15" t="s">
+      <c r="F51" s="13" t="s">
         <v>171</v>
       </c>
       <c r="G51" s="6"/>
@@ -5146,14 +5150,14 @@
       <c r="B52" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="C52" s="15" t="s">
+      <c r="C52" s="13" t="s">
         <v>226</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F52" s="15" t="s">
+      <c r="F52" s="13" t="s">
         <v>171</v>
       </c>
       <c r="G52" s="6"/>
@@ -5167,14 +5171,14 @@
       <c r="B53" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="C53" s="15" t="s">
+      <c r="C53" s="13" t="s">
         <v>228</v>
       </c>
       <c r="D53" s="6"/>
       <c r="E53" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F53" s="15" t="s">
+      <c r="F53" s="13" t="s">
         <v>171</v>
       </c>
       <c r="G53" s="6"/>
@@ -5188,14 +5192,14 @@
       <c r="B54" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="C54" s="15" t="s">
+      <c r="C54" s="13" t="s">
         <v>230</v>
       </c>
       <c r="D54" s="6"/>
       <c r="E54" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F54" s="15" t="s">
+      <c r="F54" s="13" t="s">
         <v>171</v>
       </c>
       <c r="G54" s="6"/>
@@ -5209,14 +5213,14 @@
       <c r="B55" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="C55" s="15" t="s">
+      <c r="C55" s="13" t="s">
         <v>232</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F55" s="15" t="s">
+      <c r="F55" s="13" t="s">
         <v>171</v>
       </c>
       <c r="G55" s="6"/>
@@ -5230,14 +5234,14 @@
       <c r="B56" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="C56" s="15" t="s">
+      <c r="C56" s="13" t="s">
         <v>234</v>
       </c>
       <c r="D56" s="6"/>
       <c r="E56" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F56" s="15" t="s">
+      <c r="F56" s="13" t="s">
         <v>235</v>
       </c>
       <c r="G56" s="6"/>
@@ -5251,14 +5255,14 @@
       <c r="B57" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="C57" s="15" t="s">
+      <c r="C57" s="13" t="s">
         <v>237</v>
       </c>
       <c r="D57" s="6"/>
       <c r="E57" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F57" s="15" t="s">
+      <c r="F57" s="13" t="s">
         <v>238</v>
       </c>
       <c r="G57" s="6"/>
@@ -5272,14 +5276,14 @@
       <c r="B58" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="C58" s="15" t="s">
+      <c r="C58" s="13" t="s">
         <v>240</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F58" s="15" t="s">
+      <c r="F58" s="13" t="s">
         <v>241</v>
       </c>
       <c r="G58" s="6"/>

--- a/data/kee_lab_content.xlsx
+++ b/data/kee_lab_content.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jihoon/Downloads/kee-lab-v0.5-excel-managed/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jihoon/Downloads/lab-main/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DFCFE6E-40B6-5B4B-B3D6-39952D7F4F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B34D64CB-6CD1-2949-9C17-11E15F66FC45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1280" yWindow="6940" windowWidth="27720" windowHeight="14820" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11420" yWindow="2520" windowWidth="24000" windowHeight="14820" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="253">
   <si>
     <t>KEE LAB 콘텐츠 관리 엑셀</t>
   </si>
@@ -394,13 +394,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>ma</t>
-  </si>
-  <si>
-    <t>Master</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>kimyebin.jpeg</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -773,6 +766,69 @@
   </si>
   <si>
     <t>2025</t>
+  </si>
+  <si>
+    <t>Master · Researcher</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>bio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>education</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>숭실대학교 IT대학 글로벌미디어학부 공학사
+숭실대학교 사회과학대학 평생교육학과 문학사(복수전공)
+숭실대학교 일반대학원 평생교육학과 교육학석사</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>researcher</t>
+  </si>
+  <si>
+    <t>숭실대학교 인문대학 기독교학과 문학사
+FH Vorarlberg (Austria) Exchange Student
+숭실대학교 일반대학원 평생교육학과 교육학석사</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>jane6920@naver.com</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>질적연구 &amp; 내러티브 탐구; 다문화교육 &amp; 외국인 유학생 대학 적응; 전환학습 &amp; 성인교육; 국제개발협력 &amp; 성인교육</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>한국대학교육협의회 (재직중)
+외국인 유학생 학습경험 및 대학적응 연구 프로젝트 수행 중
+국제개발협력(ODA) 교육과정 개발 및 수요 분석 프로젝트 참여
+김예빈, 기영화. (2026). 한국 체류 유럽권 교환학생의 전환학습 경험에 관한 내러티브 탐구. 문화교류와 다문화교육, 15(1), 227–251.
+김예빈. (2025). 고등교육기관 단기 교환학생의 전환적 여정에 관한 내러티브 탐구 [석사학위논문, 숭실대학교].</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lifelong Education; Adult &amp; Vocational Education; Global HRD; Career Development &amp; Transition</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>179571233@qq.com</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>우한화샤이공대학교 영어교육학과 학사 졸업
+홍콩교육대학교 대학원 교육리더십학과 석사 졸업
+숭실대학교 일반대학원 평생교육학과 박사 수료</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>숭실대학교 국제처 유학생 지원 및 관리 (2025.03 ~ 2026.08)
+평생교육 및 성인교육 관련 연구 수행 (2024 ~ 현재)
+외국인 유학생의 대학생활적응 및 고등교육 관련 연구 수행 (2025 ~ 현재)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -885,7 +941,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -928,17 +984,40 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1179,10 +1258,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="40" customHeight="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
+      <c r="B1" s="13"/>
     </row>
     <row r="2" spans="1:2" ht="30">
       <c r="A2" s="1" t="s">
@@ -1283,23 +1362,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K201"/>
+  <dimension ref="A1:M201"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="36" customWidth="1"/>
-    <col min="9" max="9" width="28" customWidth="1"/>
-    <col min="10" max="10" width="30" customWidth="1"/>
-    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="1" max="1" width="10" style="15" customWidth="1"/>
+    <col min="2" max="2" width="20" style="15" customWidth="1"/>
+    <col min="3" max="3" width="12" style="15" customWidth="1"/>
+    <col min="4" max="4" width="16" style="15" customWidth="1"/>
+    <col min="5" max="5" width="20" style="15" customWidth="1"/>
+    <col min="6" max="6" width="14" style="15" customWidth="1"/>
+    <col min="7" max="7" width="20" style="15" customWidth="1"/>
+    <col min="8" max="8" width="36" style="15" customWidth="1"/>
+    <col min="9" max="9" width="28" style="15" customWidth="1"/>
+    <col min="10" max="10" width="30" style="15" customWidth="1"/>
+    <col min="11" max="11" width="24" style="15" customWidth="1"/>
+    <col min="12" max="12" width="61.1640625" style="15" customWidth="1"/>
+    <col min="13" max="13" width="50" style="15" customWidth="1"/>
+    <col min="14" max="16384" width="8.83203125" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="40" customHeight="1">
+    <row r="1" spans="1:13" ht="40" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
@@ -1333,2694 +1415,2724 @@
       <c r="K1" s="3" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="16">
-      <c r="A2" s="4" t="b">
+      <c r="L1" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="16">
+      <c r="A2" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="17">
         <v>10</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5" t="s">
+      <c r="J2" s="17"/>
+      <c r="K2" s="17" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="32">
-      <c r="A3" s="4" t="b">
+    <row r="3" spans="1:13" ht="45">
+      <c r="A3" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C3" s="5">
-        <v>10</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="17">
+        <v>1</v>
+      </c>
+      <c r="D3" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="17" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="15">
-      <c r="A4" s="4" t="b">
+      <c r="M3" s="19" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="15">
+      <c r="A4" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="C4" s="6">
-        <v>10</v>
-      </c>
-      <c r="D4" s="6" t="s">
+      <c r="C4" s="20">
+        <v>2</v>
+      </c>
+      <c r="D4" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-    </row>
-    <row r="5" spans="1:11" ht="15">
-      <c r="A5" s="4" t="b">
+      <c r="H4" s="20"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="M4" s="19"/>
+    </row>
+    <row r="5" spans="1:13" ht="45">
+      <c r="A5" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="6">
-        <v>10</v>
-      </c>
-      <c r="D5" s="6" t="s">
+      <c r="C5" s="20">
+        <v>3</v>
+      </c>
+      <c r="D5" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6" t="s">
+      <c r="H5" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="I5" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" ht="15">
-      <c r="A6" s="4" t="b">
+      <c r="L5" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="M5" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="120">
+      <c r="A6" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="C6" s="6">
-        <v>10</v>
-      </c>
-      <c r="D6" s="6" t="s">
+      <c r="C6" s="20">
+        <v>4</v>
+      </c>
+      <c r="D6" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="20" t="s">
+        <v>244</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="I6" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="G6" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
+      <c r="L6" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="M6" s="19" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="20"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="20"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="20"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="20"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="20"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="20"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
+      <c r="A17" s="20"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
+      <c r="A20" s="20"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
+      <c r="A21" s="20"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
+      <c r="A22" s="20"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
+      <c r="A23" s="20"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
+      <c r="A24" s="20"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6"/>
+      <c r="A25" s="20"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
+      <c r="A26" s="20"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
+      <c r="A27" s="20"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="20"/>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
+      <c r="A28" s="20"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="20"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
+      <c r="A29" s="20"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
+      <c r="A30" s="20"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="20"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
+      <c r="A31" s="20"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="20"/>
     </row>
     <row r="32" spans="1:11">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="6"/>
+      <c r="A32" s="20"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="20"/>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
+      <c r="A33" s="20"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="20"/>
+      <c r="K33" s="20"/>
     </row>
     <row r="34" spans="1:11">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="6"/>
+      <c r="A34" s="20"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="20"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="6"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="6"/>
+      <c r="A35" s="20"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="20"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="20"/>
+      <c r="K35" s="20"/>
     </row>
     <row r="36" spans="1:11">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="6"/>
+      <c r="A36" s="20"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="20"/>
+      <c r="K36" s="20"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="6"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="6"/>
+      <c r="A37" s="20"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
+      <c r="H37" s="20"/>
+      <c r="I37" s="20"/>
+      <c r="J37" s="20"/>
+      <c r="K37" s="20"/>
     </row>
     <row r="38" spans="1:11">
-      <c r="A38" s="6"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
+      <c r="A38" s="20"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
+      <c r="H38" s="20"/>
+      <c r="I38" s="20"/>
+      <c r="J38" s="20"/>
+      <c r="K38" s="20"/>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="6"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
+      <c r="A39" s="20"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="20"/>
+      <c r="H39" s="20"/>
+      <c r="I39" s="20"/>
+      <c r="J39" s="20"/>
+      <c r="K39" s="20"/>
     </row>
     <row r="40" spans="1:11">
-      <c r="A40" s="6"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="6"/>
-      <c r="K40" s="6"/>
+      <c r="A40" s="20"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="20"/>
+      <c r="K40" s="20"/>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="6"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6"/>
-      <c r="J41" s="6"/>
-      <c r="K41" s="6"/>
+      <c r="A41" s="20"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="20"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+      <c r="I41" s="20"/>
+      <c r="J41" s="20"/>
+      <c r="K41" s="20"/>
     </row>
     <row r="42" spans="1:11">
-      <c r="A42" s="6"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="6"/>
-      <c r="K42" s="6"/>
+      <c r="A42" s="20"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+      <c r="I42" s="20"/>
+      <c r="J42" s="20"/>
+      <c r="K42" s="20"/>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="6"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="6"/>
-      <c r="K43" s="6"/>
+      <c r="A43" s="20"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="20"/>
+      <c r="H43" s="20"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="20"/>
+      <c r="K43" s="20"/>
     </row>
     <row r="44" spans="1:11">
-      <c r="A44" s="6"/>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="6"/>
-      <c r="K44" s="6"/>
+      <c r="A44" s="20"/>
+      <c r="B44" s="20"/>
+      <c r="C44" s="20"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="20"/>
+      <c r="H44" s="20"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="20"/>
+      <c r="K44" s="20"/>
     </row>
     <row r="45" spans="1:11">
-      <c r="A45" s="6"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6"/>
-      <c r="J45" s="6"/>
-      <c r="K45" s="6"/>
+      <c r="A45" s="20"/>
+      <c r="B45" s="20"/>
+      <c r="C45" s="20"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20"/>
+      <c r="H45" s="20"/>
+      <c r="I45" s="20"/>
+      <c r="J45" s="20"/>
+      <c r="K45" s="20"/>
     </row>
     <row r="46" spans="1:11">
-      <c r="A46" s="6"/>
-      <c r="B46" s="6"/>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="6"/>
-      <c r="K46" s="6"/>
+      <c r="A46" s="20"/>
+      <c r="B46" s="20"/>
+      <c r="C46" s="20"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
+      <c r="H46" s="20"/>
+      <c r="I46" s="20"/>
+      <c r="J46" s="20"/>
+      <c r="K46" s="20"/>
     </row>
     <row r="47" spans="1:11">
-      <c r="A47" s="6"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="6"/>
-      <c r="K47" s="6"/>
+      <c r="A47" s="20"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="20"/>
+      <c r="H47" s="20"/>
+      <c r="I47" s="20"/>
+      <c r="J47" s="20"/>
+      <c r="K47" s="20"/>
     </row>
     <row r="48" spans="1:11">
-      <c r="A48" s="6"/>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="6"/>
-      <c r="K48" s="6"/>
+      <c r="A48" s="20"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="20"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="20"/>
+      <c r="H48" s="20"/>
+      <c r="I48" s="20"/>
+      <c r="J48" s="20"/>
+      <c r="K48" s="20"/>
     </row>
     <row r="49" spans="1:11">
-      <c r="A49" s="6"/>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6"/>
-      <c r="J49" s="6"/>
-      <c r="K49" s="6"/>
+      <c r="A49" s="20"/>
+      <c r="B49" s="20"/>
+      <c r="C49" s="20"/>
+      <c r="D49" s="20"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="20"/>
+      <c r="G49" s="20"/>
+      <c r="H49" s="20"/>
+      <c r="I49" s="20"/>
+      <c r="J49" s="20"/>
+      <c r="K49" s="20"/>
     </row>
     <row r="50" spans="1:11">
-      <c r="A50" s="6"/>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="6"/>
-      <c r="K50" s="6"/>
+      <c r="A50" s="20"/>
+      <c r="B50" s="20"/>
+      <c r="C50" s="20"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="20"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="20"/>
+      <c r="H50" s="20"/>
+      <c r="I50" s="20"/>
+      <c r="J50" s="20"/>
+      <c r="K50" s="20"/>
     </row>
     <row r="51" spans="1:11">
-      <c r="A51" s="6"/>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="6"/>
-      <c r="K51" s="6"/>
+      <c r="A51" s="20"/>
+      <c r="B51" s="20"/>
+      <c r="C51" s="20"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="20"/>
+      <c r="G51" s="20"/>
+      <c r="H51" s="20"/>
+      <c r="I51" s="20"/>
+      <c r="J51" s="20"/>
+      <c r="K51" s="20"/>
     </row>
     <row r="52" spans="1:11">
-      <c r="A52" s="6"/>
-      <c r="B52" s="6"/>
-      <c r="C52" s="6"/>
-      <c r="D52" s="6"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="6"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6"/>
-      <c r="J52" s="6"/>
-      <c r="K52" s="6"/>
+      <c r="A52" s="20"/>
+      <c r="B52" s="20"/>
+      <c r="C52" s="20"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="20"/>
+      <c r="G52" s="20"/>
+      <c r="H52" s="20"/>
+      <c r="I52" s="20"/>
+      <c r="J52" s="20"/>
+      <c r="K52" s="20"/>
     </row>
     <row r="53" spans="1:11">
-      <c r="A53" s="6"/>
-      <c r="B53" s="6"/>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="6"/>
-      <c r="F53" s="6"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="6"/>
-      <c r="K53" s="6"/>
+      <c r="A53" s="20"/>
+      <c r="B53" s="20"/>
+      <c r="C53" s="20"/>
+      <c r="D53" s="20"/>
+      <c r="E53" s="20"/>
+      <c r="F53" s="20"/>
+      <c r="G53" s="20"/>
+      <c r="H53" s="20"/>
+      <c r="I53" s="20"/>
+      <c r="J53" s="20"/>
+      <c r="K53" s="20"/>
     </row>
     <row r="54" spans="1:11">
-      <c r="A54" s="6"/>
-      <c r="B54" s="6"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6"/>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="6"/>
-      <c r="K54" s="6"/>
+      <c r="A54" s="20"/>
+      <c r="B54" s="20"/>
+      <c r="C54" s="20"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="20"/>
+      <c r="F54" s="20"/>
+      <c r="G54" s="20"/>
+      <c r="H54" s="20"/>
+      <c r="I54" s="20"/>
+      <c r="J54" s="20"/>
+      <c r="K54" s="20"/>
     </row>
     <row r="55" spans="1:11">
-      <c r="A55" s="6"/>
-      <c r="B55" s="6"/>
-      <c r="C55" s="6"/>
-      <c r="D55" s="6"/>
-      <c r="E55" s="6"/>
-      <c r="F55" s="6"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="6"/>
-      <c r="J55" s="6"/>
-      <c r="K55" s="6"/>
+      <c r="A55" s="20"/>
+      <c r="B55" s="20"/>
+      <c r="C55" s="20"/>
+      <c r="D55" s="20"/>
+      <c r="E55" s="20"/>
+      <c r="F55" s="20"/>
+      <c r="G55" s="20"/>
+      <c r="H55" s="20"/>
+      <c r="I55" s="20"/>
+      <c r="J55" s="20"/>
+      <c r="K55" s="20"/>
     </row>
     <row r="56" spans="1:11">
-      <c r="A56" s="6"/>
-      <c r="B56" s="6"/>
-      <c r="C56" s="6"/>
-      <c r="D56" s="6"/>
-      <c r="E56" s="6"/>
-      <c r="F56" s="6"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="6"/>
-      <c r="J56" s="6"/>
-      <c r="K56" s="6"/>
+      <c r="A56" s="20"/>
+      <c r="B56" s="20"/>
+      <c r="C56" s="20"/>
+      <c r="D56" s="20"/>
+      <c r="E56" s="20"/>
+      <c r="F56" s="20"/>
+      <c r="G56" s="20"/>
+      <c r="H56" s="20"/>
+      <c r="I56" s="20"/>
+      <c r="J56" s="20"/>
+      <c r="K56" s="20"/>
     </row>
     <row r="57" spans="1:11">
-      <c r="A57" s="6"/>
-      <c r="B57" s="6"/>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
-      <c r="E57" s="6"/>
-      <c r="F57" s="6"/>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="6"/>
-      <c r="J57" s="6"/>
-      <c r="K57" s="6"/>
+      <c r="A57" s="20"/>
+      <c r="B57" s="20"/>
+      <c r="C57" s="20"/>
+      <c r="D57" s="20"/>
+      <c r="E57" s="20"/>
+      <c r="F57" s="20"/>
+      <c r="G57" s="20"/>
+      <c r="H57" s="20"/>
+      <c r="I57" s="20"/>
+      <c r="J57" s="20"/>
+      <c r="K57" s="20"/>
     </row>
     <row r="58" spans="1:11">
-      <c r="A58" s="6"/>
-      <c r="B58" s="6"/>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="6"/>
-      <c r="F58" s="6"/>
-      <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="6"/>
-      <c r="J58" s="6"/>
-      <c r="K58" s="6"/>
+      <c r="A58" s="20"/>
+      <c r="B58" s="20"/>
+      <c r="C58" s="20"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="20"/>
+      <c r="F58" s="20"/>
+      <c r="G58" s="20"/>
+      <c r="H58" s="20"/>
+      <c r="I58" s="20"/>
+      <c r="J58" s="20"/>
+      <c r="K58" s="20"/>
     </row>
     <row r="59" spans="1:11">
-      <c r="A59" s="6"/>
-      <c r="B59" s="6"/>
-      <c r="C59" s="6"/>
-      <c r="D59" s="6"/>
-      <c r="E59" s="6"/>
-      <c r="F59" s="6"/>
-      <c r="G59" s="6"/>
-      <c r="H59" s="6"/>
-      <c r="I59" s="6"/>
-      <c r="J59" s="6"/>
-      <c r="K59" s="6"/>
+      <c r="A59" s="20"/>
+      <c r="B59" s="20"/>
+      <c r="C59" s="20"/>
+      <c r="D59" s="20"/>
+      <c r="E59" s="20"/>
+      <c r="F59" s="20"/>
+      <c r="G59" s="20"/>
+      <c r="H59" s="20"/>
+      <c r="I59" s="20"/>
+      <c r="J59" s="20"/>
+      <c r="K59" s="20"/>
     </row>
     <row r="60" spans="1:11">
-      <c r="A60" s="6"/>
-      <c r="B60" s="6"/>
-      <c r="C60" s="6"/>
-      <c r="D60" s="6"/>
-      <c r="E60" s="6"/>
-      <c r="F60" s="6"/>
-      <c r="G60" s="6"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="6"/>
-      <c r="J60" s="6"/>
-      <c r="K60" s="6"/>
+      <c r="A60" s="20"/>
+      <c r="B60" s="20"/>
+      <c r="C60" s="20"/>
+      <c r="D60" s="20"/>
+      <c r="E60" s="20"/>
+      <c r="F60" s="20"/>
+      <c r="G60" s="20"/>
+      <c r="H60" s="20"/>
+      <c r="I60" s="20"/>
+      <c r="J60" s="20"/>
+      <c r="K60" s="20"/>
     </row>
     <row r="61" spans="1:11">
-      <c r="A61" s="6"/>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
-      <c r="E61" s="6"/>
-      <c r="F61" s="6"/>
-      <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
-      <c r="I61" s="6"/>
-      <c r="J61" s="6"/>
-      <c r="K61" s="6"/>
+      <c r="A61" s="20"/>
+      <c r="B61" s="20"/>
+      <c r="C61" s="20"/>
+      <c r="D61" s="20"/>
+      <c r="E61" s="20"/>
+      <c r="F61" s="20"/>
+      <c r="G61" s="20"/>
+      <c r="H61" s="20"/>
+      <c r="I61" s="20"/>
+      <c r="J61" s="20"/>
+      <c r="K61" s="20"/>
     </row>
     <row r="62" spans="1:11">
-      <c r="A62" s="6"/>
-      <c r="B62" s="6"/>
-      <c r="C62" s="6"/>
-      <c r="D62" s="6"/>
-      <c r="E62" s="6"/>
-      <c r="F62" s="6"/>
-      <c r="G62" s="6"/>
-      <c r="H62" s="6"/>
-      <c r="I62" s="6"/>
-      <c r="J62" s="6"/>
-      <c r="K62" s="6"/>
+      <c r="A62" s="20"/>
+      <c r="B62" s="20"/>
+      <c r="C62" s="20"/>
+      <c r="D62" s="20"/>
+      <c r="E62" s="20"/>
+      <c r="F62" s="20"/>
+      <c r="G62" s="20"/>
+      <c r="H62" s="20"/>
+      <c r="I62" s="20"/>
+      <c r="J62" s="20"/>
+      <c r="K62" s="20"/>
     </row>
     <row r="63" spans="1:11">
-      <c r="A63" s="6"/>
-      <c r="B63" s="6"/>
-      <c r="C63" s="6"/>
-      <c r="D63" s="6"/>
-      <c r="E63" s="6"/>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
-      <c r="I63" s="6"/>
-      <c r="J63" s="6"/>
-      <c r="K63" s="6"/>
+      <c r="A63" s="20"/>
+      <c r="B63" s="20"/>
+      <c r="C63" s="20"/>
+      <c r="D63" s="20"/>
+      <c r="E63" s="20"/>
+      <c r="F63" s="20"/>
+      <c r="G63" s="20"/>
+      <c r="H63" s="20"/>
+      <c r="I63" s="20"/>
+      <c r="J63" s="20"/>
+      <c r="K63" s="20"/>
     </row>
     <row r="64" spans="1:11">
-      <c r="A64" s="6"/>
-      <c r="B64" s="6"/>
-      <c r="C64" s="6"/>
-      <c r="D64" s="6"/>
-      <c r="E64" s="6"/>
-      <c r="F64" s="6"/>
-      <c r="G64" s="6"/>
-      <c r="H64" s="6"/>
-      <c r="I64" s="6"/>
-      <c r="J64" s="6"/>
-      <c r="K64" s="6"/>
+      <c r="A64" s="20"/>
+      <c r="B64" s="20"/>
+      <c r="C64" s="20"/>
+      <c r="D64" s="20"/>
+      <c r="E64" s="20"/>
+      <c r="F64" s="20"/>
+      <c r="G64" s="20"/>
+      <c r="H64" s="20"/>
+      <c r="I64" s="20"/>
+      <c r="J64" s="20"/>
+      <c r="K64" s="20"/>
     </row>
     <row r="65" spans="1:11">
-      <c r="A65" s="6"/>
-      <c r="B65" s="6"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
-      <c r="E65" s="6"/>
-      <c r="F65" s="6"/>
-      <c r="G65" s="6"/>
-      <c r="H65" s="6"/>
-      <c r="I65" s="6"/>
-      <c r="J65" s="6"/>
-      <c r="K65" s="6"/>
+      <c r="A65" s="20"/>
+      <c r="B65" s="20"/>
+      <c r="C65" s="20"/>
+      <c r="D65" s="20"/>
+      <c r="E65" s="20"/>
+      <c r="F65" s="20"/>
+      <c r="G65" s="20"/>
+      <c r="H65" s="20"/>
+      <c r="I65" s="20"/>
+      <c r="J65" s="20"/>
+      <c r="K65" s="20"/>
     </row>
     <row r="66" spans="1:11">
-      <c r="A66" s="6"/>
-      <c r="B66" s="6"/>
-      <c r="C66" s="6"/>
-      <c r="D66" s="6"/>
-      <c r="E66" s="6"/>
-      <c r="F66" s="6"/>
-      <c r="G66" s="6"/>
-      <c r="H66" s="6"/>
-      <c r="I66" s="6"/>
-      <c r="J66" s="6"/>
-      <c r="K66" s="6"/>
+      <c r="A66" s="20"/>
+      <c r="B66" s="20"/>
+      <c r="C66" s="20"/>
+      <c r="D66" s="20"/>
+      <c r="E66" s="20"/>
+      <c r="F66" s="20"/>
+      <c r="G66" s="20"/>
+      <c r="H66" s="20"/>
+      <c r="I66" s="20"/>
+      <c r="J66" s="20"/>
+      <c r="K66" s="20"/>
     </row>
     <row r="67" spans="1:11">
-      <c r="A67" s="6"/>
-      <c r="B67" s="6"/>
-      <c r="C67" s="6"/>
-      <c r="D67" s="6"/>
-      <c r="E67" s="6"/>
-      <c r="F67" s="6"/>
-      <c r="G67" s="6"/>
-      <c r="H67" s="6"/>
-      <c r="I67" s="6"/>
-      <c r="J67" s="6"/>
-      <c r="K67" s="6"/>
+      <c r="A67" s="20"/>
+      <c r="B67" s="20"/>
+      <c r="C67" s="20"/>
+      <c r="D67" s="20"/>
+      <c r="E67" s="20"/>
+      <c r="F67" s="20"/>
+      <c r="G67" s="20"/>
+      <c r="H67" s="20"/>
+      <c r="I67" s="20"/>
+      <c r="J67" s="20"/>
+      <c r="K67" s="20"/>
     </row>
     <row r="68" spans="1:11">
-      <c r="A68" s="6"/>
-      <c r="B68" s="6"/>
-      <c r="C68" s="6"/>
-      <c r="D68" s="6"/>
-      <c r="E68" s="6"/>
-      <c r="F68" s="6"/>
-      <c r="G68" s="6"/>
-      <c r="H68" s="6"/>
-      <c r="I68" s="6"/>
-      <c r="J68" s="6"/>
-      <c r="K68" s="6"/>
+      <c r="A68" s="20"/>
+      <c r="B68" s="20"/>
+      <c r="C68" s="20"/>
+      <c r="D68" s="20"/>
+      <c r="E68" s="20"/>
+      <c r="F68" s="20"/>
+      <c r="G68" s="20"/>
+      <c r="H68" s="20"/>
+      <c r="I68" s="20"/>
+      <c r="J68" s="20"/>
+      <c r="K68" s="20"/>
     </row>
     <row r="69" spans="1:11">
-      <c r="A69" s="6"/>
-      <c r="B69" s="6"/>
-      <c r="C69" s="6"/>
-      <c r="D69" s="6"/>
-      <c r="E69" s="6"/>
-      <c r="F69" s="6"/>
-      <c r="G69" s="6"/>
-      <c r="H69" s="6"/>
-      <c r="I69" s="6"/>
-      <c r="J69" s="6"/>
-      <c r="K69" s="6"/>
+      <c r="A69" s="20"/>
+      <c r="B69" s="20"/>
+      <c r="C69" s="20"/>
+      <c r="D69" s="20"/>
+      <c r="E69" s="20"/>
+      <c r="F69" s="20"/>
+      <c r="G69" s="20"/>
+      <c r="H69" s="20"/>
+      <c r="I69" s="20"/>
+      <c r="J69" s="20"/>
+      <c r="K69" s="20"/>
     </row>
     <row r="70" spans="1:11">
-      <c r="A70" s="6"/>
-      <c r="B70" s="6"/>
-      <c r="C70" s="6"/>
-      <c r="D70" s="6"/>
-      <c r="E70" s="6"/>
-      <c r="F70" s="6"/>
-      <c r="G70" s="6"/>
-      <c r="H70" s="6"/>
-      <c r="I70" s="6"/>
-      <c r="J70" s="6"/>
-      <c r="K70" s="6"/>
+      <c r="A70" s="20"/>
+      <c r="B70" s="20"/>
+      <c r="C70" s="20"/>
+      <c r="D70" s="20"/>
+      <c r="E70" s="20"/>
+      <c r="F70" s="20"/>
+      <c r="G70" s="20"/>
+      <c r="H70" s="20"/>
+      <c r="I70" s="20"/>
+      <c r="J70" s="20"/>
+      <c r="K70" s="20"/>
     </row>
     <row r="71" spans="1:11">
-      <c r="A71" s="6"/>
-      <c r="B71" s="6"/>
-      <c r="C71" s="6"/>
-      <c r="D71" s="6"/>
-      <c r="E71" s="6"/>
-      <c r="F71" s="6"/>
-      <c r="G71" s="6"/>
-      <c r="H71" s="6"/>
-      <c r="I71" s="6"/>
-      <c r="J71" s="6"/>
-      <c r="K71" s="6"/>
+      <c r="A71" s="20"/>
+      <c r="B71" s="20"/>
+      <c r="C71" s="20"/>
+      <c r="D71" s="20"/>
+      <c r="E71" s="20"/>
+      <c r="F71" s="20"/>
+      <c r="G71" s="20"/>
+      <c r="H71" s="20"/>
+      <c r="I71" s="20"/>
+      <c r="J71" s="20"/>
+      <c r="K71" s="20"/>
     </row>
     <row r="72" spans="1:11">
-      <c r="A72" s="6"/>
-      <c r="B72" s="6"/>
-      <c r="C72" s="6"/>
-      <c r="D72" s="6"/>
-      <c r="E72" s="6"/>
-      <c r="F72" s="6"/>
-      <c r="G72" s="6"/>
-      <c r="H72" s="6"/>
-      <c r="I72" s="6"/>
-      <c r="J72" s="6"/>
-      <c r="K72" s="6"/>
+      <c r="A72" s="20"/>
+      <c r="B72" s="20"/>
+      <c r="C72" s="20"/>
+      <c r="D72" s="20"/>
+      <c r="E72" s="20"/>
+      <c r="F72" s="20"/>
+      <c r="G72" s="20"/>
+      <c r="H72" s="20"/>
+      <c r="I72" s="20"/>
+      <c r="J72" s="20"/>
+      <c r="K72" s="20"/>
     </row>
     <row r="73" spans="1:11">
-      <c r="A73" s="6"/>
-      <c r="B73" s="6"/>
-      <c r="C73" s="6"/>
-      <c r="D73" s="6"/>
-      <c r="E73" s="6"/>
-      <c r="F73" s="6"/>
-      <c r="G73" s="6"/>
-      <c r="H73" s="6"/>
-      <c r="I73" s="6"/>
-      <c r="J73" s="6"/>
-      <c r="K73" s="6"/>
+      <c r="A73" s="20"/>
+      <c r="B73" s="20"/>
+      <c r="C73" s="20"/>
+      <c r="D73" s="20"/>
+      <c r="E73" s="20"/>
+      <c r="F73" s="20"/>
+      <c r="G73" s="20"/>
+      <c r="H73" s="20"/>
+      <c r="I73" s="20"/>
+      <c r="J73" s="20"/>
+      <c r="K73" s="20"/>
     </row>
     <row r="74" spans="1:11">
-      <c r="A74" s="6"/>
-      <c r="B74" s="6"/>
-      <c r="C74" s="6"/>
-      <c r="D74" s="6"/>
-      <c r="E74" s="6"/>
-      <c r="F74" s="6"/>
-      <c r="G74" s="6"/>
-      <c r="H74" s="6"/>
-      <c r="I74" s="6"/>
-      <c r="J74" s="6"/>
-      <c r="K74" s="6"/>
+      <c r="A74" s="20"/>
+      <c r="B74" s="20"/>
+      <c r="C74" s="20"/>
+      <c r="D74" s="20"/>
+      <c r="E74" s="20"/>
+      <c r="F74" s="20"/>
+      <c r="G74" s="20"/>
+      <c r="H74" s="20"/>
+      <c r="I74" s="20"/>
+      <c r="J74" s="20"/>
+      <c r="K74" s="20"/>
     </row>
     <row r="75" spans="1:11">
-      <c r="A75" s="6"/>
-      <c r="B75" s="6"/>
-      <c r="C75" s="6"/>
-      <c r="D75" s="6"/>
-      <c r="E75" s="6"/>
-      <c r="F75" s="6"/>
-      <c r="G75" s="6"/>
-      <c r="H75" s="6"/>
-      <c r="I75" s="6"/>
-      <c r="J75" s="6"/>
-      <c r="K75" s="6"/>
+      <c r="A75" s="20"/>
+      <c r="B75" s="20"/>
+      <c r="C75" s="20"/>
+      <c r="D75" s="20"/>
+      <c r="E75" s="20"/>
+      <c r="F75" s="20"/>
+      <c r="G75" s="20"/>
+      <c r="H75" s="20"/>
+      <c r="I75" s="20"/>
+      <c r="J75" s="20"/>
+      <c r="K75" s="20"/>
     </row>
     <row r="76" spans="1:11">
-      <c r="A76" s="6"/>
-      <c r="B76" s="6"/>
-      <c r="C76" s="6"/>
-      <c r="D76" s="6"/>
-      <c r="E76" s="6"/>
-      <c r="F76" s="6"/>
-      <c r="G76" s="6"/>
-      <c r="H76" s="6"/>
-      <c r="I76" s="6"/>
-      <c r="J76" s="6"/>
-      <c r="K76" s="6"/>
+      <c r="A76" s="20"/>
+      <c r="B76" s="20"/>
+      <c r="C76" s="20"/>
+      <c r="D76" s="20"/>
+      <c r="E76" s="20"/>
+      <c r="F76" s="20"/>
+      <c r="G76" s="20"/>
+      <c r="H76" s="20"/>
+      <c r="I76" s="20"/>
+      <c r="J76" s="20"/>
+      <c r="K76" s="20"/>
     </row>
     <row r="77" spans="1:11">
-      <c r="A77" s="6"/>
-      <c r="B77" s="6"/>
-      <c r="C77" s="6"/>
-      <c r="D77" s="6"/>
-      <c r="E77" s="6"/>
-      <c r="F77" s="6"/>
-      <c r="G77" s="6"/>
-      <c r="H77" s="6"/>
-      <c r="I77" s="6"/>
-      <c r="J77" s="6"/>
-      <c r="K77" s="6"/>
+      <c r="A77" s="20"/>
+      <c r="B77" s="20"/>
+      <c r="C77" s="20"/>
+      <c r="D77" s="20"/>
+      <c r="E77" s="20"/>
+      <c r="F77" s="20"/>
+      <c r="G77" s="20"/>
+      <c r="H77" s="20"/>
+      <c r="I77" s="20"/>
+      <c r="J77" s="20"/>
+      <c r="K77" s="20"/>
     </row>
     <row r="78" spans="1:11">
-      <c r="A78" s="6"/>
-      <c r="B78" s="6"/>
-      <c r="C78" s="6"/>
-      <c r="D78" s="6"/>
-      <c r="E78" s="6"/>
-      <c r="F78" s="6"/>
-      <c r="G78" s="6"/>
-      <c r="H78" s="6"/>
-      <c r="I78" s="6"/>
-      <c r="J78" s="6"/>
-      <c r="K78" s="6"/>
+      <c r="A78" s="20"/>
+      <c r="B78" s="20"/>
+      <c r="C78" s="20"/>
+      <c r="D78" s="20"/>
+      <c r="E78" s="20"/>
+      <c r="F78" s="20"/>
+      <c r="G78" s="20"/>
+      <c r="H78" s="20"/>
+      <c r="I78" s="20"/>
+      <c r="J78" s="20"/>
+      <c r="K78" s="20"/>
     </row>
     <row r="79" spans="1:11">
-      <c r="A79" s="6"/>
-      <c r="B79" s="6"/>
-      <c r="C79" s="6"/>
-      <c r="D79" s="6"/>
-      <c r="E79" s="6"/>
-      <c r="F79" s="6"/>
-      <c r="G79" s="6"/>
-      <c r="H79" s="6"/>
-      <c r="I79" s="6"/>
-      <c r="J79" s="6"/>
-      <c r="K79" s="6"/>
+      <c r="A79" s="20"/>
+      <c r="B79" s="20"/>
+      <c r="C79" s="20"/>
+      <c r="D79" s="20"/>
+      <c r="E79" s="20"/>
+      <c r="F79" s="20"/>
+      <c r="G79" s="20"/>
+      <c r="H79" s="20"/>
+      <c r="I79" s="20"/>
+      <c r="J79" s="20"/>
+      <c r="K79" s="20"/>
     </row>
     <row r="80" spans="1:11">
-      <c r="A80" s="6"/>
-      <c r="B80" s="6"/>
-      <c r="C80" s="6"/>
-      <c r="D80" s="6"/>
-      <c r="E80" s="6"/>
-      <c r="F80" s="6"/>
-      <c r="G80" s="6"/>
-      <c r="H80" s="6"/>
-      <c r="I80" s="6"/>
-      <c r="J80" s="6"/>
-      <c r="K80" s="6"/>
+      <c r="A80" s="20"/>
+      <c r="B80" s="20"/>
+      <c r="C80" s="20"/>
+      <c r="D80" s="20"/>
+      <c r="E80" s="20"/>
+      <c r="F80" s="20"/>
+      <c r="G80" s="20"/>
+      <c r="H80" s="20"/>
+      <c r="I80" s="20"/>
+      <c r="J80" s="20"/>
+      <c r="K80" s="20"/>
     </row>
     <row r="81" spans="1:11">
-      <c r="A81" s="6"/>
-      <c r="B81" s="6"/>
-      <c r="C81" s="6"/>
-      <c r="D81" s="6"/>
-      <c r="E81" s="6"/>
-      <c r="F81" s="6"/>
-      <c r="G81" s="6"/>
-      <c r="H81" s="6"/>
-      <c r="I81" s="6"/>
-      <c r="J81" s="6"/>
-      <c r="K81" s="6"/>
+      <c r="A81" s="20"/>
+      <c r="B81" s="20"/>
+      <c r="C81" s="20"/>
+      <c r="D81" s="20"/>
+      <c r="E81" s="20"/>
+      <c r="F81" s="20"/>
+      <c r="G81" s="20"/>
+      <c r="H81" s="20"/>
+      <c r="I81" s="20"/>
+      <c r="J81" s="20"/>
+      <c r="K81" s="20"/>
     </row>
     <row r="82" spans="1:11">
-      <c r="A82" s="6"/>
-      <c r="B82" s="6"/>
-      <c r="C82" s="6"/>
-      <c r="D82" s="6"/>
-      <c r="E82" s="6"/>
-      <c r="F82" s="6"/>
-      <c r="G82" s="6"/>
-      <c r="H82" s="6"/>
-      <c r="I82" s="6"/>
-      <c r="J82" s="6"/>
-      <c r="K82" s="6"/>
+      <c r="A82" s="20"/>
+      <c r="B82" s="20"/>
+      <c r="C82" s="20"/>
+      <c r="D82" s="20"/>
+      <c r="E82" s="20"/>
+      <c r="F82" s="20"/>
+      <c r="G82" s="20"/>
+      <c r="H82" s="20"/>
+      <c r="I82" s="20"/>
+      <c r="J82" s="20"/>
+      <c r="K82" s="20"/>
     </row>
     <row r="83" spans="1:11">
-      <c r="A83" s="6"/>
-      <c r="B83" s="6"/>
-      <c r="C83" s="6"/>
-      <c r="D83" s="6"/>
-      <c r="E83" s="6"/>
-      <c r="F83" s="6"/>
-      <c r="G83" s="6"/>
-      <c r="H83" s="6"/>
-      <c r="I83" s="6"/>
-      <c r="J83" s="6"/>
-      <c r="K83" s="6"/>
+      <c r="A83" s="20"/>
+      <c r="B83" s="20"/>
+      <c r="C83" s="20"/>
+      <c r="D83" s="20"/>
+      <c r="E83" s="20"/>
+      <c r="F83" s="20"/>
+      <c r="G83" s="20"/>
+      <c r="H83" s="20"/>
+      <c r="I83" s="20"/>
+      <c r="J83" s="20"/>
+      <c r="K83" s="20"/>
     </row>
     <row r="84" spans="1:11">
-      <c r="A84" s="6"/>
-      <c r="B84" s="6"/>
-      <c r="C84" s="6"/>
-      <c r="D84" s="6"/>
-      <c r="E84" s="6"/>
-      <c r="F84" s="6"/>
-      <c r="G84" s="6"/>
-      <c r="H84" s="6"/>
-      <c r="I84" s="6"/>
-      <c r="J84" s="6"/>
-      <c r="K84" s="6"/>
+      <c r="A84" s="20"/>
+      <c r="B84" s="20"/>
+      <c r="C84" s="20"/>
+      <c r="D84" s="20"/>
+      <c r="E84" s="20"/>
+      <c r="F84" s="20"/>
+      <c r="G84" s="20"/>
+      <c r="H84" s="20"/>
+      <c r="I84" s="20"/>
+      <c r="J84" s="20"/>
+      <c r="K84" s="20"/>
     </row>
     <row r="85" spans="1:11">
-      <c r="A85" s="6"/>
-      <c r="B85" s="6"/>
-      <c r="C85" s="6"/>
-      <c r="D85" s="6"/>
-      <c r="E85" s="6"/>
-      <c r="F85" s="6"/>
-      <c r="G85" s="6"/>
-      <c r="H85" s="6"/>
-      <c r="I85" s="6"/>
-      <c r="J85" s="6"/>
-      <c r="K85" s="6"/>
+      <c r="A85" s="20"/>
+      <c r="B85" s="20"/>
+      <c r="C85" s="20"/>
+      <c r="D85" s="20"/>
+      <c r="E85" s="20"/>
+      <c r="F85" s="20"/>
+      <c r="G85" s="20"/>
+      <c r="H85" s="20"/>
+      <c r="I85" s="20"/>
+      <c r="J85" s="20"/>
+      <c r="K85" s="20"/>
     </row>
     <row r="86" spans="1:11">
-      <c r="A86" s="6"/>
-      <c r="B86" s="6"/>
-      <c r="C86" s="6"/>
-      <c r="D86" s="6"/>
-      <c r="E86" s="6"/>
-      <c r="F86" s="6"/>
-      <c r="G86" s="6"/>
-      <c r="H86" s="6"/>
-      <c r="I86" s="6"/>
-      <c r="J86" s="6"/>
-      <c r="K86" s="6"/>
+      <c r="A86" s="20"/>
+      <c r="B86" s="20"/>
+      <c r="C86" s="20"/>
+      <c r="D86" s="20"/>
+      <c r="E86" s="20"/>
+      <c r="F86" s="20"/>
+      <c r="G86" s="20"/>
+      <c r="H86" s="20"/>
+      <c r="I86" s="20"/>
+      <c r="J86" s="20"/>
+      <c r="K86" s="20"/>
     </row>
     <row r="87" spans="1:11">
-      <c r="A87" s="6"/>
-      <c r="B87" s="6"/>
-      <c r="C87" s="6"/>
-      <c r="D87" s="6"/>
-      <c r="E87" s="6"/>
-      <c r="F87" s="6"/>
-      <c r="G87" s="6"/>
-      <c r="H87" s="6"/>
-      <c r="I87" s="6"/>
-      <c r="J87" s="6"/>
-      <c r="K87" s="6"/>
+      <c r="A87" s="20"/>
+      <c r="B87" s="20"/>
+      <c r="C87" s="20"/>
+      <c r="D87" s="20"/>
+      <c r="E87" s="20"/>
+      <c r="F87" s="20"/>
+      <c r="G87" s="20"/>
+      <c r="H87" s="20"/>
+      <c r="I87" s="20"/>
+      <c r="J87" s="20"/>
+      <c r="K87" s="20"/>
     </row>
     <row r="88" spans="1:11">
-      <c r="A88" s="6"/>
-      <c r="B88" s="6"/>
-      <c r="C88" s="6"/>
-      <c r="D88" s="6"/>
-      <c r="E88" s="6"/>
-      <c r="F88" s="6"/>
-      <c r="G88" s="6"/>
-      <c r="H88" s="6"/>
-      <c r="I88" s="6"/>
-      <c r="J88" s="6"/>
-      <c r="K88" s="6"/>
+      <c r="A88" s="20"/>
+      <c r="B88" s="20"/>
+      <c r="C88" s="20"/>
+      <c r="D88" s="20"/>
+      <c r="E88" s="20"/>
+      <c r="F88" s="20"/>
+      <c r="G88" s="20"/>
+      <c r="H88" s="20"/>
+      <c r="I88" s="20"/>
+      <c r="J88" s="20"/>
+      <c r="K88" s="20"/>
     </row>
     <row r="89" spans="1:11">
-      <c r="A89" s="6"/>
-      <c r="B89" s="6"/>
-      <c r="C89" s="6"/>
-      <c r="D89" s="6"/>
-      <c r="E89" s="6"/>
-      <c r="F89" s="6"/>
-      <c r="G89" s="6"/>
-      <c r="H89" s="6"/>
-      <c r="I89" s="6"/>
-      <c r="J89" s="6"/>
-      <c r="K89" s="6"/>
+      <c r="A89" s="20"/>
+      <c r="B89" s="20"/>
+      <c r="C89" s="20"/>
+      <c r="D89" s="20"/>
+      <c r="E89" s="20"/>
+      <c r="F89" s="20"/>
+      <c r="G89" s="20"/>
+      <c r="H89" s="20"/>
+      <c r="I89" s="20"/>
+      <c r="J89" s="20"/>
+      <c r="K89" s="20"/>
     </row>
     <row r="90" spans="1:11">
-      <c r="A90" s="6"/>
-      <c r="B90" s="6"/>
-      <c r="C90" s="6"/>
-      <c r="D90" s="6"/>
-      <c r="E90" s="6"/>
-      <c r="F90" s="6"/>
-      <c r="G90" s="6"/>
-      <c r="H90" s="6"/>
-      <c r="I90" s="6"/>
-      <c r="J90" s="6"/>
-      <c r="K90" s="6"/>
+      <c r="A90" s="20"/>
+      <c r="B90" s="20"/>
+      <c r="C90" s="20"/>
+      <c r="D90" s="20"/>
+      <c r="E90" s="20"/>
+      <c r="F90" s="20"/>
+      <c r="G90" s="20"/>
+      <c r="H90" s="20"/>
+      <c r="I90" s="20"/>
+      <c r="J90" s="20"/>
+      <c r="K90" s="20"/>
     </row>
     <row r="91" spans="1:11">
-      <c r="A91" s="6"/>
-      <c r="B91" s="6"/>
-      <c r="C91" s="6"/>
-      <c r="D91" s="6"/>
-      <c r="E91" s="6"/>
-      <c r="F91" s="6"/>
-      <c r="G91" s="6"/>
-      <c r="H91" s="6"/>
-      <c r="I91" s="6"/>
-      <c r="J91" s="6"/>
-      <c r="K91" s="6"/>
+      <c r="A91" s="20"/>
+      <c r="B91" s="20"/>
+      <c r="C91" s="20"/>
+      <c r="D91" s="20"/>
+      <c r="E91" s="20"/>
+      <c r="F91" s="20"/>
+      <c r="G91" s="20"/>
+      <c r="H91" s="20"/>
+      <c r="I91" s="20"/>
+      <c r="J91" s="20"/>
+      <c r="K91" s="20"/>
     </row>
     <row r="92" spans="1:11">
-      <c r="A92" s="6"/>
-      <c r="B92" s="6"/>
-      <c r="C92" s="6"/>
-      <c r="D92" s="6"/>
-      <c r="E92" s="6"/>
-      <c r="F92" s="6"/>
-      <c r="G92" s="6"/>
-      <c r="H92" s="6"/>
-      <c r="I92" s="6"/>
-      <c r="J92" s="6"/>
-      <c r="K92" s="6"/>
+      <c r="A92" s="20"/>
+      <c r="B92" s="20"/>
+      <c r="C92" s="20"/>
+      <c r="D92" s="20"/>
+      <c r="E92" s="20"/>
+      <c r="F92" s="20"/>
+      <c r="G92" s="20"/>
+      <c r="H92" s="20"/>
+      <c r="I92" s="20"/>
+      <c r="J92" s="20"/>
+      <c r="K92" s="20"/>
     </row>
     <row r="93" spans="1:11">
-      <c r="A93" s="6"/>
-      <c r="B93" s="6"/>
-      <c r="C93" s="6"/>
-      <c r="D93" s="6"/>
-      <c r="E93" s="6"/>
-      <c r="F93" s="6"/>
-      <c r="G93" s="6"/>
-      <c r="H93" s="6"/>
-      <c r="I93" s="6"/>
-      <c r="J93" s="6"/>
-      <c r="K93" s="6"/>
+      <c r="A93" s="20"/>
+      <c r="B93" s="20"/>
+      <c r="C93" s="20"/>
+      <c r="D93" s="20"/>
+      <c r="E93" s="20"/>
+      <c r="F93" s="20"/>
+      <c r="G93" s="20"/>
+      <c r="H93" s="20"/>
+      <c r="I93" s="20"/>
+      <c r="J93" s="20"/>
+      <c r="K93" s="20"/>
     </row>
     <row r="94" spans="1:11">
-      <c r="A94" s="6"/>
-      <c r="B94" s="6"/>
-      <c r="C94" s="6"/>
-      <c r="D94" s="6"/>
-      <c r="E94" s="6"/>
-      <c r="F94" s="6"/>
-      <c r="G94" s="6"/>
-      <c r="H94" s="6"/>
-      <c r="I94" s="6"/>
-      <c r="J94" s="6"/>
-      <c r="K94" s="6"/>
+      <c r="A94" s="20"/>
+      <c r="B94" s="20"/>
+      <c r="C94" s="20"/>
+      <c r="D94" s="20"/>
+      <c r="E94" s="20"/>
+      <c r="F94" s="20"/>
+      <c r="G94" s="20"/>
+      <c r="H94" s="20"/>
+      <c r="I94" s="20"/>
+      <c r="J94" s="20"/>
+      <c r="K94" s="20"/>
     </row>
     <row r="95" spans="1:11">
-      <c r="A95" s="6"/>
-      <c r="B95" s="6"/>
-      <c r="C95" s="6"/>
-      <c r="D95" s="6"/>
-      <c r="E95" s="6"/>
-      <c r="F95" s="6"/>
-      <c r="G95" s="6"/>
-      <c r="H95" s="6"/>
-      <c r="I95" s="6"/>
-      <c r="J95" s="6"/>
-      <c r="K95" s="6"/>
+      <c r="A95" s="20"/>
+      <c r="B95" s="20"/>
+      <c r="C95" s="20"/>
+      <c r="D95" s="20"/>
+      <c r="E95" s="20"/>
+      <c r="F95" s="20"/>
+      <c r="G95" s="20"/>
+      <c r="H95" s="20"/>
+      <c r="I95" s="20"/>
+      <c r="J95" s="20"/>
+      <c r="K95" s="20"/>
     </row>
     <row r="96" spans="1:11">
-      <c r="A96" s="6"/>
-      <c r="B96" s="6"/>
-      <c r="C96" s="6"/>
-      <c r="D96" s="6"/>
-      <c r="E96" s="6"/>
-      <c r="F96" s="6"/>
-      <c r="G96" s="6"/>
-      <c r="H96" s="6"/>
-      <c r="I96" s="6"/>
-      <c r="J96" s="6"/>
-      <c r="K96" s="6"/>
+      <c r="A96" s="20"/>
+      <c r="B96" s="20"/>
+      <c r="C96" s="20"/>
+      <c r="D96" s="20"/>
+      <c r="E96" s="20"/>
+      <c r="F96" s="20"/>
+      <c r="G96" s="20"/>
+      <c r="H96" s="20"/>
+      <c r="I96" s="20"/>
+      <c r="J96" s="20"/>
+      <c r="K96" s="20"/>
     </row>
     <row r="97" spans="1:11">
-      <c r="A97" s="6"/>
-      <c r="B97" s="6"/>
-      <c r="C97" s="6"/>
-      <c r="D97" s="6"/>
-      <c r="E97" s="6"/>
-      <c r="F97" s="6"/>
-      <c r="G97" s="6"/>
-      <c r="H97" s="6"/>
-      <c r="I97" s="6"/>
-      <c r="J97" s="6"/>
-      <c r="K97" s="6"/>
+      <c r="A97" s="20"/>
+      <c r="B97" s="20"/>
+      <c r="C97" s="20"/>
+      <c r="D97" s="20"/>
+      <c r="E97" s="20"/>
+      <c r="F97" s="20"/>
+      <c r="G97" s="20"/>
+      <c r="H97" s="20"/>
+      <c r="I97" s="20"/>
+      <c r="J97" s="20"/>
+      <c r="K97" s="20"/>
     </row>
     <row r="98" spans="1:11">
-      <c r="A98" s="6"/>
-      <c r="B98" s="6"/>
-      <c r="C98" s="6"/>
-      <c r="D98" s="6"/>
-      <c r="E98" s="6"/>
-      <c r="F98" s="6"/>
-      <c r="G98" s="6"/>
-      <c r="H98" s="6"/>
-      <c r="I98" s="6"/>
-      <c r="J98" s="6"/>
-      <c r="K98" s="6"/>
+      <c r="A98" s="20"/>
+      <c r="B98" s="20"/>
+      <c r="C98" s="20"/>
+      <c r="D98" s="20"/>
+      <c r="E98" s="20"/>
+      <c r="F98" s="20"/>
+      <c r="G98" s="20"/>
+      <c r="H98" s="20"/>
+      <c r="I98" s="20"/>
+      <c r="J98" s="20"/>
+      <c r="K98" s="20"/>
     </row>
     <row r="99" spans="1:11">
-      <c r="A99" s="6"/>
-      <c r="B99" s="6"/>
-      <c r="C99" s="6"/>
-      <c r="D99" s="6"/>
-      <c r="E99" s="6"/>
-      <c r="F99" s="6"/>
-      <c r="G99" s="6"/>
-      <c r="H99" s="6"/>
-      <c r="I99" s="6"/>
-      <c r="J99" s="6"/>
-      <c r="K99" s="6"/>
+      <c r="A99" s="20"/>
+      <c r="B99" s="20"/>
+      <c r="C99" s="20"/>
+      <c r="D99" s="20"/>
+      <c r="E99" s="20"/>
+      <c r="F99" s="20"/>
+      <c r="G99" s="20"/>
+      <c r="H99" s="20"/>
+      <c r="I99" s="20"/>
+      <c r="J99" s="20"/>
+      <c r="K99" s="20"/>
     </row>
     <row r="100" spans="1:11">
-      <c r="A100" s="6"/>
-      <c r="B100" s="6"/>
-      <c r="C100" s="6"/>
-      <c r="D100" s="6"/>
-      <c r="E100" s="6"/>
-      <c r="F100" s="6"/>
-      <c r="G100" s="6"/>
-      <c r="H100" s="6"/>
-      <c r="I100" s="6"/>
-      <c r="J100" s="6"/>
-      <c r="K100" s="6"/>
+      <c r="A100" s="20"/>
+      <c r="B100" s="20"/>
+      <c r="C100" s="20"/>
+      <c r="D100" s="20"/>
+      <c r="E100" s="20"/>
+      <c r="F100" s="20"/>
+      <c r="G100" s="20"/>
+      <c r="H100" s="20"/>
+      <c r="I100" s="20"/>
+      <c r="J100" s="20"/>
+      <c r="K100" s="20"/>
     </row>
     <row r="101" spans="1:11">
-      <c r="A101" s="6"/>
-      <c r="B101" s="6"/>
-      <c r="C101" s="6"/>
-      <c r="D101" s="6"/>
-      <c r="E101" s="6"/>
-      <c r="F101" s="6"/>
-      <c r="G101" s="6"/>
-      <c r="H101" s="6"/>
-      <c r="I101" s="6"/>
-      <c r="J101" s="6"/>
-      <c r="K101" s="6"/>
+      <c r="A101" s="20"/>
+      <c r="B101" s="20"/>
+      <c r="C101" s="20"/>
+      <c r="D101" s="20"/>
+      <c r="E101" s="20"/>
+      <c r="F101" s="20"/>
+      <c r="G101" s="20"/>
+      <c r="H101" s="20"/>
+      <c r="I101" s="20"/>
+      <c r="J101" s="20"/>
+      <c r="K101" s="20"/>
     </row>
     <row r="102" spans="1:11">
-      <c r="A102" s="6"/>
-      <c r="B102" s="6"/>
-      <c r="C102" s="6"/>
-      <c r="D102" s="6"/>
-      <c r="E102" s="6"/>
-      <c r="F102" s="6"/>
-      <c r="G102" s="6"/>
-      <c r="H102" s="6"/>
-      <c r="I102" s="6"/>
-      <c r="J102" s="6"/>
-      <c r="K102" s="6"/>
+      <c r="A102" s="20"/>
+      <c r="B102" s="20"/>
+      <c r="C102" s="20"/>
+      <c r="D102" s="20"/>
+      <c r="E102" s="20"/>
+      <c r="F102" s="20"/>
+      <c r="G102" s="20"/>
+      <c r="H102" s="20"/>
+      <c r="I102" s="20"/>
+      <c r="J102" s="20"/>
+      <c r="K102" s="20"/>
     </row>
     <row r="103" spans="1:11">
-      <c r="A103" s="6"/>
-      <c r="B103" s="6"/>
-      <c r="C103" s="6"/>
-      <c r="D103" s="6"/>
-      <c r="E103" s="6"/>
-      <c r="F103" s="6"/>
-      <c r="G103" s="6"/>
-      <c r="H103" s="6"/>
-      <c r="I103" s="6"/>
-      <c r="J103" s="6"/>
-      <c r="K103" s="6"/>
+      <c r="A103" s="20"/>
+      <c r="B103" s="20"/>
+      <c r="C103" s="20"/>
+      <c r="D103" s="20"/>
+      <c r="E103" s="20"/>
+      <c r="F103" s="20"/>
+      <c r="G103" s="20"/>
+      <c r="H103" s="20"/>
+      <c r="I103" s="20"/>
+      <c r="J103" s="20"/>
+      <c r="K103" s="20"/>
     </row>
     <row r="104" spans="1:11">
-      <c r="A104" s="6"/>
-      <c r="B104" s="6"/>
-      <c r="C104" s="6"/>
-      <c r="D104" s="6"/>
-      <c r="E104" s="6"/>
-      <c r="F104" s="6"/>
-      <c r="G104" s="6"/>
-      <c r="H104" s="6"/>
-      <c r="I104" s="6"/>
-      <c r="J104" s="6"/>
-      <c r="K104" s="6"/>
+      <c r="A104" s="20"/>
+      <c r="B104" s="20"/>
+      <c r="C104" s="20"/>
+      <c r="D104" s="20"/>
+      <c r="E104" s="20"/>
+      <c r="F104" s="20"/>
+      <c r="G104" s="20"/>
+      <c r="H104" s="20"/>
+      <c r="I104" s="20"/>
+      <c r="J104" s="20"/>
+      <c r="K104" s="20"/>
     </row>
     <row r="105" spans="1:11">
-      <c r="A105" s="6"/>
-      <c r="B105" s="6"/>
-      <c r="C105" s="6"/>
-      <c r="D105" s="6"/>
-      <c r="E105" s="6"/>
-      <c r="F105" s="6"/>
-      <c r="G105" s="6"/>
-      <c r="H105" s="6"/>
-      <c r="I105" s="6"/>
-      <c r="J105" s="6"/>
-      <c r="K105" s="6"/>
+      <c r="A105" s="20"/>
+      <c r="B105" s="20"/>
+      <c r="C105" s="20"/>
+      <c r="D105" s="20"/>
+      <c r="E105" s="20"/>
+      <c r="F105" s="20"/>
+      <c r="G105" s="20"/>
+      <c r="H105" s="20"/>
+      <c r="I105" s="20"/>
+      <c r="J105" s="20"/>
+      <c r="K105" s="20"/>
     </row>
     <row r="106" spans="1:11">
-      <c r="A106" s="6"/>
-      <c r="B106" s="6"/>
-      <c r="C106" s="6"/>
-      <c r="D106" s="6"/>
-      <c r="E106" s="6"/>
-      <c r="F106" s="6"/>
-      <c r="G106" s="6"/>
-      <c r="H106" s="6"/>
-      <c r="I106" s="6"/>
-      <c r="J106" s="6"/>
-      <c r="K106" s="6"/>
+      <c r="A106" s="20"/>
+      <c r="B106" s="20"/>
+      <c r="C106" s="20"/>
+      <c r="D106" s="20"/>
+      <c r="E106" s="20"/>
+      <c r="F106" s="20"/>
+      <c r="G106" s="20"/>
+      <c r="H106" s="20"/>
+      <c r="I106" s="20"/>
+      <c r="J106" s="20"/>
+      <c r="K106" s="20"/>
     </row>
     <row r="107" spans="1:11">
-      <c r="A107" s="6"/>
-      <c r="B107" s="6"/>
-      <c r="C107" s="6"/>
-      <c r="D107" s="6"/>
-      <c r="E107" s="6"/>
-      <c r="F107" s="6"/>
-      <c r="G107" s="6"/>
-      <c r="H107" s="6"/>
-      <c r="I107" s="6"/>
-      <c r="J107" s="6"/>
-      <c r="K107" s="6"/>
+      <c r="A107" s="20"/>
+      <c r="B107" s="20"/>
+      <c r="C107" s="20"/>
+      <c r="D107" s="20"/>
+      <c r="E107" s="20"/>
+      <c r="F107" s="20"/>
+      <c r="G107" s="20"/>
+      <c r="H107" s="20"/>
+      <c r="I107" s="20"/>
+      <c r="J107" s="20"/>
+      <c r="K107" s="20"/>
     </row>
     <row r="108" spans="1:11">
-      <c r="A108" s="6"/>
-      <c r="B108" s="6"/>
-      <c r="C108" s="6"/>
-      <c r="D108" s="6"/>
-      <c r="E108" s="6"/>
-      <c r="F108" s="6"/>
-      <c r="G108" s="6"/>
-      <c r="H108" s="6"/>
-      <c r="I108" s="6"/>
-      <c r="J108" s="6"/>
-      <c r="K108" s="6"/>
+      <c r="A108" s="20"/>
+      <c r="B108" s="20"/>
+      <c r="C108" s="20"/>
+      <c r="D108" s="20"/>
+      <c r="E108" s="20"/>
+      <c r="F108" s="20"/>
+      <c r="G108" s="20"/>
+      <c r="H108" s="20"/>
+      <c r="I108" s="20"/>
+      <c r="J108" s="20"/>
+      <c r="K108" s="20"/>
     </row>
     <row r="109" spans="1:11">
-      <c r="A109" s="6"/>
-      <c r="B109" s="6"/>
-      <c r="C109" s="6"/>
-      <c r="D109" s="6"/>
-      <c r="E109" s="6"/>
-      <c r="F109" s="6"/>
-      <c r="G109" s="6"/>
-      <c r="H109" s="6"/>
-      <c r="I109" s="6"/>
-      <c r="J109" s="6"/>
-      <c r="K109" s="6"/>
+      <c r="A109" s="20"/>
+      <c r="B109" s="20"/>
+      <c r="C109" s="20"/>
+      <c r="D109" s="20"/>
+      <c r="E109" s="20"/>
+      <c r="F109" s="20"/>
+      <c r="G109" s="20"/>
+      <c r="H109" s="20"/>
+      <c r="I109" s="20"/>
+      <c r="J109" s="20"/>
+      <c r="K109" s="20"/>
     </row>
     <row r="110" spans="1:11">
-      <c r="A110" s="6"/>
-      <c r="B110" s="6"/>
-      <c r="C110" s="6"/>
-      <c r="D110" s="6"/>
-      <c r="E110" s="6"/>
-      <c r="F110" s="6"/>
-      <c r="G110" s="6"/>
-      <c r="H110" s="6"/>
-      <c r="I110" s="6"/>
-      <c r="J110" s="6"/>
-      <c r="K110" s="6"/>
+      <c r="A110" s="20"/>
+      <c r="B110" s="20"/>
+      <c r="C110" s="20"/>
+      <c r="D110" s="20"/>
+      <c r="E110" s="20"/>
+      <c r="F110" s="20"/>
+      <c r="G110" s="20"/>
+      <c r="H110" s="20"/>
+      <c r="I110" s="20"/>
+      <c r="J110" s="20"/>
+      <c r="K110" s="20"/>
     </row>
     <row r="111" spans="1:11">
-      <c r="A111" s="6"/>
-      <c r="B111" s="6"/>
-      <c r="C111" s="6"/>
-      <c r="D111" s="6"/>
-      <c r="E111" s="6"/>
-      <c r="F111" s="6"/>
-      <c r="G111" s="6"/>
-      <c r="H111" s="6"/>
-      <c r="I111" s="6"/>
-      <c r="J111" s="6"/>
-      <c r="K111" s="6"/>
+      <c r="A111" s="20"/>
+      <c r="B111" s="20"/>
+      <c r="C111" s="20"/>
+      <c r="D111" s="20"/>
+      <c r="E111" s="20"/>
+      <c r="F111" s="20"/>
+      <c r="G111" s="20"/>
+      <c r="H111" s="20"/>
+      <c r="I111" s="20"/>
+      <c r="J111" s="20"/>
+      <c r="K111" s="20"/>
     </row>
     <row r="112" spans="1:11">
-      <c r="A112" s="6"/>
-      <c r="B112" s="6"/>
-      <c r="C112" s="6"/>
-      <c r="D112" s="6"/>
-      <c r="E112" s="6"/>
-      <c r="F112" s="6"/>
-      <c r="G112" s="6"/>
-      <c r="H112" s="6"/>
-      <c r="I112" s="6"/>
-      <c r="J112" s="6"/>
-      <c r="K112" s="6"/>
+      <c r="A112" s="20"/>
+      <c r="B112" s="20"/>
+      <c r="C112" s="20"/>
+      <c r="D112" s="20"/>
+      <c r="E112" s="20"/>
+      <c r="F112" s="20"/>
+      <c r="G112" s="20"/>
+      <c r="H112" s="20"/>
+      <c r="I112" s="20"/>
+      <c r="J112" s="20"/>
+      <c r="K112" s="20"/>
     </row>
     <row r="113" spans="1:11">
-      <c r="A113" s="6"/>
-      <c r="B113" s="6"/>
-      <c r="C113" s="6"/>
-      <c r="D113" s="6"/>
-      <c r="E113" s="6"/>
-      <c r="F113" s="6"/>
-      <c r="G113" s="6"/>
-      <c r="H113" s="6"/>
-      <c r="I113" s="6"/>
-      <c r="J113" s="6"/>
-      <c r="K113" s="6"/>
+      <c r="A113" s="20"/>
+      <c r="B113" s="20"/>
+      <c r="C113" s="20"/>
+      <c r="D113" s="20"/>
+      <c r="E113" s="20"/>
+      <c r="F113" s="20"/>
+      <c r="G113" s="20"/>
+      <c r="H113" s="20"/>
+      <c r="I113" s="20"/>
+      <c r="J113" s="20"/>
+      <c r="K113" s="20"/>
     </row>
     <row r="114" spans="1:11">
-      <c r="A114" s="6"/>
-      <c r="B114" s="6"/>
-      <c r="C114" s="6"/>
-      <c r="D114" s="6"/>
-      <c r="E114" s="6"/>
-      <c r="F114" s="6"/>
-      <c r="G114" s="6"/>
-      <c r="H114" s="6"/>
-      <c r="I114" s="6"/>
-      <c r="J114" s="6"/>
-      <c r="K114" s="6"/>
+      <c r="A114" s="20"/>
+      <c r="B114" s="20"/>
+      <c r="C114" s="20"/>
+      <c r="D114" s="20"/>
+      <c r="E114" s="20"/>
+      <c r="F114" s="20"/>
+      <c r="G114" s="20"/>
+      <c r="H114" s="20"/>
+      <c r="I114" s="20"/>
+      <c r="J114" s="20"/>
+      <c r="K114" s="20"/>
     </row>
     <row r="115" spans="1:11">
-      <c r="A115" s="6"/>
-      <c r="B115" s="6"/>
-      <c r="C115" s="6"/>
-      <c r="D115" s="6"/>
-      <c r="E115" s="6"/>
-      <c r="F115" s="6"/>
-      <c r="G115" s="6"/>
-      <c r="H115" s="6"/>
-      <c r="I115" s="6"/>
-      <c r="J115" s="6"/>
-      <c r="K115" s="6"/>
+      <c r="A115" s="20"/>
+      <c r="B115" s="20"/>
+      <c r="C115" s="20"/>
+      <c r="D115" s="20"/>
+      <c r="E115" s="20"/>
+      <c r="F115" s="20"/>
+      <c r="G115" s="20"/>
+      <c r="H115" s="20"/>
+      <c r="I115" s="20"/>
+      <c r="J115" s="20"/>
+      <c r="K115" s="20"/>
     </row>
     <row r="116" spans="1:11">
-      <c r="A116" s="6"/>
-      <c r="B116" s="6"/>
-      <c r="C116" s="6"/>
-      <c r="D116" s="6"/>
-      <c r="E116" s="6"/>
-      <c r="F116" s="6"/>
-      <c r="G116" s="6"/>
-      <c r="H116" s="6"/>
-      <c r="I116" s="6"/>
-      <c r="J116" s="6"/>
-      <c r="K116" s="6"/>
+      <c r="A116" s="20"/>
+      <c r="B116" s="20"/>
+      <c r="C116" s="20"/>
+      <c r="D116" s="20"/>
+      <c r="E116" s="20"/>
+      <c r="F116" s="20"/>
+      <c r="G116" s="20"/>
+      <c r="H116" s="20"/>
+      <c r="I116" s="20"/>
+      <c r="J116" s="20"/>
+      <c r="K116" s="20"/>
     </row>
     <row r="117" spans="1:11">
-      <c r="A117" s="6"/>
-      <c r="B117" s="6"/>
-      <c r="C117" s="6"/>
-      <c r="D117" s="6"/>
-      <c r="E117" s="6"/>
-      <c r="F117" s="6"/>
-      <c r="G117" s="6"/>
-      <c r="H117" s="6"/>
-      <c r="I117" s="6"/>
-      <c r="J117" s="6"/>
-      <c r="K117" s="6"/>
+      <c r="A117" s="20"/>
+      <c r="B117" s="20"/>
+      <c r="C117" s="20"/>
+      <c r="D117" s="20"/>
+      <c r="E117" s="20"/>
+      <c r="F117" s="20"/>
+      <c r="G117" s="20"/>
+      <c r="H117" s="20"/>
+      <c r="I117" s="20"/>
+      <c r="J117" s="20"/>
+      <c r="K117" s="20"/>
     </row>
     <row r="118" spans="1:11">
-      <c r="A118" s="6"/>
-      <c r="B118" s="6"/>
-      <c r="C118" s="6"/>
-      <c r="D118" s="6"/>
-      <c r="E118" s="6"/>
-      <c r="F118" s="6"/>
-      <c r="G118" s="6"/>
-      <c r="H118" s="6"/>
-      <c r="I118" s="6"/>
-      <c r="J118" s="6"/>
-      <c r="K118" s="6"/>
+      <c r="A118" s="20"/>
+      <c r="B118" s="20"/>
+      <c r="C118" s="20"/>
+      <c r="D118" s="20"/>
+      <c r="E118" s="20"/>
+      <c r="F118" s="20"/>
+      <c r="G118" s="20"/>
+      <c r="H118" s="20"/>
+      <c r="I118" s="20"/>
+      <c r="J118" s="20"/>
+      <c r="K118" s="20"/>
     </row>
     <row r="119" spans="1:11">
-      <c r="A119" s="6"/>
-      <c r="B119" s="6"/>
-      <c r="C119" s="6"/>
-      <c r="D119" s="6"/>
-      <c r="E119" s="6"/>
-      <c r="F119" s="6"/>
-      <c r="G119" s="6"/>
-      <c r="H119" s="6"/>
-      <c r="I119" s="6"/>
-      <c r="J119" s="6"/>
-      <c r="K119" s="6"/>
+      <c r="A119" s="20"/>
+      <c r="B119" s="20"/>
+      <c r="C119" s="20"/>
+      <c r="D119" s="20"/>
+      <c r="E119" s="20"/>
+      <c r="F119" s="20"/>
+      <c r="G119" s="20"/>
+      <c r="H119" s="20"/>
+      <c r="I119" s="20"/>
+      <c r="J119" s="20"/>
+      <c r="K119" s="20"/>
     </row>
     <row r="120" spans="1:11">
-      <c r="A120" s="6"/>
-      <c r="B120" s="6"/>
-      <c r="C120" s="6"/>
-      <c r="D120" s="6"/>
-      <c r="E120" s="6"/>
-      <c r="F120" s="6"/>
-      <c r="G120" s="6"/>
-      <c r="H120" s="6"/>
-      <c r="I120" s="6"/>
-      <c r="J120" s="6"/>
-      <c r="K120" s="6"/>
+      <c r="A120" s="20"/>
+      <c r="B120" s="20"/>
+      <c r="C120" s="20"/>
+      <c r="D120" s="20"/>
+      <c r="E120" s="20"/>
+      <c r="F120" s="20"/>
+      <c r="G120" s="20"/>
+      <c r="H120" s="20"/>
+      <c r="I120" s="20"/>
+      <c r="J120" s="20"/>
+      <c r="K120" s="20"/>
     </row>
     <row r="121" spans="1:11">
-      <c r="A121" s="6"/>
-      <c r="B121" s="6"/>
-      <c r="C121" s="6"/>
-      <c r="D121" s="6"/>
-      <c r="E121" s="6"/>
-      <c r="F121" s="6"/>
-      <c r="G121" s="6"/>
-      <c r="H121" s="6"/>
-      <c r="I121" s="6"/>
-      <c r="J121" s="6"/>
-      <c r="K121" s="6"/>
+      <c r="A121" s="20"/>
+      <c r="B121" s="20"/>
+      <c r="C121" s="20"/>
+      <c r="D121" s="20"/>
+      <c r="E121" s="20"/>
+      <c r="F121" s="20"/>
+      <c r="G121" s="20"/>
+      <c r="H121" s="20"/>
+      <c r="I121" s="20"/>
+      <c r="J121" s="20"/>
+      <c r="K121" s="20"/>
     </row>
     <row r="122" spans="1:11">
-      <c r="A122" s="6"/>
-      <c r="B122" s="6"/>
-      <c r="C122" s="6"/>
-      <c r="D122" s="6"/>
-      <c r="E122" s="6"/>
-      <c r="F122" s="6"/>
-      <c r="G122" s="6"/>
-      <c r="H122" s="6"/>
-      <c r="I122" s="6"/>
-      <c r="J122" s="6"/>
-      <c r="K122" s="6"/>
+      <c r="A122" s="20"/>
+      <c r="B122" s="20"/>
+      <c r="C122" s="20"/>
+      <c r="D122" s="20"/>
+      <c r="E122" s="20"/>
+      <c r="F122" s="20"/>
+      <c r="G122" s="20"/>
+      <c r="H122" s="20"/>
+      <c r="I122" s="20"/>
+      <c r="J122" s="20"/>
+      <c r="K122" s="20"/>
     </row>
     <row r="123" spans="1:11">
-      <c r="A123" s="6"/>
-      <c r="B123" s="6"/>
-      <c r="C123" s="6"/>
-      <c r="D123" s="6"/>
-      <c r="E123" s="6"/>
-      <c r="F123" s="6"/>
-      <c r="G123" s="6"/>
-      <c r="H123" s="6"/>
-      <c r="I123" s="6"/>
-      <c r="J123" s="6"/>
-      <c r="K123" s="6"/>
+      <c r="A123" s="20"/>
+      <c r="B123" s="20"/>
+      <c r="C123" s="20"/>
+      <c r="D123" s="20"/>
+      <c r="E123" s="20"/>
+      <c r="F123" s="20"/>
+      <c r="G123" s="20"/>
+      <c r="H123" s="20"/>
+      <c r="I123" s="20"/>
+      <c r="J123" s="20"/>
+      <c r="K123" s="20"/>
     </row>
     <row r="124" spans="1:11">
-      <c r="A124" s="6"/>
-      <c r="B124" s="6"/>
-      <c r="C124" s="6"/>
-      <c r="D124" s="6"/>
-      <c r="E124" s="6"/>
-      <c r="F124" s="6"/>
-      <c r="G124" s="6"/>
-      <c r="H124" s="6"/>
-      <c r="I124" s="6"/>
-      <c r="J124" s="6"/>
-      <c r="K124" s="6"/>
+      <c r="A124" s="20"/>
+      <c r="B124" s="20"/>
+      <c r="C124" s="20"/>
+      <c r="D124" s="20"/>
+      <c r="E124" s="20"/>
+      <c r="F124" s="20"/>
+      <c r="G124" s="20"/>
+      <c r="H124" s="20"/>
+      <c r="I124" s="20"/>
+      <c r="J124" s="20"/>
+      <c r="K124" s="20"/>
     </row>
     <row r="125" spans="1:11">
-      <c r="A125" s="6"/>
-      <c r="B125" s="6"/>
-      <c r="C125" s="6"/>
-      <c r="D125" s="6"/>
-      <c r="E125" s="6"/>
-      <c r="F125" s="6"/>
-      <c r="G125" s="6"/>
-      <c r="H125" s="6"/>
-      <c r="I125" s="6"/>
-      <c r="J125" s="6"/>
-      <c r="K125" s="6"/>
+      <c r="A125" s="20"/>
+      <c r="B125" s="20"/>
+      <c r="C125" s="20"/>
+      <c r="D125" s="20"/>
+      <c r="E125" s="20"/>
+      <c r="F125" s="20"/>
+      <c r="G125" s="20"/>
+      <c r="H125" s="20"/>
+      <c r="I125" s="20"/>
+      <c r="J125" s="20"/>
+      <c r="K125" s="20"/>
     </row>
     <row r="126" spans="1:11">
-      <c r="A126" s="6"/>
-      <c r="B126" s="6"/>
-      <c r="C126" s="6"/>
-      <c r="D126" s="6"/>
-      <c r="E126" s="6"/>
-      <c r="F126" s="6"/>
-      <c r="G126" s="6"/>
-      <c r="H126" s="6"/>
-      <c r="I126" s="6"/>
-      <c r="J126" s="6"/>
-      <c r="K126" s="6"/>
+      <c r="A126" s="20"/>
+      <c r="B126" s="20"/>
+      <c r="C126" s="20"/>
+      <c r="D126" s="20"/>
+      <c r="E126" s="20"/>
+      <c r="F126" s="20"/>
+      <c r="G126" s="20"/>
+      <c r="H126" s="20"/>
+      <c r="I126" s="20"/>
+      <c r="J126" s="20"/>
+      <c r="K126" s="20"/>
     </row>
     <row r="127" spans="1:11">
-      <c r="A127" s="6"/>
-      <c r="B127" s="6"/>
-      <c r="C127" s="6"/>
-      <c r="D127" s="6"/>
-      <c r="E127" s="6"/>
-      <c r="F127" s="6"/>
-      <c r="G127" s="6"/>
-      <c r="H127" s="6"/>
-      <c r="I127" s="6"/>
-      <c r="J127" s="6"/>
-      <c r="K127" s="6"/>
+      <c r="A127" s="20"/>
+      <c r="B127" s="20"/>
+      <c r="C127" s="20"/>
+      <c r="D127" s="20"/>
+      <c r="E127" s="20"/>
+      <c r="F127" s="20"/>
+      <c r="G127" s="20"/>
+      <c r="H127" s="20"/>
+      <c r="I127" s="20"/>
+      <c r="J127" s="20"/>
+      <c r="K127" s="20"/>
     </row>
     <row r="128" spans="1:11">
-      <c r="A128" s="6"/>
-      <c r="B128" s="6"/>
-      <c r="C128" s="6"/>
-      <c r="D128" s="6"/>
-      <c r="E128" s="6"/>
-      <c r="F128" s="6"/>
-      <c r="G128" s="6"/>
-      <c r="H128" s="6"/>
-      <c r="I128" s="6"/>
-      <c r="J128" s="6"/>
-      <c r="K128" s="6"/>
+      <c r="A128" s="20"/>
+      <c r="B128" s="20"/>
+      <c r="C128" s="20"/>
+      <c r="D128" s="20"/>
+      <c r="E128" s="20"/>
+      <c r="F128" s="20"/>
+      <c r="G128" s="20"/>
+      <c r="H128" s="20"/>
+      <c r="I128" s="20"/>
+      <c r="J128" s="20"/>
+      <c r="K128" s="20"/>
     </row>
     <row r="129" spans="1:11">
-      <c r="A129" s="6"/>
-      <c r="B129" s="6"/>
-      <c r="C129" s="6"/>
-      <c r="D129" s="6"/>
-      <c r="E129" s="6"/>
-      <c r="F129" s="6"/>
-      <c r="G129" s="6"/>
-      <c r="H129" s="6"/>
-      <c r="I129" s="6"/>
-      <c r="J129" s="6"/>
-      <c r="K129" s="6"/>
+      <c r="A129" s="20"/>
+      <c r="B129" s="20"/>
+      <c r="C129" s="20"/>
+      <c r="D129" s="20"/>
+      <c r="E129" s="20"/>
+      <c r="F129" s="20"/>
+      <c r="G129" s="20"/>
+      <c r="H129" s="20"/>
+      <c r="I129" s="20"/>
+      <c r="J129" s="20"/>
+      <c r="K129" s="20"/>
     </row>
     <row r="130" spans="1:11">
-      <c r="A130" s="6"/>
-      <c r="B130" s="6"/>
-      <c r="C130" s="6"/>
-      <c r="D130" s="6"/>
-      <c r="E130" s="6"/>
-      <c r="F130" s="6"/>
-      <c r="G130" s="6"/>
-      <c r="H130" s="6"/>
-      <c r="I130" s="6"/>
-      <c r="J130" s="6"/>
-      <c r="K130" s="6"/>
+      <c r="A130" s="20"/>
+      <c r="B130" s="20"/>
+      <c r="C130" s="20"/>
+      <c r="D130" s="20"/>
+      <c r="E130" s="20"/>
+      <c r="F130" s="20"/>
+      <c r="G130" s="20"/>
+      <c r="H130" s="20"/>
+      <c r="I130" s="20"/>
+      <c r="J130" s="20"/>
+      <c r="K130" s="20"/>
     </row>
     <row r="131" spans="1:11">
-      <c r="A131" s="6"/>
-      <c r="B131" s="6"/>
-      <c r="C131" s="6"/>
-      <c r="D131" s="6"/>
-      <c r="E131" s="6"/>
-      <c r="F131" s="6"/>
-      <c r="G131" s="6"/>
-      <c r="H131" s="6"/>
-      <c r="I131" s="6"/>
-      <c r="J131" s="6"/>
-      <c r="K131" s="6"/>
+      <c r="A131" s="20"/>
+      <c r="B131" s="20"/>
+      <c r="C131" s="20"/>
+      <c r="D131" s="20"/>
+      <c r="E131" s="20"/>
+      <c r="F131" s="20"/>
+      <c r="G131" s="20"/>
+      <c r="H131" s="20"/>
+      <c r="I131" s="20"/>
+      <c r="J131" s="20"/>
+      <c r="K131" s="20"/>
     </row>
     <row r="132" spans="1:11">
-      <c r="A132" s="6"/>
-      <c r="B132" s="6"/>
-      <c r="C132" s="6"/>
-      <c r="D132" s="6"/>
-      <c r="E132" s="6"/>
-      <c r="F132" s="6"/>
-      <c r="G132" s="6"/>
-      <c r="H132" s="6"/>
-      <c r="I132" s="6"/>
-      <c r="J132" s="6"/>
-      <c r="K132" s="6"/>
+      <c r="A132" s="20"/>
+      <c r="B132" s="20"/>
+      <c r="C132" s="20"/>
+      <c r="D132" s="20"/>
+      <c r="E132" s="20"/>
+      <c r="F132" s="20"/>
+      <c r="G132" s="20"/>
+      <c r="H132" s="20"/>
+      <c r="I132" s="20"/>
+      <c r="J132" s="20"/>
+      <c r="K132" s="20"/>
     </row>
     <row r="133" spans="1:11">
-      <c r="A133" s="6"/>
-      <c r="B133" s="6"/>
-      <c r="C133" s="6"/>
-      <c r="D133" s="6"/>
-      <c r="E133" s="6"/>
-      <c r="F133" s="6"/>
-      <c r="G133" s="6"/>
-      <c r="H133" s="6"/>
-      <c r="I133" s="6"/>
-      <c r="J133" s="6"/>
-      <c r="K133" s="6"/>
+      <c r="A133" s="20"/>
+      <c r="B133" s="20"/>
+      <c r="C133" s="20"/>
+      <c r="D133" s="20"/>
+      <c r="E133" s="20"/>
+      <c r="F133" s="20"/>
+      <c r="G133" s="20"/>
+      <c r="H133" s="20"/>
+      <c r="I133" s="20"/>
+      <c r="J133" s="20"/>
+      <c r="K133" s="20"/>
     </row>
     <row r="134" spans="1:11">
-      <c r="A134" s="6"/>
-      <c r="B134" s="6"/>
-      <c r="C134" s="6"/>
-      <c r="D134" s="6"/>
-      <c r="E134" s="6"/>
-      <c r="F134" s="6"/>
-      <c r="G134" s="6"/>
-      <c r="H134" s="6"/>
-      <c r="I134" s="6"/>
-      <c r="J134" s="6"/>
-      <c r="K134" s="6"/>
+      <c r="A134" s="20"/>
+      <c r="B134" s="20"/>
+      <c r="C134" s="20"/>
+      <c r="D134" s="20"/>
+      <c r="E134" s="20"/>
+      <c r="F134" s="20"/>
+      <c r="G134" s="20"/>
+      <c r="H134" s="20"/>
+      <c r="I134" s="20"/>
+      <c r="J134" s="20"/>
+      <c r="K134" s="20"/>
     </row>
     <row r="135" spans="1:11">
-      <c r="A135" s="6"/>
-      <c r="B135" s="6"/>
-      <c r="C135" s="6"/>
-      <c r="D135" s="6"/>
-      <c r="E135" s="6"/>
-      <c r="F135" s="6"/>
-      <c r="G135" s="6"/>
-      <c r="H135" s="6"/>
-      <c r="I135" s="6"/>
-      <c r="J135" s="6"/>
-      <c r="K135" s="6"/>
+      <c r="A135" s="20"/>
+      <c r="B135" s="20"/>
+      <c r="C135" s="20"/>
+      <c r="D135" s="20"/>
+      <c r="E135" s="20"/>
+      <c r="F135" s="20"/>
+      <c r="G135" s="20"/>
+      <c r="H135" s="20"/>
+      <c r="I135" s="20"/>
+      <c r="J135" s="20"/>
+      <c r="K135" s="20"/>
     </row>
     <row r="136" spans="1:11">
-      <c r="A136" s="6"/>
-      <c r="B136" s="6"/>
-      <c r="C136" s="6"/>
-      <c r="D136" s="6"/>
-      <c r="E136" s="6"/>
-      <c r="F136" s="6"/>
-      <c r="G136" s="6"/>
-      <c r="H136" s="6"/>
-      <c r="I136" s="6"/>
-      <c r="J136" s="6"/>
-      <c r="K136" s="6"/>
+      <c r="A136" s="20"/>
+      <c r="B136" s="20"/>
+      <c r="C136" s="20"/>
+      <c r="D136" s="20"/>
+      <c r="E136" s="20"/>
+      <c r="F136" s="20"/>
+      <c r="G136" s="20"/>
+      <c r="H136" s="20"/>
+      <c r="I136" s="20"/>
+      <c r="J136" s="20"/>
+      <c r="K136" s="20"/>
     </row>
     <row r="137" spans="1:11">
-      <c r="A137" s="6"/>
-      <c r="B137" s="6"/>
-      <c r="C137" s="6"/>
-      <c r="D137" s="6"/>
-      <c r="E137" s="6"/>
-      <c r="F137" s="6"/>
-      <c r="G137" s="6"/>
-      <c r="H137" s="6"/>
-      <c r="I137" s="6"/>
-      <c r="J137" s="6"/>
-      <c r="K137" s="6"/>
+      <c r="A137" s="20"/>
+      <c r="B137" s="20"/>
+      <c r="C137" s="20"/>
+      <c r="D137" s="20"/>
+      <c r="E137" s="20"/>
+      <c r="F137" s="20"/>
+      <c r="G137" s="20"/>
+      <c r="H137" s="20"/>
+      <c r="I137" s="20"/>
+      <c r="J137" s="20"/>
+      <c r="K137" s="20"/>
     </row>
     <row r="138" spans="1:11">
-      <c r="A138" s="6"/>
-      <c r="B138" s="6"/>
-      <c r="C138" s="6"/>
-      <c r="D138" s="6"/>
-      <c r="E138" s="6"/>
-      <c r="F138" s="6"/>
-      <c r="G138" s="6"/>
-      <c r="H138" s="6"/>
-      <c r="I138" s="6"/>
-      <c r="J138" s="6"/>
-      <c r="K138" s="6"/>
+      <c r="A138" s="20"/>
+      <c r="B138" s="20"/>
+      <c r="C138" s="20"/>
+      <c r="D138" s="20"/>
+      <c r="E138" s="20"/>
+      <c r="F138" s="20"/>
+      <c r="G138" s="20"/>
+      <c r="H138" s="20"/>
+      <c r="I138" s="20"/>
+      <c r="J138" s="20"/>
+      <c r="K138" s="20"/>
     </row>
     <row r="139" spans="1:11">
-      <c r="A139" s="6"/>
-      <c r="B139" s="6"/>
-      <c r="C139" s="6"/>
-      <c r="D139" s="6"/>
-      <c r="E139" s="6"/>
-      <c r="F139" s="6"/>
-      <c r="G139" s="6"/>
-      <c r="H139" s="6"/>
-      <c r="I139" s="6"/>
-      <c r="J139" s="6"/>
-      <c r="K139" s="6"/>
+      <c r="A139" s="20"/>
+      <c r="B139" s="20"/>
+      <c r="C139" s="20"/>
+      <c r="D139" s="20"/>
+      <c r="E139" s="20"/>
+      <c r="F139" s="20"/>
+      <c r="G139" s="20"/>
+      <c r="H139" s="20"/>
+      <c r="I139" s="20"/>
+      <c r="J139" s="20"/>
+      <c r="K139" s="20"/>
     </row>
     <row r="140" spans="1:11">
-      <c r="A140" s="6"/>
-      <c r="B140" s="6"/>
-      <c r="C140" s="6"/>
-      <c r="D140" s="6"/>
-      <c r="E140" s="6"/>
-      <c r="F140" s="6"/>
-      <c r="G140" s="6"/>
-      <c r="H140" s="6"/>
-      <c r="I140" s="6"/>
-      <c r="J140" s="6"/>
-      <c r="K140" s="6"/>
+      <c r="A140" s="20"/>
+      <c r="B140" s="20"/>
+      <c r="C140" s="20"/>
+      <c r="D140" s="20"/>
+      <c r="E140" s="20"/>
+      <c r="F140" s="20"/>
+      <c r="G140" s="20"/>
+      <c r="H140" s="20"/>
+      <c r="I140" s="20"/>
+      <c r="J140" s="20"/>
+      <c r="K140" s="20"/>
     </row>
     <row r="141" spans="1:11">
-      <c r="A141" s="6"/>
-      <c r="B141" s="6"/>
-      <c r="C141" s="6"/>
-      <c r="D141" s="6"/>
-      <c r="E141" s="6"/>
-      <c r="F141" s="6"/>
-      <c r="G141" s="6"/>
-      <c r="H141" s="6"/>
-      <c r="I141" s="6"/>
-      <c r="J141" s="6"/>
-      <c r="K141" s="6"/>
+      <c r="A141" s="20"/>
+      <c r="B141" s="20"/>
+      <c r="C141" s="20"/>
+      <c r="D141" s="20"/>
+      <c r="E141" s="20"/>
+      <c r="F141" s="20"/>
+      <c r="G141" s="20"/>
+      <c r="H141" s="20"/>
+      <c r="I141" s="20"/>
+      <c r="J141" s="20"/>
+      <c r="K141" s="20"/>
     </row>
     <row r="142" spans="1:11">
-      <c r="A142" s="6"/>
-      <c r="B142" s="6"/>
-      <c r="C142" s="6"/>
-      <c r="D142" s="6"/>
-      <c r="E142" s="6"/>
-      <c r="F142" s="6"/>
-      <c r="G142" s="6"/>
-      <c r="H142" s="6"/>
-      <c r="I142" s="6"/>
-      <c r="J142" s="6"/>
-      <c r="K142" s="6"/>
+      <c r="A142" s="20"/>
+      <c r="B142" s="20"/>
+      <c r="C142" s="20"/>
+      <c r="D142" s="20"/>
+      <c r="E142" s="20"/>
+      <c r="F142" s="20"/>
+      <c r="G142" s="20"/>
+      <c r="H142" s="20"/>
+      <c r="I142" s="20"/>
+      <c r="J142" s="20"/>
+      <c r="K142" s="20"/>
     </row>
     <row r="143" spans="1:11">
-      <c r="A143" s="6"/>
-      <c r="B143" s="6"/>
-      <c r="C143" s="6"/>
-      <c r="D143" s="6"/>
-      <c r="E143" s="6"/>
-      <c r="F143" s="6"/>
-      <c r="G143" s="6"/>
-      <c r="H143" s="6"/>
-      <c r="I143" s="6"/>
-      <c r="J143" s="6"/>
-      <c r="K143" s="6"/>
+      <c r="A143" s="20"/>
+      <c r="B143" s="20"/>
+      <c r="C143" s="20"/>
+      <c r="D143" s="20"/>
+      <c r="E143" s="20"/>
+      <c r="F143" s="20"/>
+      <c r="G143" s="20"/>
+      <c r="H143" s="20"/>
+      <c r="I143" s="20"/>
+      <c r="J143" s="20"/>
+      <c r="K143" s="20"/>
     </row>
     <row r="144" spans="1:11">
-      <c r="A144" s="6"/>
-      <c r="B144" s="6"/>
-      <c r="C144" s="6"/>
-      <c r="D144" s="6"/>
-      <c r="E144" s="6"/>
-      <c r="F144" s="6"/>
-      <c r="G144" s="6"/>
-      <c r="H144" s="6"/>
-      <c r="I144" s="6"/>
-      <c r="J144" s="6"/>
-      <c r="K144" s="6"/>
+      <c r="A144" s="20"/>
+      <c r="B144" s="20"/>
+      <c r="C144" s="20"/>
+      <c r="D144" s="20"/>
+      <c r="E144" s="20"/>
+      <c r="F144" s="20"/>
+      <c r="G144" s="20"/>
+      <c r="H144" s="20"/>
+      <c r="I144" s="20"/>
+      <c r="J144" s="20"/>
+      <c r="K144" s="20"/>
     </row>
     <row r="145" spans="1:11">
-      <c r="A145" s="6"/>
-      <c r="B145" s="6"/>
-      <c r="C145" s="6"/>
-      <c r="D145" s="6"/>
-      <c r="E145" s="6"/>
-      <c r="F145" s="6"/>
-      <c r="G145" s="6"/>
-      <c r="H145" s="6"/>
-      <c r="I145" s="6"/>
-      <c r="J145" s="6"/>
-      <c r="K145" s="6"/>
+      <c r="A145" s="20"/>
+      <c r="B145" s="20"/>
+      <c r="C145" s="20"/>
+      <c r="D145" s="20"/>
+      <c r="E145" s="20"/>
+      <c r="F145" s="20"/>
+      <c r="G145" s="20"/>
+      <c r="H145" s="20"/>
+      <c r="I145" s="20"/>
+      <c r="J145" s="20"/>
+      <c r="K145" s="20"/>
     </row>
     <row r="146" spans="1:11">
-      <c r="A146" s="6"/>
-      <c r="B146" s="6"/>
-      <c r="C146" s="6"/>
-      <c r="D146" s="6"/>
-      <c r="E146" s="6"/>
-      <c r="F146" s="6"/>
-      <c r="G146" s="6"/>
-      <c r="H146" s="6"/>
-      <c r="I146" s="6"/>
-      <c r="J146" s="6"/>
-      <c r="K146" s="6"/>
+      <c r="A146" s="20"/>
+      <c r="B146" s="20"/>
+      <c r="C146" s="20"/>
+      <c r="D146" s="20"/>
+      <c r="E146" s="20"/>
+      <c r="F146" s="20"/>
+      <c r="G146" s="20"/>
+      <c r="H146" s="20"/>
+      <c r="I146" s="20"/>
+      <c r="J146" s="20"/>
+      <c r="K146" s="20"/>
     </row>
     <row r="147" spans="1:11">
-      <c r="A147" s="6"/>
-      <c r="B147" s="6"/>
-      <c r="C147" s="6"/>
-      <c r="D147" s="6"/>
-      <c r="E147" s="6"/>
-      <c r="F147" s="6"/>
-      <c r="G147" s="6"/>
-      <c r="H147" s="6"/>
-      <c r="I147" s="6"/>
-      <c r="J147" s="6"/>
-      <c r="K147" s="6"/>
+      <c r="A147" s="20"/>
+      <c r="B147" s="20"/>
+      <c r="C147" s="20"/>
+      <c r="D147" s="20"/>
+      <c r="E147" s="20"/>
+      <c r="F147" s="20"/>
+      <c r="G147" s="20"/>
+      <c r="H147" s="20"/>
+      <c r="I147" s="20"/>
+      <c r="J147" s="20"/>
+      <c r="K147" s="20"/>
     </row>
     <row r="148" spans="1:11">
-      <c r="A148" s="6"/>
-      <c r="B148" s="6"/>
-      <c r="C148" s="6"/>
-      <c r="D148" s="6"/>
-      <c r="E148" s="6"/>
-      <c r="F148" s="6"/>
-      <c r="G148" s="6"/>
-      <c r="H148" s="6"/>
-      <c r="I148" s="6"/>
-      <c r="J148" s="6"/>
-      <c r="K148" s="6"/>
+      <c r="A148" s="20"/>
+      <c r="B148" s="20"/>
+      <c r="C148" s="20"/>
+      <c r="D148" s="20"/>
+      <c r="E148" s="20"/>
+      <c r="F148" s="20"/>
+      <c r="G148" s="20"/>
+      <c r="H148" s="20"/>
+      <c r="I148" s="20"/>
+      <c r="J148" s="20"/>
+      <c r="K148" s="20"/>
     </row>
     <row r="149" spans="1:11">
-      <c r="A149" s="6"/>
-      <c r="B149" s="6"/>
-      <c r="C149" s="6"/>
-      <c r="D149" s="6"/>
-      <c r="E149" s="6"/>
-      <c r="F149" s="6"/>
-      <c r="G149" s="6"/>
-      <c r="H149" s="6"/>
-      <c r="I149" s="6"/>
-      <c r="J149" s="6"/>
-      <c r="K149" s="6"/>
+      <c r="A149" s="20"/>
+      <c r="B149" s="20"/>
+      <c r="C149" s="20"/>
+      <c r="D149" s="20"/>
+      <c r="E149" s="20"/>
+      <c r="F149" s="20"/>
+      <c r="G149" s="20"/>
+      <c r="H149" s="20"/>
+      <c r="I149" s="20"/>
+      <c r="J149" s="20"/>
+      <c r="K149" s="20"/>
     </row>
     <row r="150" spans="1:11">
-      <c r="A150" s="6"/>
-      <c r="B150" s="6"/>
-      <c r="C150" s="6"/>
-      <c r="D150" s="6"/>
-      <c r="E150" s="6"/>
-      <c r="F150" s="6"/>
-      <c r="G150" s="6"/>
-      <c r="H150" s="6"/>
-      <c r="I150" s="6"/>
-      <c r="J150" s="6"/>
-      <c r="K150" s="6"/>
+      <c r="A150" s="20"/>
+      <c r="B150" s="20"/>
+      <c r="C150" s="20"/>
+      <c r="D150" s="20"/>
+      <c r="E150" s="20"/>
+      <c r="F150" s="20"/>
+      <c r="G150" s="20"/>
+      <c r="H150" s="20"/>
+      <c r="I150" s="20"/>
+      <c r="J150" s="20"/>
+      <c r="K150" s="20"/>
     </row>
     <row r="151" spans="1:11">
-      <c r="A151" s="6"/>
-      <c r="B151" s="6"/>
-      <c r="C151" s="6"/>
-      <c r="D151" s="6"/>
-      <c r="E151" s="6"/>
-      <c r="F151" s="6"/>
-      <c r="G151" s="6"/>
-      <c r="H151" s="6"/>
-      <c r="I151" s="6"/>
-      <c r="J151" s="6"/>
-      <c r="K151" s="6"/>
+      <c r="A151" s="20"/>
+      <c r="B151" s="20"/>
+      <c r="C151" s="20"/>
+      <c r="D151" s="20"/>
+      <c r="E151" s="20"/>
+      <c r="F151" s="20"/>
+      <c r="G151" s="20"/>
+      <c r="H151" s="20"/>
+      <c r="I151" s="20"/>
+      <c r="J151" s="20"/>
+      <c r="K151" s="20"/>
     </row>
     <row r="152" spans="1:11">
-      <c r="A152" s="6"/>
-      <c r="B152" s="6"/>
-      <c r="C152" s="6"/>
-      <c r="D152" s="6"/>
-      <c r="E152" s="6"/>
-      <c r="F152" s="6"/>
-      <c r="G152" s="6"/>
-      <c r="H152" s="6"/>
-      <c r="I152" s="6"/>
-      <c r="J152" s="6"/>
-      <c r="K152" s="6"/>
+      <c r="A152" s="20"/>
+      <c r="B152" s="20"/>
+      <c r="C152" s="20"/>
+      <c r="D152" s="20"/>
+      <c r="E152" s="20"/>
+      <c r="F152" s="20"/>
+      <c r="G152" s="20"/>
+      <c r="H152" s="20"/>
+      <c r="I152" s="20"/>
+      <c r="J152" s="20"/>
+      <c r="K152" s="20"/>
     </row>
     <row r="153" spans="1:11">
-      <c r="A153" s="6"/>
-      <c r="B153" s="6"/>
-      <c r="C153" s="6"/>
-      <c r="D153" s="6"/>
-      <c r="E153" s="6"/>
-      <c r="F153" s="6"/>
-      <c r="G153" s="6"/>
-      <c r="H153" s="6"/>
-      <c r="I153" s="6"/>
-      <c r="J153" s="6"/>
-      <c r="K153" s="6"/>
+      <c r="A153" s="20"/>
+      <c r="B153" s="20"/>
+      <c r="C153" s="20"/>
+      <c r="D153" s="20"/>
+      <c r="E153" s="20"/>
+      <c r="F153" s="20"/>
+      <c r="G153" s="20"/>
+      <c r="H153" s="20"/>
+      <c r="I153" s="20"/>
+      <c r="J153" s="20"/>
+      <c r="K153" s="20"/>
     </row>
     <row r="154" spans="1:11">
-      <c r="A154" s="6"/>
-      <c r="B154" s="6"/>
-      <c r="C154" s="6"/>
-      <c r="D154" s="6"/>
-      <c r="E154" s="6"/>
-      <c r="F154" s="6"/>
-      <c r="G154" s="6"/>
-      <c r="H154" s="6"/>
-      <c r="I154" s="6"/>
-      <c r="J154" s="6"/>
-      <c r="K154" s="6"/>
+      <c r="A154" s="20"/>
+      <c r="B154" s="20"/>
+      <c r="C154" s="20"/>
+      <c r="D154" s="20"/>
+      <c r="E154" s="20"/>
+      <c r="F154" s="20"/>
+      <c r="G154" s="20"/>
+      <c r="H154" s="20"/>
+      <c r="I154" s="20"/>
+      <c r="J154" s="20"/>
+      <c r="K154" s="20"/>
     </row>
     <row r="155" spans="1:11">
-      <c r="A155" s="6"/>
-      <c r="B155" s="6"/>
-      <c r="C155" s="6"/>
-      <c r="D155" s="6"/>
-      <c r="E155" s="6"/>
-      <c r="F155" s="6"/>
-      <c r="G155" s="6"/>
-      <c r="H155" s="6"/>
-      <c r="I155" s="6"/>
-      <c r="J155" s="6"/>
-      <c r="K155" s="6"/>
+      <c r="A155" s="20"/>
+      <c r="B155" s="20"/>
+      <c r="C155" s="20"/>
+      <c r="D155" s="20"/>
+      <c r="E155" s="20"/>
+      <c r="F155" s="20"/>
+      <c r="G155" s="20"/>
+      <c r="H155" s="20"/>
+      <c r="I155" s="20"/>
+      <c r="J155" s="20"/>
+      <c r="K155" s="20"/>
     </row>
     <row r="156" spans="1:11">
-      <c r="A156" s="6"/>
-      <c r="B156" s="6"/>
-      <c r="C156" s="6"/>
-      <c r="D156" s="6"/>
-      <c r="E156" s="6"/>
-      <c r="F156" s="6"/>
-      <c r="G156" s="6"/>
-      <c r="H156" s="6"/>
-      <c r="I156" s="6"/>
-      <c r="J156" s="6"/>
-      <c r="K156" s="6"/>
+      <c r="A156" s="20"/>
+      <c r="B156" s="20"/>
+      <c r="C156" s="20"/>
+      <c r="D156" s="20"/>
+      <c r="E156" s="20"/>
+      <c r="F156" s="20"/>
+      <c r="G156" s="20"/>
+      <c r="H156" s="20"/>
+      <c r="I156" s="20"/>
+      <c r="J156" s="20"/>
+      <c r="K156" s="20"/>
     </row>
     <row r="157" spans="1:11">
-      <c r="A157" s="6"/>
-      <c r="B157" s="6"/>
-      <c r="C157" s="6"/>
-      <c r="D157" s="6"/>
-      <c r="E157" s="6"/>
-      <c r="F157" s="6"/>
-      <c r="G157" s="6"/>
-      <c r="H157" s="6"/>
-      <c r="I157" s="6"/>
-      <c r="J157" s="6"/>
-      <c r="K157" s="6"/>
+      <c r="A157" s="20"/>
+      <c r="B157" s="20"/>
+      <c r="C157" s="20"/>
+      <c r="D157" s="20"/>
+      <c r="E157" s="20"/>
+      <c r="F157" s="20"/>
+      <c r="G157" s="20"/>
+      <c r="H157" s="20"/>
+      <c r="I157" s="20"/>
+      <c r="J157" s="20"/>
+      <c r="K157" s="20"/>
     </row>
     <row r="158" spans="1:11">
-      <c r="A158" s="6"/>
-      <c r="B158" s="6"/>
-      <c r="C158" s="6"/>
-      <c r="D158" s="6"/>
-      <c r="E158" s="6"/>
-      <c r="F158" s="6"/>
-      <c r="G158" s="6"/>
-      <c r="H158" s="6"/>
-      <c r="I158" s="6"/>
-      <c r="J158" s="6"/>
-      <c r="K158" s="6"/>
+      <c r="A158" s="20"/>
+      <c r="B158" s="20"/>
+      <c r="C158" s="20"/>
+      <c r="D158" s="20"/>
+      <c r="E158" s="20"/>
+      <c r="F158" s="20"/>
+      <c r="G158" s="20"/>
+      <c r="H158" s="20"/>
+      <c r="I158" s="20"/>
+      <c r="J158" s="20"/>
+      <c r="K158" s="20"/>
     </row>
     <row r="159" spans="1:11">
-      <c r="A159" s="6"/>
-      <c r="B159" s="6"/>
-      <c r="C159" s="6"/>
-      <c r="D159" s="6"/>
-      <c r="E159" s="6"/>
-      <c r="F159" s="6"/>
-      <c r="G159" s="6"/>
-      <c r="H159" s="6"/>
-      <c r="I159" s="6"/>
-      <c r="J159" s="6"/>
-      <c r="K159" s="6"/>
+      <c r="A159" s="20"/>
+      <c r="B159" s="20"/>
+      <c r="C159" s="20"/>
+      <c r="D159" s="20"/>
+      <c r="E159" s="20"/>
+      <c r="F159" s="20"/>
+      <c r="G159" s="20"/>
+      <c r="H159" s="20"/>
+      <c r="I159" s="20"/>
+      <c r="J159" s="20"/>
+      <c r="K159" s="20"/>
     </row>
     <row r="160" spans="1:11">
-      <c r="A160" s="6"/>
-      <c r="B160" s="6"/>
-      <c r="C160" s="6"/>
-      <c r="D160" s="6"/>
-      <c r="E160" s="6"/>
-      <c r="F160" s="6"/>
-      <c r="G160" s="6"/>
-      <c r="H160" s="6"/>
-      <c r="I160" s="6"/>
-      <c r="J160" s="6"/>
-      <c r="K160" s="6"/>
+      <c r="A160" s="20"/>
+      <c r="B160" s="20"/>
+      <c r="C160" s="20"/>
+      <c r="D160" s="20"/>
+      <c r="E160" s="20"/>
+      <c r="F160" s="20"/>
+      <c r="G160" s="20"/>
+      <c r="H160" s="20"/>
+      <c r="I160" s="20"/>
+      <c r="J160" s="20"/>
+      <c r="K160" s="20"/>
     </row>
     <row r="161" spans="1:11">
-      <c r="A161" s="6"/>
-      <c r="B161" s="6"/>
-      <c r="C161" s="6"/>
-      <c r="D161" s="6"/>
-      <c r="E161" s="6"/>
-      <c r="F161" s="6"/>
-      <c r="G161" s="6"/>
-      <c r="H161" s="6"/>
-      <c r="I161" s="6"/>
-      <c r="J161" s="6"/>
-      <c r="K161" s="6"/>
+      <c r="A161" s="20"/>
+      <c r="B161" s="20"/>
+      <c r="C161" s="20"/>
+      <c r="D161" s="20"/>
+      <c r="E161" s="20"/>
+      <c r="F161" s="20"/>
+      <c r="G161" s="20"/>
+      <c r="H161" s="20"/>
+      <c r="I161" s="20"/>
+      <c r="J161" s="20"/>
+      <c r="K161" s="20"/>
     </row>
     <row r="162" spans="1:11">
-      <c r="A162" s="6"/>
-      <c r="B162" s="6"/>
-      <c r="C162" s="6"/>
-      <c r="D162" s="6"/>
-      <c r="E162" s="6"/>
-      <c r="F162" s="6"/>
-      <c r="G162" s="6"/>
-      <c r="H162" s="6"/>
-      <c r="I162" s="6"/>
-      <c r="J162" s="6"/>
-      <c r="K162" s="6"/>
+      <c r="A162" s="20"/>
+      <c r="B162" s="20"/>
+      <c r="C162" s="20"/>
+      <c r="D162" s="20"/>
+      <c r="E162" s="20"/>
+      <c r="F162" s="20"/>
+      <c r="G162" s="20"/>
+      <c r="H162" s="20"/>
+      <c r="I162" s="20"/>
+      <c r="J162" s="20"/>
+      <c r="K162" s="20"/>
     </row>
     <row r="163" spans="1:11">
-      <c r="A163" s="6"/>
-      <c r="B163" s="6"/>
-      <c r="C163" s="6"/>
-      <c r="D163" s="6"/>
-      <c r="E163" s="6"/>
-      <c r="F163" s="6"/>
-      <c r="G163" s="6"/>
-      <c r="H163" s="6"/>
-      <c r="I163" s="6"/>
-      <c r="J163" s="6"/>
-      <c r="K163" s="6"/>
+      <c r="A163" s="20"/>
+      <c r="B163" s="20"/>
+      <c r="C163" s="20"/>
+      <c r="D163" s="20"/>
+      <c r="E163" s="20"/>
+      <c r="F163" s="20"/>
+      <c r="G163" s="20"/>
+      <c r="H163" s="20"/>
+      <c r="I163" s="20"/>
+      <c r="J163" s="20"/>
+      <c r="K163" s="20"/>
     </row>
     <row r="164" spans="1:11">
-      <c r="A164" s="6"/>
-      <c r="B164" s="6"/>
-      <c r="C164" s="6"/>
-      <c r="D164" s="6"/>
-      <c r="E164" s="6"/>
-      <c r="F164" s="6"/>
-      <c r="G164" s="6"/>
-      <c r="H164" s="6"/>
-      <c r="I164" s="6"/>
-      <c r="J164" s="6"/>
-      <c r="K164" s="6"/>
+      <c r="A164" s="20"/>
+      <c r="B164" s="20"/>
+      <c r="C164" s="20"/>
+      <c r="D164" s="20"/>
+      <c r="E164" s="20"/>
+      <c r="F164" s="20"/>
+      <c r="G164" s="20"/>
+      <c r="H164" s="20"/>
+      <c r="I164" s="20"/>
+      <c r="J164" s="20"/>
+      <c r="K164" s="20"/>
     </row>
     <row r="165" spans="1:11">
-      <c r="A165" s="6"/>
-      <c r="B165" s="6"/>
-      <c r="C165" s="6"/>
-      <c r="D165" s="6"/>
-      <c r="E165" s="6"/>
-      <c r="F165" s="6"/>
-      <c r="G165" s="6"/>
-      <c r="H165" s="6"/>
-      <c r="I165" s="6"/>
-      <c r="J165" s="6"/>
-      <c r="K165" s="6"/>
+      <c r="A165" s="20"/>
+      <c r="B165" s="20"/>
+      <c r="C165" s="20"/>
+      <c r="D165" s="20"/>
+      <c r="E165" s="20"/>
+      <c r="F165" s="20"/>
+      <c r="G165" s="20"/>
+      <c r="H165" s="20"/>
+      <c r="I165" s="20"/>
+      <c r="J165" s="20"/>
+      <c r="K165" s="20"/>
     </row>
     <row r="166" spans="1:11">
-      <c r="A166" s="6"/>
-      <c r="B166" s="6"/>
-      <c r="C166" s="6"/>
-      <c r="D166" s="6"/>
-      <c r="E166" s="6"/>
-      <c r="F166" s="6"/>
-      <c r="G166" s="6"/>
-      <c r="H166" s="6"/>
-      <c r="I166" s="6"/>
-      <c r="J166" s="6"/>
-      <c r="K166" s="6"/>
+      <c r="A166" s="20"/>
+      <c r="B166" s="20"/>
+      <c r="C166" s="20"/>
+      <c r="D166" s="20"/>
+      <c r="E166" s="20"/>
+      <c r="F166" s="20"/>
+      <c r="G166" s="20"/>
+      <c r="H166" s="20"/>
+      <c r="I166" s="20"/>
+      <c r="J166" s="20"/>
+      <c r="K166" s="20"/>
     </row>
     <row r="167" spans="1:11">
-      <c r="A167" s="6"/>
-      <c r="B167" s="6"/>
-      <c r="C167" s="6"/>
-      <c r="D167" s="6"/>
-      <c r="E167" s="6"/>
-      <c r="F167" s="6"/>
-      <c r="G167" s="6"/>
-      <c r="H167" s="6"/>
-      <c r="I167" s="6"/>
-      <c r="J167" s="6"/>
-      <c r="K167" s="6"/>
+      <c r="A167" s="20"/>
+      <c r="B167" s="20"/>
+      <c r="C167" s="20"/>
+      <c r="D167" s="20"/>
+      <c r="E167" s="20"/>
+      <c r="F167" s="20"/>
+      <c r="G167" s="20"/>
+      <c r="H167" s="20"/>
+      <c r="I167" s="20"/>
+      <c r="J167" s="20"/>
+      <c r="K167" s="20"/>
     </row>
     <row r="168" spans="1:11">
-      <c r="A168" s="6"/>
-      <c r="B168" s="6"/>
-      <c r="C168" s="6"/>
-      <c r="D168" s="6"/>
-      <c r="E168" s="6"/>
-      <c r="F168" s="6"/>
-      <c r="G168" s="6"/>
-      <c r="H168" s="6"/>
-      <c r="I168" s="6"/>
-      <c r="J168" s="6"/>
-      <c r="K168" s="6"/>
+      <c r="A168" s="20"/>
+      <c r="B168" s="20"/>
+      <c r="C168" s="20"/>
+      <c r="D168" s="20"/>
+      <c r="E168" s="20"/>
+      <c r="F168" s="20"/>
+      <c r="G168" s="20"/>
+      <c r="H168" s="20"/>
+      <c r="I168" s="20"/>
+      <c r="J168" s="20"/>
+      <c r="K168" s="20"/>
     </row>
     <row r="169" spans="1:11">
-      <c r="A169" s="6"/>
-      <c r="B169" s="6"/>
-      <c r="C169" s="6"/>
-      <c r="D169" s="6"/>
-      <c r="E169" s="6"/>
-      <c r="F169" s="6"/>
-      <c r="G169" s="6"/>
-      <c r="H169" s="6"/>
-      <c r="I169" s="6"/>
-      <c r="J169" s="6"/>
-      <c r="K169" s="6"/>
+      <c r="A169" s="20"/>
+      <c r="B169" s="20"/>
+      <c r="C169" s="20"/>
+      <c r="D169" s="20"/>
+      <c r="E169" s="20"/>
+      <c r="F169" s="20"/>
+      <c r="G169" s="20"/>
+      <c r="H169" s="20"/>
+      <c r="I169" s="20"/>
+      <c r="J169" s="20"/>
+      <c r="K169" s="20"/>
     </row>
     <row r="170" spans="1:11">
-      <c r="A170" s="6"/>
-      <c r="B170" s="6"/>
-      <c r="C170" s="6"/>
-      <c r="D170" s="6"/>
-      <c r="E170" s="6"/>
-      <c r="F170" s="6"/>
-      <c r="G170" s="6"/>
-      <c r="H170" s="6"/>
-      <c r="I170" s="6"/>
-      <c r="J170" s="6"/>
-      <c r="K170" s="6"/>
+      <c r="A170" s="20"/>
+      <c r="B170" s="20"/>
+      <c r="C170" s="20"/>
+      <c r="D170" s="20"/>
+      <c r="E170" s="20"/>
+      <c r="F170" s="20"/>
+      <c r="G170" s="20"/>
+      <c r="H170" s="20"/>
+      <c r="I170" s="20"/>
+      <c r="J170" s="20"/>
+      <c r="K170" s="20"/>
     </row>
     <row r="171" spans="1:11">
-      <c r="A171" s="6"/>
-      <c r="B171" s="6"/>
-      <c r="C171" s="6"/>
-      <c r="D171" s="6"/>
-      <c r="E171" s="6"/>
-      <c r="F171" s="6"/>
-      <c r="G171" s="6"/>
-      <c r="H171" s="6"/>
-      <c r="I171" s="6"/>
-      <c r="J171" s="6"/>
-      <c r="K171" s="6"/>
+      <c r="A171" s="20"/>
+      <c r="B171" s="20"/>
+      <c r="C171" s="20"/>
+      <c r="D171" s="20"/>
+      <c r="E171" s="20"/>
+      <c r="F171" s="20"/>
+      <c r="G171" s="20"/>
+      <c r="H171" s="20"/>
+      <c r="I171" s="20"/>
+      <c r="J171" s="20"/>
+      <c r="K171" s="20"/>
     </row>
     <row r="172" spans="1:11">
-      <c r="A172" s="6"/>
-      <c r="B172" s="6"/>
-      <c r="C172" s="6"/>
-      <c r="D172" s="6"/>
-      <c r="E172" s="6"/>
-      <c r="F172" s="6"/>
-      <c r="G172" s="6"/>
-      <c r="H172" s="6"/>
-      <c r="I172" s="6"/>
-      <c r="J172" s="6"/>
-      <c r="K172" s="6"/>
+      <c r="A172" s="20"/>
+      <c r="B172" s="20"/>
+      <c r="C172" s="20"/>
+      <c r="D172" s="20"/>
+      <c r="E172" s="20"/>
+      <c r="F172" s="20"/>
+      <c r="G172" s="20"/>
+      <c r="H172" s="20"/>
+      <c r="I172" s="20"/>
+      <c r="J172" s="20"/>
+      <c r="K172" s="20"/>
     </row>
     <row r="173" spans="1:11">
-      <c r="A173" s="6"/>
-      <c r="B173" s="6"/>
-      <c r="C173" s="6"/>
-      <c r="D173" s="6"/>
-      <c r="E173" s="6"/>
-      <c r="F173" s="6"/>
-      <c r="G173" s="6"/>
-      <c r="H173" s="6"/>
-      <c r="I173" s="6"/>
-      <c r="J173" s="6"/>
-      <c r="K173" s="6"/>
+      <c r="A173" s="20"/>
+      <c r="B173" s="20"/>
+      <c r="C173" s="20"/>
+      <c r="D173" s="20"/>
+      <c r="E173" s="20"/>
+      <c r="F173" s="20"/>
+      <c r="G173" s="20"/>
+      <c r="H173" s="20"/>
+      <c r="I173" s="20"/>
+      <c r="J173" s="20"/>
+      <c r="K173" s="20"/>
     </row>
     <row r="174" spans="1:11">
-      <c r="A174" s="6"/>
-      <c r="B174" s="6"/>
-      <c r="C174" s="6"/>
-      <c r="D174" s="6"/>
-      <c r="E174" s="6"/>
-      <c r="F174" s="6"/>
-      <c r="G174" s="6"/>
-      <c r="H174" s="6"/>
-      <c r="I174" s="6"/>
-      <c r="J174" s="6"/>
-      <c r="K174" s="6"/>
+      <c r="A174" s="20"/>
+      <c r="B174" s="20"/>
+      <c r="C174" s="20"/>
+      <c r="D174" s="20"/>
+      <c r="E174" s="20"/>
+      <c r="F174" s="20"/>
+      <c r="G174" s="20"/>
+      <c r="H174" s="20"/>
+      <c r="I174" s="20"/>
+      <c r="J174" s="20"/>
+      <c r="K174" s="20"/>
     </row>
     <row r="175" spans="1:11">
-      <c r="A175" s="6"/>
-      <c r="B175" s="6"/>
-      <c r="C175" s="6"/>
-      <c r="D175" s="6"/>
-      <c r="E175" s="6"/>
-      <c r="F175" s="6"/>
-      <c r="G175" s="6"/>
-      <c r="H175" s="6"/>
-      <c r="I175" s="6"/>
-      <c r="J175" s="6"/>
-      <c r="K175" s="6"/>
+      <c r="A175" s="20"/>
+      <c r="B175" s="20"/>
+      <c r="C175" s="20"/>
+      <c r="D175" s="20"/>
+      <c r="E175" s="20"/>
+      <c r="F175" s="20"/>
+      <c r="G175" s="20"/>
+      <c r="H175" s="20"/>
+      <c r="I175" s="20"/>
+      <c r="J175" s="20"/>
+      <c r="K175" s="20"/>
     </row>
     <row r="176" spans="1:11">
-      <c r="A176" s="6"/>
-      <c r="B176" s="6"/>
-      <c r="C176" s="6"/>
-      <c r="D176" s="6"/>
-      <c r="E176" s="6"/>
-      <c r="F176" s="6"/>
-      <c r="G176" s="6"/>
-      <c r="H176" s="6"/>
-      <c r="I176" s="6"/>
-      <c r="J176" s="6"/>
-      <c r="K176" s="6"/>
+      <c r="A176" s="20"/>
+      <c r="B176" s="20"/>
+      <c r="C176" s="20"/>
+      <c r="D176" s="20"/>
+      <c r="E176" s="20"/>
+      <c r="F176" s="20"/>
+      <c r="G176" s="20"/>
+      <c r="H176" s="20"/>
+      <c r="I176" s="20"/>
+      <c r="J176" s="20"/>
+      <c r="K176" s="20"/>
     </row>
     <row r="177" spans="1:11">
-      <c r="A177" s="6"/>
-      <c r="B177" s="6"/>
-      <c r="C177" s="6"/>
-      <c r="D177" s="6"/>
-      <c r="E177" s="6"/>
-      <c r="F177" s="6"/>
-      <c r="G177" s="6"/>
-      <c r="H177" s="6"/>
-      <c r="I177" s="6"/>
-      <c r="J177" s="6"/>
-      <c r="K177" s="6"/>
+      <c r="A177" s="20"/>
+      <c r="B177" s="20"/>
+      <c r="C177" s="20"/>
+      <c r="D177" s="20"/>
+      <c r="E177" s="20"/>
+      <c r="F177" s="20"/>
+      <c r="G177" s="20"/>
+      <c r="H177" s="20"/>
+      <c r="I177" s="20"/>
+      <c r="J177" s="20"/>
+      <c r="K177" s="20"/>
     </row>
     <row r="178" spans="1:11">
-      <c r="A178" s="6"/>
-      <c r="B178" s="6"/>
-      <c r="C178" s="6"/>
-      <c r="D178" s="6"/>
-      <c r="E178" s="6"/>
-      <c r="F178" s="6"/>
-      <c r="G178" s="6"/>
-      <c r="H178" s="6"/>
-      <c r="I178" s="6"/>
-      <c r="J178" s="6"/>
-      <c r="K178" s="6"/>
+      <c r="A178" s="20"/>
+      <c r="B178" s="20"/>
+      <c r="C178" s="20"/>
+      <c r="D178" s="20"/>
+      <c r="E178" s="20"/>
+      <c r="F178" s="20"/>
+      <c r="G178" s="20"/>
+      <c r="H178" s="20"/>
+      <c r="I178" s="20"/>
+      <c r="J178" s="20"/>
+      <c r="K178" s="20"/>
     </row>
     <row r="179" spans="1:11">
-      <c r="A179" s="6"/>
-      <c r="B179" s="6"/>
-      <c r="C179" s="6"/>
-      <c r="D179" s="6"/>
-      <c r="E179" s="6"/>
-      <c r="F179" s="6"/>
-      <c r="G179" s="6"/>
-      <c r="H179" s="6"/>
-      <c r="I179" s="6"/>
-      <c r="J179" s="6"/>
-      <c r="K179" s="6"/>
+      <c r="A179" s="20"/>
+      <c r="B179" s="20"/>
+      <c r="C179" s="20"/>
+      <c r="D179" s="20"/>
+      <c r="E179" s="20"/>
+      <c r="F179" s="20"/>
+      <c r="G179" s="20"/>
+      <c r="H179" s="20"/>
+      <c r="I179" s="20"/>
+      <c r="J179" s="20"/>
+      <c r="K179" s="20"/>
     </row>
     <row r="180" spans="1:11">
-      <c r="A180" s="6"/>
-      <c r="B180" s="6"/>
-      <c r="C180" s="6"/>
-      <c r="D180" s="6"/>
-      <c r="E180" s="6"/>
-      <c r="F180" s="6"/>
-      <c r="G180" s="6"/>
-      <c r="H180" s="6"/>
-      <c r="I180" s="6"/>
-      <c r="J180" s="6"/>
-      <c r="K180" s="6"/>
+      <c r="A180" s="20"/>
+      <c r="B180" s="20"/>
+      <c r="C180" s="20"/>
+      <c r="D180" s="20"/>
+      <c r="E180" s="20"/>
+      <c r="F180" s="20"/>
+      <c r="G180" s="20"/>
+      <c r="H180" s="20"/>
+      <c r="I180" s="20"/>
+      <c r="J180" s="20"/>
+      <c r="K180" s="20"/>
     </row>
     <row r="181" spans="1:11">
-      <c r="A181" s="6"/>
-      <c r="B181" s="6"/>
-      <c r="C181" s="6"/>
-      <c r="D181" s="6"/>
-      <c r="E181" s="6"/>
-      <c r="F181" s="6"/>
-      <c r="G181" s="6"/>
-      <c r="H181" s="6"/>
-      <c r="I181" s="6"/>
-      <c r="J181" s="6"/>
-      <c r="K181" s="6"/>
+      <c r="A181" s="20"/>
+      <c r="B181" s="20"/>
+      <c r="C181" s="20"/>
+      <c r="D181" s="20"/>
+      <c r="E181" s="20"/>
+      <c r="F181" s="20"/>
+      <c r="G181" s="20"/>
+      <c r="H181" s="20"/>
+      <c r="I181" s="20"/>
+      <c r="J181" s="20"/>
+      <c r="K181" s="20"/>
     </row>
     <row r="182" spans="1:11">
-      <c r="A182" s="6"/>
-      <c r="B182" s="6"/>
-      <c r="C182" s="6"/>
-      <c r="D182" s="6"/>
-      <c r="E182" s="6"/>
-      <c r="F182" s="6"/>
-      <c r="G182" s="6"/>
-      <c r="H182" s="6"/>
-      <c r="I182" s="6"/>
-      <c r="J182" s="6"/>
-      <c r="K182" s="6"/>
+      <c r="A182" s="20"/>
+      <c r="B182" s="20"/>
+      <c r="C182" s="20"/>
+      <c r="D182" s="20"/>
+      <c r="E182" s="20"/>
+      <c r="F182" s="20"/>
+      <c r="G182" s="20"/>
+      <c r="H182" s="20"/>
+      <c r="I182" s="20"/>
+      <c r="J182" s="20"/>
+      <c r="K182" s="20"/>
     </row>
     <row r="183" spans="1:11">
-      <c r="A183" s="6"/>
-      <c r="B183" s="6"/>
-      <c r="C183" s="6"/>
-      <c r="D183" s="6"/>
-      <c r="E183" s="6"/>
-      <c r="F183" s="6"/>
-      <c r="G183" s="6"/>
-      <c r="H183" s="6"/>
-      <c r="I183" s="6"/>
-      <c r="J183" s="6"/>
-      <c r="K183" s="6"/>
+      <c r="A183" s="20"/>
+      <c r="B183" s="20"/>
+      <c r="C183" s="20"/>
+      <c r="D183" s="20"/>
+      <c r="E183" s="20"/>
+      <c r="F183" s="20"/>
+      <c r="G183" s="20"/>
+      <c r="H183" s="20"/>
+      <c r="I183" s="20"/>
+      <c r="J183" s="20"/>
+      <c r="K183" s="20"/>
     </row>
     <row r="184" spans="1:11">
-      <c r="A184" s="6"/>
-      <c r="B184" s="6"/>
-      <c r="C184" s="6"/>
-      <c r="D184" s="6"/>
-      <c r="E184" s="6"/>
-      <c r="F184" s="6"/>
-      <c r="G184" s="6"/>
-      <c r="H184" s="6"/>
-      <c r="I184" s="6"/>
-      <c r="J184" s="6"/>
-      <c r="K184" s="6"/>
+      <c r="A184" s="20"/>
+      <c r="B184" s="20"/>
+      <c r="C184" s="20"/>
+      <c r="D184" s="20"/>
+      <c r="E184" s="20"/>
+      <c r="F184" s="20"/>
+      <c r="G184" s="20"/>
+      <c r="H184" s="20"/>
+      <c r="I184" s="20"/>
+      <c r="J184" s="20"/>
+      <c r="K184" s="20"/>
     </row>
     <row r="185" spans="1:11">
-      <c r="A185" s="6"/>
-      <c r="B185" s="6"/>
-      <c r="C185" s="6"/>
-      <c r="D185" s="6"/>
-      <c r="E185" s="6"/>
-      <c r="F185" s="6"/>
-      <c r="G185" s="6"/>
-      <c r="H185" s="6"/>
-      <c r="I185" s="6"/>
-      <c r="J185" s="6"/>
-      <c r="K185" s="6"/>
+      <c r="A185" s="20"/>
+      <c r="B185" s="20"/>
+      <c r="C185" s="20"/>
+      <c r="D185" s="20"/>
+      <c r="E185" s="20"/>
+      <c r="F185" s="20"/>
+      <c r="G185" s="20"/>
+      <c r="H185" s="20"/>
+      <c r="I185" s="20"/>
+      <c r="J185" s="20"/>
+      <c r="K185" s="20"/>
     </row>
     <row r="186" spans="1:11">
-      <c r="A186" s="6"/>
-      <c r="B186" s="6"/>
-      <c r="C186" s="6"/>
-      <c r="D186" s="6"/>
-      <c r="E186" s="6"/>
-      <c r="F186" s="6"/>
-      <c r="G186" s="6"/>
-      <c r="H186" s="6"/>
-      <c r="I186" s="6"/>
-      <c r="J186" s="6"/>
-      <c r="K186" s="6"/>
+      <c r="A186" s="20"/>
+      <c r="B186" s="20"/>
+      <c r="C186" s="20"/>
+      <c r="D186" s="20"/>
+      <c r="E186" s="20"/>
+      <c r="F186" s="20"/>
+      <c r="G186" s="20"/>
+      <c r="H186" s="20"/>
+      <c r="I186" s="20"/>
+      <c r="J186" s="20"/>
+      <c r="K186" s="20"/>
     </row>
     <row r="187" spans="1:11">
-      <c r="A187" s="6"/>
-      <c r="B187" s="6"/>
-      <c r="C187" s="6"/>
-      <c r="D187" s="6"/>
-      <c r="E187" s="6"/>
-      <c r="F187" s="6"/>
-      <c r="G187" s="6"/>
-      <c r="H187" s="6"/>
-      <c r="I187" s="6"/>
-      <c r="J187" s="6"/>
-      <c r="K187" s="6"/>
+      <c r="A187" s="20"/>
+      <c r="B187" s="20"/>
+      <c r="C187" s="20"/>
+      <c r="D187" s="20"/>
+      <c r="E187" s="20"/>
+      <c r="F187" s="20"/>
+      <c r="G187" s="20"/>
+      <c r="H187" s="20"/>
+      <c r="I187" s="20"/>
+      <c r="J187" s="20"/>
+      <c r="K187" s="20"/>
     </row>
     <row r="188" spans="1:11">
-      <c r="A188" s="6"/>
-      <c r="B188" s="6"/>
-      <c r="C188" s="6"/>
-      <c r="D188" s="6"/>
-      <c r="E188" s="6"/>
-      <c r="F188" s="6"/>
-      <c r="G188" s="6"/>
-      <c r="H188" s="6"/>
-      <c r="I188" s="6"/>
-      <c r="J188" s="6"/>
-      <c r="K188" s="6"/>
+      <c r="A188" s="20"/>
+      <c r="B188" s="20"/>
+      <c r="C188" s="20"/>
+      <c r="D188" s="20"/>
+      <c r="E188" s="20"/>
+      <c r="F188" s="20"/>
+      <c r="G188" s="20"/>
+      <c r="H188" s="20"/>
+      <c r="I188" s="20"/>
+      <c r="J188" s="20"/>
+      <c r="K188" s="20"/>
     </row>
     <row r="189" spans="1:11">
-      <c r="A189" s="6"/>
-      <c r="B189" s="6"/>
-      <c r="C189" s="6"/>
-      <c r="D189" s="6"/>
-      <c r="E189" s="6"/>
-      <c r="F189" s="6"/>
-      <c r="G189" s="6"/>
-      <c r="H189" s="6"/>
-      <c r="I189" s="6"/>
-      <c r="J189" s="6"/>
-      <c r="K189" s="6"/>
+      <c r="A189" s="20"/>
+      <c r="B189" s="20"/>
+      <c r="C189" s="20"/>
+      <c r="D189" s="20"/>
+      <c r="E189" s="20"/>
+      <c r="F189" s="20"/>
+      <c r="G189" s="20"/>
+      <c r="H189" s="20"/>
+      <c r="I189" s="20"/>
+      <c r="J189" s="20"/>
+      <c r="K189" s="20"/>
     </row>
     <row r="190" spans="1:11">
-      <c r="A190" s="6"/>
-      <c r="B190" s="6"/>
-      <c r="C190" s="6"/>
-      <c r="D190" s="6"/>
-      <c r="E190" s="6"/>
-      <c r="F190" s="6"/>
-      <c r="G190" s="6"/>
-      <c r="H190" s="6"/>
-      <c r="I190" s="6"/>
-      <c r="J190" s="6"/>
-      <c r="K190" s="6"/>
+      <c r="A190" s="20"/>
+      <c r="B190" s="20"/>
+      <c r="C190" s="20"/>
+      <c r="D190" s="20"/>
+      <c r="E190" s="20"/>
+      <c r="F190" s="20"/>
+      <c r="G190" s="20"/>
+      <c r="H190" s="20"/>
+      <c r="I190" s="20"/>
+      <c r="J190" s="20"/>
+      <c r="K190" s="20"/>
     </row>
     <row r="191" spans="1:11">
-      <c r="A191" s="6"/>
-      <c r="B191" s="6"/>
-      <c r="C191" s="6"/>
-      <c r="D191" s="6"/>
-      <c r="E191" s="6"/>
-      <c r="F191" s="6"/>
-      <c r="G191" s="6"/>
-      <c r="H191" s="6"/>
-      <c r="I191" s="6"/>
-      <c r="J191" s="6"/>
-      <c r="K191" s="6"/>
+      <c r="A191" s="20"/>
+      <c r="B191" s="20"/>
+      <c r="C191" s="20"/>
+      <c r="D191" s="20"/>
+      <c r="E191" s="20"/>
+      <c r="F191" s="20"/>
+      <c r="G191" s="20"/>
+      <c r="H191" s="20"/>
+      <c r="I191" s="20"/>
+      <c r="J191" s="20"/>
+      <c r="K191" s="20"/>
     </row>
     <row r="192" spans="1:11">
-      <c r="A192" s="6"/>
-      <c r="B192" s="6"/>
-      <c r="C192" s="6"/>
-      <c r="D192" s="6"/>
-      <c r="E192" s="6"/>
-      <c r="F192" s="6"/>
-      <c r="G192" s="6"/>
-      <c r="H192" s="6"/>
-      <c r="I192" s="6"/>
-      <c r="J192" s="6"/>
-      <c r="K192" s="6"/>
+      <c r="A192" s="20"/>
+      <c r="B192" s="20"/>
+      <c r="C192" s="20"/>
+      <c r="D192" s="20"/>
+      <c r="E192" s="20"/>
+      <c r="F192" s="20"/>
+      <c r="G192" s="20"/>
+      <c r="H192" s="20"/>
+      <c r="I192" s="20"/>
+      <c r="J192" s="20"/>
+      <c r="K192" s="20"/>
     </row>
     <row r="193" spans="1:11">
-      <c r="A193" s="6"/>
-      <c r="B193" s="6"/>
-      <c r="C193" s="6"/>
-      <c r="D193" s="6"/>
-      <c r="E193" s="6"/>
-      <c r="F193" s="6"/>
-      <c r="G193" s="6"/>
-      <c r="H193" s="6"/>
-      <c r="I193" s="6"/>
-      <c r="J193" s="6"/>
-      <c r="K193" s="6"/>
+      <c r="A193" s="20"/>
+      <c r="B193" s="20"/>
+      <c r="C193" s="20"/>
+      <c r="D193" s="20"/>
+      <c r="E193" s="20"/>
+      <c r="F193" s="20"/>
+      <c r="G193" s="20"/>
+      <c r="H193" s="20"/>
+      <c r="I193" s="20"/>
+      <c r="J193" s="20"/>
+      <c r="K193" s="20"/>
     </row>
     <row r="194" spans="1:11">
-      <c r="A194" s="6"/>
-      <c r="B194" s="6"/>
-      <c r="C194" s="6"/>
-      <c r="D194" s="6"/>
-      <c r="E194" s="6"/>
-      <c r="F194" s="6"/>
-      <c r="G194" s="6"/>
-      <c r="H194" s="6"/>
-      <c r="I194" s="6"/>
-      <c r="J194" s="6"/>
-      <c r="K194" s="6"/>
+      <c r="A194" s="20"/>
+      <c r="B194" s="20"/>
+      <c r="C194" s="20"/>
+      <c r="D194" s="20"/>
+      <c r="E194" s="20"/>
+      <c r="F194" s="20"/>
+      <c r="G194" s="20"/>
+      <c r="H194" s="20"/>
+      <c r="I194" s="20"/>
+      <c r="J194" s="20"/>
+      <c r="K194" s="20"/>
     </row>
     <row r="195" spans="1:11">
-      <c r="A195" s="6"/>
-      <c r="B195" s="6"/>
-      <c r="C195" s="6"/>
-      <c r="D195" s="6"/>
-      <c r="E195" s="6"/>
-      <c r="F195" s="6"/>
-      <c r="G195" s="6"/>
-      <c r="H195" s="6"/>
-      <c r="I195" s="6"/>
-      <c r="J195" s="6"/>
-      <c r="K195" s="6"/>
+      <c r="A195" s="20"/>
+      <c r="B195" s="20"/>
+      <c r="C195" s="20"/>
+      <c r="D195" s="20"/>
+      <c r="E195" s="20"/>
+      <c r="F195" s="20"/>
+      <c r="G195" s="20"/>
+      <c r="H195" s="20"/>
+      <c r="I195" s="20"/>
+      <c r="J195" s="20"/>
+      <c r="K195" s="20"/>
     </row>
     <row r="196" spans="1:11">
-      <c r="A196" s="6"/>
-      <c r="B196" s="6"/>
-      <c r="C196" s="6"/>
-      <c r="D196" s="6"/>
-      <c r="E196" s="6"/>
-      <c r="F196" s="6"/>
-      <c r="G196" s="6"/>
-      <c r="H196" s="6"/>
-      <c r="I196" s="6"/>
-      <c r="J196" s="6"/>
-      <c r="K196" s="6"/>
+      <c r="A196" s="20"/>
+      <c r="B196" s="20"/>
+      <c r="C196" s="20"/>
+      <c r="D196" s="20"/>
+      <c r="E196" s="20"/>
+      <c r="F196" s="20"/>
+      <c r="G196" s="20"/>
+      <c r="H196" s="20"/>
+      <c r="I196" s="20"/>
+      <c r="J196" s="20"/>
+      <c r="K196" s="20"/>
     </row>
     <row r="197" spans="1:11">
-      <c r="A197" s="6"/>
-      <c r="B197" s="6"/>
-      <c r="C197" s="6"/>
-      <c r="D197" s="6"/>
-      <c r="E197" s="6"/>
-      <c r="F197" s="6"/>
-      <c r="G197" s="6"/>
-      <c r="H197" s="6"/>
-      <c r="I197" s="6"/>
-      <c r="J197" s="6"/>
-      <c r="K197" s="6"/>
+      <c r="A197" s="20"/>
+      <c r="B197" s="20"/>
+      <c r="C197" s="20"/>
+      <c r="D197" s="20"/>
+      <c r="E197" s="20"/>
+      <c r="F197" s="20"/>
+      <c r="G197" s="20"/>
+      <c r="H197" s="20"/>
+      <c r="I197" s="20"/>
+      <c r="J197" s="20"/>
+      <c r="K197" s="20"/>
     </row>
     <row r="198" spans="1:11">
-      <c r="A198" s="6"/>
-      <c r="B198" s="6"/>
-      <c r="C198" s="6"/>
-      <c r="D198" s="6"/>
-      <c r="E198" s="6"/>
-      <c r="F198" s="6"/>
-      <c r="G198" s="6"/>
-      <c r="H198" s="6"/>
-      <c r="I198" s="6"/>
-      <c r="J198" s="6"/>
-      <c r="K198" s="6"/>
+      <c r="A198" s="20"/>
+      <c r="B198" s="20"/>
+      <c r="C198" s="20"/>
+      <c r="D198" s="20"/>
+      <c r="E198" s="20"/>
+      <c r="F198" s="20"/>
+      <c r="G198" s="20"/>
+      <c r="H198" s="20"/>
+      <c r="I198" s="20"/>
+      <c r="J198" s="20"/>
+      <c r="K198" s="20"/>
     </row>
     <row r="199" spans="1:11">
-      <c r="A199" s="6"/>
-      <c r="B199" s="6"/>
-      <c r="C199" s="6"/>
-      <c r="D199" s="6"/>
-      <c r="E199" s="6"/>
-      <c r="F199" s="6"/>
-      <c r="G199" s="6"/>
-      <c r="H199" s="6"/>
-      <c r="I199" s="6"/>
-      <c r="J199" s="6"/>
-      <c r="K199" s="6"/>
+      <c r="A199" s="20"/>
+      <c r="B199" s="20"/>
+      <c r="C199" s="20"/>
+      <c r="D199" s="20"/>
+      <c r="E199" s="20"/>
+      <c r="F199" s="20"/>
+      <c r="G199" s="20"/>
+      <c r="H199" s="20"/>
+      <c r="I199" s="20"/>
+      <c r="J199" s="20"/>
+      <c r="K199" s="20"/>
     </row>
     <row r="200" spans="1:11">
-      <c r="A200" s="6"/>
-      <c r="B200" s="6"/>
-      <c r="C200" s="6"/>
-      <c r="D200" s="6"/>
-      <c r="E200" s="6"/>
-      <c r="F200" s="6"/>
-      <c r="G200" s="6"/>
-      <c r="H200" s="6"/>
-      <c r="I200" s="6"/>
-      <c r="J200" s="6"/>
-      <c r="K200" s="6"/>
+      <c r="A200" s="20"/>
+      <c r="B200" s="20"/>
+      <c r="C200" s="20"/>
+      <c r="D200" s="20"/>
+      <c r="E200" s="20"/>
+      <c r="F200" s="20"/>
+      <c r="G200" s="20"/>
+      <c r="H200" s="20"/>
+      <c r="I200" s="20"/>
+      <c r="J200" s="20"/>
+      <c r="K200" s="20"/>
     </row>
     <row r="201" spans="1:11">
-      <c r="A201" s="6"/>
-      <c r="B201" s="6"/>
-      <c r="C201" s="6"/>
-      <c r="D201" s="6"/>
-      <c r="E201" s="6"/>
-      <c r="F201" s="6"/>
-      <c r="G201" s="6"/>
-      <c r="H201" s="6"/>
-      <c r="I201" s="6"/>
-      <c r="J201" s="6"/>
-      <c r="K201" s="6"/>
+      <c r="A201" s="20"/>
+      <c r="B201" s="20"/>
+      <c r="C201" s="20"/>
+      <c r="D201" s="20"/>
+      <c r="E201" s="20"/>
+      <c r="F201" s="20"/>
+      <c r="G201" s="20"/>
+      <c r="H201" s="20"/>
+      <c r="I201" s="20"/>
+      <c r="J201" s="20"/>
+      <c r="K201" s="20"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -4035,6 +4147,8 @@
   <hyperlinks>
     <hyperlink ref="I3" r:id="rId1" xr:uid="{08EFECAE-71E2-7F41-8591-76D48AF259CA}"/>
     <hyperlink ref="J3" r:id="rId2" xr:uid="{631B9F73-7FA5-AC4A-8DC8-BB9639841662}"/>
+    <hyperlink ref="I6" r:id="rId3" xr:uid="{41BBCAD2-13FE-474B-BE55-5B6F2FCBB1FA}"/>
+    <hyperlink ref="I5" r:id="rId4" xr:uid="{BE333321-8F9A-2542-B29F-589152EDD6E9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4119,17 +4233,17 @@
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>120</v>
+        <v>117</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>118</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="13" t="s">
-        <v>121</v>
+      <c r="F3" s="12" t="s">
+        <v>119</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
@@ -4140,17 +4254,17 @@
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>123</v>
+        <v>120</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>121</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="13" t="s">
-        <v>121</v>
+      <c r="F4" s="12" t="s">
+        <v>119</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
@@ -4161,17 +4275,17 @@
         <v>1</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>125</v>
+        <v>122</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>123</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F5" s="13" t="s">
-        <v>121</v>
+      <c r="F5" s="12" t="s">
+        <v>119</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
@@ -4182,17 +4296,17 @@
         <v>1</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>127</v>
+        <v>124</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>125</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F6" s="13" t="s">
-        <v>128</v>
+      <c r="F6" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
@@ -4203,17 +4317,17 @@
         <v>1</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>130</v>
+        <v>127</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>128</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="13" t="s">
-        <v>128</v>
+      <c r="F7" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
@@ -4224,17 +4338,17 @@
         <v>1</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>132</v>
+        <v>129</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="13" t="s">
-        <v>128</v>
+      <c r="F8" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
@@ -4245,17 +4359,17 @@
         <v>1</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>134</v>
+        <v>131</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>132</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F9" s="13" t="s">
-        <v>135</v>
+      <c r="F9" s="12" t="s">
+        <v>133</v>
       </c>
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
@@ -4266,17 +4380,17 @@
         <v>1</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>137</v>
+        <v>134</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>135</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F10" s="13" t="s">
-        <v>135</v>
+      <c r="F10" s="12" t="s">
+        <v>133</v>
       </c>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
@@ -4287,17 +4401,17 @@
         <v>1</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>139</v>
+        <v>136</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>137</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="13" t="s">
-        <v>135</v>
+      <c r="F11" s="12" t="s">
+        <v>133</v>
       </c>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
@@ -4308,17 +4422,17 @@
         <v>1</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>141</v>
+        <v>138</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>139</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="13" t="s">
-        <v>135</v>
+      <c r="F12" s="12" t="s">
+        <v>133</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
@@ -4329,17 +4443,17 @@
         <v>1</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>143</v>
+        <v>140</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>141</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="13" t="s">
-        <v>135</v>
+      <c r="F13" s="12" t="s">
+        <v>133</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
@@ -4350,17 +4464,17 @@
         <v>1</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>145</v>
+        <v>142</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>143</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>135</v>
+      <c r="F14" s="12" t="s">
+        <v>133</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
@@ -4371,17 +4485,17 @@
         <v>1</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>147</v>
+        <v>144</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>145</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>135</v>
+      <c r="F15" s="12" t="s">
+        <v>133</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
@@ -4392,17 +4506,17 @@
         <v>1</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>149</v>
+        <v>146</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>147</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F16" s="13" t="s">
-        <v>150</v>
+      <c r="F16" s="12" t="s">
+        <v>148</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
@@ -4413,17 +4527,17 @@
         <v>1</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>152</v>
+        <v>149</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>150</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="13" t="s">
-        <v>150</v>
+      <c r="F17" s="12" t="s">
+        <v>148</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
@@ -4434,17 +4548,17 @@
         <v>1</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>154</v>
+        <v>151</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>152</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F18" s="13" t="s">
-        <v>150</v>
+      <c r="F18" s="12" t="s">
+        <v>148</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
@@ -4455,17 +4569,17 @@
         <v>1</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>156</v>
+        <v>153</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>154</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F19" s="13" t="s">
-        <v>150</v>
+      <c r="F19" s="12" t="s">
+        <v>148</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
@@ -4476,17 +4590,17 @@
         <v>1</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>158</v>
+        <v>155</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>156</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F20" s="13" t="s">
-        <v>159</v>
+      <c r="F20" s="12" t="s">
+        <v>157</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
@@ -4497,17 +4611,17 @@
         <v>1</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>161</v>
+        <v>158</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>159</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F21" s="13" t="s">
-        <v>159</v>
+      <c r="F21" s="12" t="s">
+        <v>157</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
@@ -4518,17 +4632,17 @@
         <v>1</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>163</v>
+        <v>160</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>161</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>159</v>
+      <c r="F22" s="12" t="s">
+        <v>157</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
@@ -4539,17 +4653,17 @@
         <v>1</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>165</v>
+        <v>162</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>163</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F23" s="13" t="s">
-        <v>166</v>
+      <c r="F23" s="12" t="s">
+        <v>164</v>
       </c>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
@@ -4560,17 +4674,17 @@
         <v>1</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>168</v>
+        <v>165</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>166</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F24" s="13" t="s">
-        <v>166</v>
+      <c r="F24" s="12" t="s">
+        <v>164</v>
       </c>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
@@ -4581,17 +4695,17 @@
         <v>1</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>170</v>
+        <v>167</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>168</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F25" s="13" t="s">
-        <v>171</v>
+      <c r="F25" s="12" t="s">
+        <v>169</v>
       </c>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
@@ -4602,17 +4716,17 @@
         <v>1</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>173</v>
+        <v>170</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>171</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F26" s="13" t="s">
-        <v>171</v>
+      <c r="F26" s="12" t="s">
+        <v>169</v>
       </c>
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
@@ -4623,17 +4737,17 @@
         <v>1</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>175</v>
+        <v>172</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>173</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F27" s="13" t="s">
-        <v>176</v>
+      <c r="F27" s="12" t="s">
+        <v>174</v>
       </c>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
@@ -4644,17 +4758,17 @@
         <v>1</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>178</v>
+        <v>175</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>176</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F28" s="13" t="s">
-        <v>176</v>
+      <c r="F28" s="12" t="s">
+        <v>174</v>
       </c>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
@@ -4665,17 +4779,17 @@
         <v>1</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>180</v>
+        <v>177</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>178</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>176</v>
+      <c r="F29" s="12" t="s">
+        <v>174</v>
       </c>
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
@@ -4686,17 +4800,17 @@
         <v>1</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>182</v>
+        <v>179</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>180</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>135</v>
+        <v>181</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>133</v>
       </c>
       <c r="G30" s="6"/>
       <c r="H30" s="6"/>
@@ -4707,17 +4821,17 @@
         <v>1</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>185</v>
+        <v>182</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>183</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>135</v>
+        <v>181</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>133</v>
       </c>
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
@@ -4728,17 +4842,17 @@
         <v>1</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>187</v>
+        <v>184</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>185</v>
       </c>
       <c r="D32" s="6"/>
       <c r="E32" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F32" s="13" t="s">
-        <v>135</v>
+        <v>181</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>133</v>
       </c>
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
@@ -4749,17 +4863,17 @@
         <v>1</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>189</v>
+        <v>186</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>187</v>
       </c>
       <c r="D33" s="6"/>
       <c r="E33" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>150</v>
+        <v>181</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>148</v>
       </c>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
@@ -4770,17 +4884,17 @@
         <v>1</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="C34" s="13" t="s">
-        <v>191</v>
+        <v>188</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>189</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>150</v>
+        <v>181</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>148</v>
       </c>
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
@@ -4791,17 +4905,17 @@
         <v>1</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="C35" s="13" t="s">
-        <v>193</v>
+        <v>190</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>191</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F35" s="13" t="s">
-        <v>194</v>
+        <v>181</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>192</v>
       </c>
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
@@ -4812,17 +4926,17 @@
         <v>1</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>196</v>
+        <v>193</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>194</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F36" s="13" t="s">
-        <v>194</v>
+        <v>181</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>192</v>
       </c>
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
@@ -4833,17 +4947,17 @@
         <v>1</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>198</v>
+        <v>195</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>196</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F37" s="13" t="s">
-        <v>194</v>
+        <v>181</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>192</v>
       </c>
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
@@ -4854,17 +4968,17 @@
         <v>1</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="C38" s="13" t="s">
-        <v>200</v>
+        <v>197</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>198</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F38" s="13" t="s">
-        <v>194</v>
+        <v>181</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>192</v>
       </c>
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
@@ -4875,17 +4989,17 @@
         <v>1</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>202</v>
+        <v>199</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>200</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F39" s="13" t="s">
-        <v>194</v>
+        <v>181</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>192</v>
       </c>
       <c r="G39" s="6"/>
       <c r="H39" s="6"/>
@@ -4896,17 +5010,17 @@
         <v>1</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="C40" s="13" t="s">
-        <v>204</v>
+        <v>201</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>202</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F40" s="13" t="s">
-        <v>194</v>
+        <v>181</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>192</v>
       </c>
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
@@ -4917,17 +5031,17 @@
         <v>1</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>206</v>
+        <v>203</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>204</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F41" s="13" t="s">
-        <v>194</v>
+        <v>181</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>192</v>
       </c>
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
@@ -4938,17 +5052,17 @@
         <v>1</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="C42" s="13" t="s">
-        <v>208</v>
+        <v>205</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>206</v>
       </c>
       <c r="D42" s="6"/>
       <c r="E42" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F42" s="13" t="s">
-        <v>194</v>
+        <v>181</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>192</v>
       </c>
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
@@ -4959,17 +5073,17 @@
         <v>1</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="C43" s="13" t="s">
-        <v>210</v>
+        <v>207</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>208</v>
       </c>
       <c r="D43" s="6"/>
       <c r="E43" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F43" s="13" t="s">
-        <v>194</v>
+        <v>181</v>
+      </c>
+      <c r="F43" s="12" t="s">
+        <v>192</v>
       </c>
       <c r="G43" s="6"/>
       <c r="H43" s="6"/>
@@ -4980,17 +5094,17 @@
         <v>1</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="C44" s="13" t="s">
-        <v>212</v>
+        <v>209</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>210</v>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F44" s="13" t="s">
-        <v>194</v>
+        <v>181</v>
+      </c>
+      <c r="F44" s="12" t="s">
+        <v>192</v>
       </c>
       <c r="G44" s="6"/>
       <c r="H44" s="6"/>
@@ -5001,17 +5115,17 @@
         <v>1</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="C45" s="13" t="s">
-        <v>214</v>
+        <v>211</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>212</v>
       </c>
       <c r="D45" s="6"/>
       <c r="E45" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F45" s="13" t="s">
-        <v>159</v>
+        <v>181</v>
+      </c>
+      <c r="F45" s="12" t="s">
+        <v>157</v>
       </c>
       <c r="G45" s="6"/>
       <c r="H45" s="6"/>
@@ -5022,17 +5136,17 @@
         <v>1</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="C46" s="13" t="s">
-        <v>173</v>
+        <v>213</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>171</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F46" s="13" t="s">
-        <v>159</v>
+        <v>181</v>
+      </c>
+      <c r="F46" s="12" t="s">
+        <v>157</v>
       </c>
       <c r="G46" s="6"/>
       <c r="H46" s="6"/>
@@ -5043,17 +5157,17 @@
         <v>1</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="C47" s="13" t="s">
-        <v>217</v>
+        <v>214</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>215</v>
       </c>
       <c r="D47" s="6"/>
       <c r="E47" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F47" s="13" t="s">
-        <v>159</v>
+        <v>181</v>
+      </c>
+      <c r="F47" s="12" t="s">
+        <v>157</v>
       </c>
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
@@ -5064,17 +5178,17 @@
         <v>1</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="C48" s="13" t="s">
-        <v>175</v>
+        <v>216</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>173</v>
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F48" s="13" t="s">
-        <v>166</v>
+        <v>181</v>
+      </c>
+      <c r="F48" s="12" t="s">
+        <v>164</v>
       </c>
       <c r="G48" s="6"/>
       <c r="H48" s="6"/>
@@ -5085,17 +5199,17 @@
         <v>1</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>220</v>
+        <v>217</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>218</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F49" s="13" t="s">
-        <v>166</v>
+        <v>181</v>
+      </c>
+      <c r="F49" s="12" t="s">
+        <v>164</v>
       </c>
       <c r="G49" s="6"/>
       <c r="H49" s="6"/>
@@ -5106,17 +5220,17 @@
         <v>1</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="C50" s="13" t="s">
-        <v>222</v>
+        <v>219</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>220</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F50" s="13" t="s">
-        <v>166</v>
+        <v>181</v>
+      </c>
+      <c r="F50" s="12" t="s">
+        <v>164</v>
       </c>
       <c r="G50" s="6"/>
       <c r="H50" s="6"/>
@@ -5127,17 +5241,17 @@
         <v>1</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="C51" s="13" t="s">
-        <v>224</v>
+        <v>221</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>222</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F51" s="13" t="s">
-        <v>171</v>
+        <v>181</v>
+      </c>
+      <c r="F51" s="12" t="s">
+        <v>169</v>
       </c>
       <c r="G51" s="6"/>
       <c r="H51" s="6"/>
@@ -5148,17 +5262,17 @@
         <v>1</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="C52" s="13" t="s">
-        <v>226</v>
+        <v>223</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>224</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F52" s="13" t="s">
-        <v>171</v>
+        <v>181</v>
+      </c>
+      <c r="F52" s="12" t="s">
+        <v>169</v>
       </c>
       <c r="G52" s="6"/>
       <c r="H52" s="6"/>
@@ -5169,17 +5283,17 @@
         <v>1</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="C53" s="13" t="s">
-        <v>228</v>
+        <v>225</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>226</v>
       </c>
       <c r="D53" s="6"/>
       <c r="E53" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F53" s="13" t="s">
-        <v>171</v>
+        <v>181</v>
+      </c>
+      <c r="F53" s="12" t="s">
+        <v>169</v>
       </c>
       <c r="G53" s="6"/>
       <c r="H53" s="6"/>
@@ -5190,17 +5304,17 @@
         <v>1</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="C54" s="13" t="s">
-        <v>230</v>
+        <v>227</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>228</v>
       </c>
       <c r="D54" s="6"/>
       <c r="E54" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F54" s="13" t="s">
-        <v>171</v>
+        <v>181</v>
+      </c>
+      <c r="F54" s="12" t="s">
+        <v>169</v>
       </c>
       <c r="G54" s="6"/>
       <c r="H54" s="6"/>
@@ -5211,17 +5325,17 @@
         <v>1</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="C55" s="13" t="s">
-        <v>232</v>
+        <v>229</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>230</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F55" s="13" t="s">
-        <v>171</v>
+        <v>181</v>
+      </c>
+      <c r="F55" s="12" t="s">
+        <v>169</v>
       </c>
       <c r="G55" s="6"/>
       <c r="H55" s="6"/>
@@ -5232,17 +5346,17 @@
         <v>1</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="C56" s="13" t="s">
-        <v>234</v>
+        <v>231</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>232</v>
       </c>
       <c r="D56" s="6"/>
       <c r="E56" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F56" s="13" t="s">
-        <v>235</v>
+        <v>181</v>
+      </c>
+      <c r="F56" s="12" t="s">
+        <v>233</v>
       </c>
       <c r="G56" s="6"/>
       <c r="H56" s="6"/>
@@ -5253,17 +5367,17 @@
         <v>1</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="C57" s="13" t="s">
-        <v>237</v>
+        <v>234</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>235</v>
       </c>
       <c r="D57" s="6"/>
       <c r="E57" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F57" s="13" t="s">
-        <v>238</v>
+        <v>181</v>
+      </c>
+      <c r="F57" s="12" t="s">
+        <v>236</v>
       </c>
       <c r="G57" s="6"/>
       <c r="H57" s="6"/>
@@ -5274,17 +5388,17 @@
         <v>1</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="C58" s="13" t="s">
-        <v>240</v>
+        <v>237</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>238</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F58" s="13" t="s">
-        <v>241</v>
+        <v>181</v>
+      </c>
+      <c r="F58" s="12" t="s">
+        <v>239</v>
       </c>
       <c r="G58" s="6"/>
       <c r="H58" s="6"/>
